--- a/biodym_mfa_tool/data/02_output/results_scientific_baseline.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific_baseline.xlsx
@@ -364,9 +364,9 @@
     <t>CC_F_09_10</t>
   </si>
   <si>
-    <t>[0.4   0.408 0.416 0.424 0.432 0.44  0.448 0.456 0.464 0.472 0.48  0.488
- 0.496 0.504 0.512 0.52  0.528 0.536 0.544 0.552 0.56  0.568 0.576 0.584
- 0.592 0.6  ]</t>
+    <t>[0.5   0.504 0.508 0.512 0.516 0.52  0.524 0.528 0.532 0.536 0.54  0.544
+ 0.548 0.552 0.556 0.56  0.564 0.568 0.572 0.576 0.58  0.584 0.588 0.592
+ 0.596 0.6  ]</t>
   </si>
   <si>
     <t>[0.3   0.296 0.292 0.288 0.284 0.28  0.276 0.272 0.268 0.264 0.26  0.256
@@ -374,9 +374,8 @@
  0.204 0.2  ]</t>
   </si>
   <si>
-    <t>[0.2   0.208 0.216 0.224 0.232 0.24  0.248 0.256 0.264 0.272 0.28  0.288
- 0.296 0.304 0.312 0.32  0.328 0.336 0.344 0.352 0.36  0.368 0.376 0.384
- 0.392 0.4  ]</t>
+    <t>[0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2
+ 0.2 0.2 0.2 0.2 0.2 0.2 0.2 0.2]</t>
   </si>
   <si>
     <t>Metric</t>
@@ -4429,16 +4428,16 @@
         <v>2025</v>
       </c>
       <c r="C184">
-        <v>151838.95772</v>
+        <v>189798.69715</v>
       </c>
       <c r="D184">
-        <v>21257.45408080001</v>
+        <v>26571.81760100001</v>
       </c>
       <c r="E184">
-        <v>130581.5036392</v>
+        <v>163226.879549</v>
       </c>
       <c r="F184">
-        <v>62679.12174681602</v>
+        <v>78348.90218352001</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -4449,16 +4448,16 @@
         <v>2026</v>
       </c>
       <c r="C185">
-        <v>176314.6683192</v>
+        <v>217800.4726296</v>
       </c>
       <c r="D185">
-        <v>24684.05356468801</v>
+        <v>30492.06616814401</v>
       </c>
       <c r="E185">
-        <v>151630.614754512</v>
+        <v>187308.406461456</v>
       </c>
       <c r="F185">
-        <v>72782.69508216577</v>
+        <v>89908.0351014989</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -4469,16 +4468,16 @@
         <v>2027</v>
       </c>
       <c r="C186">
-        <v>136256.504384</v>
+        <v>166390.154392</v>
       </c>
       <c r="D186">
-        <v>19075.91061376</v>
+        <v>23294.62161488</v>
       </c>
       <c r="E186">
-        <v>117180.59377024</v>
+        <v>143095.53277712</v>
       </c>
       <c r="F186">
-        <v>56246.6850097152</v>
+        <v>68685.8557330176</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -4489,16 +4488,16 @@
         <v>2028</v>
       </c>
       <c r="C187">
-        <v>142657.54469616</v>
+        <v>172265.71435008</v>
       </c>
       <c r="D187">
-        <v>19972.05625746241</v>
+        <v>24117.20000901121</v>
       </c>
       <c r="E187">
-        <v>122685.4884386976</v>
+        <v>148148.5143410688</v>
       </c>
       <c r="F187">
-        <v>58889.03445057487</v>
+        <v>71111.28688371304</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -4509,16 +4508,16 @@
         <v>2029</v>
       </c>
       <c r="C188">
-        <v>189444.45228768</v>
+        <v>226280.87356584</v>
       </c>
       <c r="D188">
-        <v>26522.2233202752</v>
+        <v>31679.32229921761</v>
       </c>
       <c r="E188">
-        <v>162922.2289674048</v>
+        <v>194601.5512666224</v>
       </c>
       <c r="F188">
-        <v>78202.6699043543</v>
+        <v>93408.74460797876</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -4529,16 +4528,16 @@
         <v>2030</v>
       </c>
       <c r="C189">
-        <v>176799.5178664</v>
+        <v>208944.8847512</v>
       </c>
       <c r="D189">
-        <v>24751.93250129601</v>
+        <v>29252.28386516801</v>
       </c>
       <c r="E189">
-        <v>152047.585365104</v>
+        <v>179692.600886032</v>
       </c>
       <c r="F189">
-        <v>72982.84097524994</v>
+        <v>86252.44842529537</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -4549,16 +4548,16 @@
         <v>2031</v>
       </c>
       <c r="C190">
-        <v>213849.4524544</v>
+        <v>250127.4845672</v>
       </c>
       <c r="D190">
-        <v>29938.92334361601</v>
+        <v>35017.84783940801</v>
       </c>
       <c r="E190">
-        <v>183910.529110784</v>
+        <v>215109.636727792</v>
       </c>
       <c r="F190">
-        <v>88277.05397317633</v>
+        <v>103252.6256293402</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -4569,16 +4568,16 @@
         <v>2032</v>
       </c>
       <c r="C191">
-        <v>205139.05787088</v>
+        <v>237529.43542944</v>
       </c>
       <c r="D191">
-        <v>28719.4681019232</v>
+        <v>33254.1209601216</v>
       </c>
       <c r="E191">
-        <v>176419.5897689568</v>
+        <v>204275.3144693184</v>
       </c>
       <c r="F191">
-        <v>84681.40308909926</v>
+        <v>98052.15094527285</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -4589,16 +4588,16 @@
         <v>2033</v>
       </c>
       <c r="C192">
-        <v>230278.14014496</v>
+        <v>264025.7986144801</v>
       </c>
       <c r="D192">
-        <v>32238.93962029441</v>
+        <v>36963.61180602721</v>
       </c>
       <c r="E192">
-        <v>198039.2005246656</v>
+        <v>227062.1868084529</v>
       </c>
       <c r="F192">
-        <v>95058.8162518395</v>
+        <v>108989.8496680574</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -4609,16 +4608,16 @@
         <v>2034</v>
       </c>
       <c r="C193">
-        <v>205195.15450848</v>
+        <v>233018.22630624</v>
       </c>
       <c r="D193">
-        <v>28727.32163118721</v>
+        <v>32622.55168287361</v>
       </c>
       <c r="E193">
-        <v>176467.8328772928</v>
+        <v>200395.6746233664</v>
       </c>
       <c r="F193">
-        <v>84704.55978110056</v>
+        <v>96189.9238192159</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -4629,16 +4628,16 @@
         <v>2035</v>
       </c>
       <c r="C194">
-        <v>197219.5054656</v>
+        <v>221871.9436488</v>
       </c>
       <c r="D194">
-        <v>27610.730765184</v>
+        <v>31062.07211083201</v>
       </c>
       <c r="E194">
-        <v>169608.774700416</v>
+        <v>190809.871537968</v>
       </c>
       <c r="F194">
-        <v>81412.21185619968</v>
+        <v>91588.73833822465</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -4649,16 +4648,16 @@
         <v>2036</v>
       </c>
       <c r="C195">
-        <v>199130.49809744</v>
+        <v>221981.53886272</v>
       </c>
       <c r="D195">
-        <v>27878.26973364161</v>
+        <v>31077.41544078081</v>
       </c>
       <c r="E195">
-        <v>171252.2283637984</v>
+        <v>190904.1234219392</v>
       </c>
       <c r="F195">
-        <v>82201.06961462324</v>
+        <v>91633.97924253084</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -4669,16 +4668,16 @@
         <v>2037</v>
       </c>
       <c r="C196">
-        <v>240105.22645856</v>
+        <v>265277.54858728</v>
       </c>
       <c r="D196">
-        <v>33614.73170419841</v>
+        <v>37138.8568022192</v>
       </c>
       <c r="E196">
-        <v>206490.4947543616</v>
+        <v>228138.6917850608</v>
       </c>
       <c r="F196">
-        <v>99115.43748209358</v>
+        <v>109506.5720568292</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -4689,16 +4688,16 @@
         <v>2038</v>
       </c>
       <c r="C197">
-        <v>234551.54075472</v>
+        <v>256889.78273136</v>
       </c>
       <c r="D197">
-        <v>32837.2157056608</v>
+        <v>35964.56958239041</v>
       </c>
       <c r="E197">
-        <v>201714.3250490592</v>
+        <v>220925.2131489696</v>
       </c>
       <c r="F197">
-        <v>96822.87602354842</v>
+        <v>106044.1023115054</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -4709,16 +4708,16 @@
         <v>2039</v>
       </c>
       <c r="C198">
-        <v>207352.54081536</v>
+        <v>225171.89979168</v>
       </c>
       <c r="D198">
-        <v>29029.3557141504</v>
+        <v>31524.0659708352</v>
       </c>
       <c r="E198">
-        <v>178323.1851012096</v>
+        <v>193647.8338208448</v>
       </c>
       <c r="F198">
-        <v>85595.12884858061</v>
+        <v>92950.9602340055</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -4729,16 +4728,16 @@
         <v>2040</v>
       </c>
       <c r="C199">
-        <v>262301.5060848</v>
+        <v>282478.5450144</v>
       </c>
       <c r="D199">
-        <v>36722.21085187201</v>
+        <v>39546.996302016</v>
       </c>
       <c r="E199">
-        <v>225579.295232928</v>
+        <v>242931.548712384</v>
       </c>
       <c r="F199">
-        <v>108278.0617118054</v>
+        <v>116607.1433819443</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -4749,16 +4748,16 @@
         <v>2041</v>
       </c>
       <c r="C200">
-        <v>218171.55776064</v>
+        <v>233046.89124432</v>
       </c>
       <c r="D200">
-        <v>30544.01808648961</v>
+        <v>32626.5647742048</v>
       </c>
       <c r="E200">
-        <v>187627.5396741504</v>
+        <v>200420.3264701152</v>
       </c>
       <c r="F200">
-        <v>90061.21904359219</v>
+        <v>96201.75670565528</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -4769,16 +4768,16 @@
         <v>2042</v>
       </c>
       <c r="C201">
-        <v>243144.42576</v>
+        <v>257660.51088</v>
       </c>
       <c r="D201">
-        <v>34040.21960640001</v>
+        <v>36072.4715232</v>
       </c>
       <c r="E201">
-        <v>209104.2061536</v>
+        <v>221588.0393568</v>
       </c>
       <c r="F201">
-        <v>100370.018953728</v>
+        <v>106362.258891264</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -4789,16 +4788,16 @@
         <v>2043</v>
       </c>
       <c r="C202">
-        <v>238932.33171264</v>
+        <v>251230.31937432</v>
       </c>
       <c r="D202">
-        <v>33450.52643976961</v>
+        <v>35172.2447124048</v>
       </c>
       <c r="E202">
-        <v>205481.8052728704</v>
+        <v>216058.0746619152</v>
       </c>
       <c r="F202">
-        <v>98631.26653097781</v>
+        <v>103707.8758377193</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -4809,16 +4808,16 @@
         <v>2044</v>
       </c>
       <c r="C203">
-        <v>216281.41042464</v>
+        <v>225684.95000832</v>
       </c>
       <c r="D203">
-        <v>30279.39745944961</v>
+        <v>31595.8930011648</v>
       </c>
       <c r="E203">
-        <v>186002.0129651904</v>
+        <v>194089.0570071552</v>
       </c>
       <c r="F203">
-        <v>89280.9662232914</v>
+        <v>93162.74736343451</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -4829,16 +4828,16 @@
         <v>2045</v>
       </c>
       <c r="C204">
-        <v>225891.2331536</v>
+        <v>233958.7771948</v>
       </c>
       <c r="D204">
-        <v>31624.77264150401</v>
+        <v>32754.228807272</v>
       </c>
       <c r="E204">
-        <v>194266.460512096</v>
+        <v>201204.548387528</v>
       </c>
       <c r="F204">
-        <v>93247.90104580609</v>
+        <v>96578.18322601344</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -4849,16 +4848,16 @@
         <v>2046</v>
       </c>
       <c r="C205">
-        <v>251426.1040856</v>
+        <v>258508.5295528</v>
       </c>
       <c r="D205">
-        <v>35199.654571984</v>
+        <v>36191.194137392</v>
       </c>
       <c r="E205">
-        <v>216226.449513616</v>
+        <v>222317.335415408</v>
       </c>
       <c r="F205">
-        <v>103788.6957665357</v>
+        <v>106712.3209993958</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -4869,16 +4868,16 @@
         <v>2047</v>
       </c>
       <c r="C206">
-        <v>259672.25233152</v>
+        <v>265082.09092176</v>
       </c>
       <c r="D206">
-        <v>36354.1153264128</v>
+        <v>37111.4927290464</v>
       </c>
       <c r="E206">
-        <v>223318.1370051072</v>
+        <v>227970.5981927136</v>
       </c>
       <c r="F206">
-        <v>107192.7057624515</v>
+        <v>109425.8871325025</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -4889,16 +4888,16 @@
         <v>2048</v>
       </c>
       <c r="C207">
-        <v>215438.68175488</v>
+        <v>218389.89657344</v>
       </c>
       <c r="D207">
-        <v>30161.41544568321</v>
+        <v>30574.58552028161</v>
       </c>
       <c r="E207">
-        <v>185277.2663091968</v>
+        <v>187815.3110531584</v>
       </c>
       <c r="F207">
-        <v>88933.08782841447</v>
+        <v>90151.34930551604</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -4909,16 +4908,16 @@
         <v>2049</v>
       </c>
       <c r="C208">
-        <v>257803.6476832</v>
+        <v>259545.5642216</v>
       </c>
       <c r="D208">
-        <v>36092.510675648</v>
+        <v>36336.378991024</v>
       </c>
       <c r="E208">
-        <v>221711.137007552</v>
+        <v>223209.185230576</v>
       </c>
       <c r="F208">
-        <v>106421.345763625</v>
+        <v>107140.4089106765</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -4949,16 +4948,16 @@
         <v>2025</v>
       </c>
       <c r="C210">
-        <v>151838.95772</v>
+        <v>189798.69715</v>
       </c>
       <c r="D210">
-        <v>21257.45408080001</v>
+        <v>26571.81760100001</v>
       </c>
       <c r="E210">
-        <v>130581.5036392</v>
+        <v>163226.879549</v>
       </c>
       <c r="F210">
-        <v>62679.12174681602</v>
+        <v>78348.90218352001</v>
       </c>
     </row>
     <row r="211" spans="1:6">
@@ -4969,16 +4968,16 @@
         <v>2026</v>
       </c>
       <c r="C211">
-        <v>176314.6683192</v>
+        <v>217800.4726296</v>
       </c>
       <c r="D211">
-        <v>24684.05356468801</v>
+        <v>30492.06616814401</v>
       </c>
       <c r="E211">
-        <v>151630.614754512</v>
+        <v>187308.406461456</v>
       </c>
       <c r="F211">
-        <v>72782.69508216577</v>
+        <v>89908.0351014989</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -4989,16 +4988,16 @@
         <v>2027</v>
       </c>
       <c r="C212">
-        <v>136256.504384</v>
+        <v>166390.154392</v>
       </c>
       <c r="D212">
-        <v>19075.91061376</v>
+        <v>23294.62161488</v>
       </c>
       <c r="E212">
-        <v>117180.59377024</v>
+        <v>143095.53277712</v>
       </c>
       <c r="F212">
-        <v>56246.6850097152</v>
+        <v>68685.8557330176</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -5009,16 +5008,16 @@
         <v>2028</v>
       </c>
       <c r="C213">
-        <v>142657.54469616</v>
+        <v>172265.71435008</v>
       </c>
       <c r="D213">
-        <v>19972.05625746241</v>
+        <v>24117.20000901121</v>
       </c>
       <c r="E213">
-        <v>122685.4884386976</v>
+        <v>148148.5143410688</v>
       </c>
       <c r="F213">
-        <v>58889.03445057487</v>
+        <v>71111.28688371304</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -5029,16 +5028,16 @@
         <v>2029</v>
       </c>
       <c r="C214">
-        <v>189444.45228768</v>
+        <v>226280.87356584</v>
       </c>
       <c r="D214">
-        <v>26522.2233202752</v>
+        <v>31679.32229921761</v>
       </c>
       <c r="E214">
-        <v>162922.2289674048</v>
+        <v>194601.5512666224</v>
       </c>
       <c r="F214">
-        <v>78202.6699043543</v>
+        <v>93408.74460797876</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -5049,16 +5048,16 @@
         <v>2030</v>
       </c>
       <c r="C215">
-        <v>176799.5178664</v>
+        <v>208944.8847512</v>
       </c>
       <c r="D215">
-        <v>24751.93250129601</v>
+        <v>29252.28386516801</v>
       </c>
       <c r="E215">
-        <v>152047.585365104</v>
+        <v>179692.600886032</v>
       </c>
       <c r="F215">
-        <v>72982.84097524994</v>
+        <v>86252.44842529537</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -5069,16 +5068,16 @@
         <v>2031</v>
       </c>
       <c r="C216">
-        <v>213849.4524544</v>
+        <v>250127.4845672</v>
       </c>
       <c r="D216">
-        <v>29938.92334361601</v>
+        <v>35017.84783940801</v>
       </c>
       <c r="E216">
-        <v>183910.529110784</v>
+        <v>215109.636727792</v>
       </c>
       <c r="F216">
-        <v>88277.05397317633</v>
+        <v>103252.6256293402</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -5089,16 +5088,16 @@
         <v>2032</v>
       </c>
       <c r="C217">
-        <v>205139.05787088</v>
+        <v>237529.43542944</v>
       </c>
       <c r="D217">
-        <v>28719.4681019232</v>
+        <v>33254.1209601216</v>
       </c>
       <c r="E217">
-        <v>176419.5897689568</v>
+        <v>204275.3144693184</v>
       </c>
       <c r="F217">
-        <v>84681.40308909926</v>
+        <v>98052.15094527285</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -5109,16 +5108,16 @@
         <v>2033</v>
       </c>
       <c r="C218">
-        <v>230278.14014496</v>
+        <v>264025.7986144801</v>
       </c>
       <c r="D218">
-        <v>32238.93962029441</v>
+        <v>36963.61180602721</v>
       </c>
       <c r="E218">
-        <v>198039.2005246656</v>
+        <v>227062.1868084529</v>
       </c>
       <c r="F218">
-        <v>95058.8162518395</v>
+        <v>108989.8496680574</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -5129,16 +5128,16 @@
         <v>2034</v>
       </c>
       <c r="C219">
-        <v>205195.15450848</v>
+        <v>233018.22630624</v>
       </c>
       <c r="D219">
-        <v>28727.32163118721</v>
+        <v>32622.55168287361</v>
       </c>
       <c r="E219">
-        <v>176467.8328772928</v>
+        <v>200395.6746233664</v>
       </c>
       <c r="F219">
-        <v>84704.55978110056</v>
+        <v>96189.9238192159</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -5149,16 +5148,16 @@
         <v>2035</v>
       </c>
       <c r="C220">
-        <v>197219.5054656</v>
+        <v>221871.9436488</v>
       </c>
       <c r="D220">
-        <v>27610.730765184</v>
+        <v>31062.07211083201</v>
       </c>
       <c r="E220">
-        <v>169608.774700416</v>
+        <v>190809.871537968</v>
       </c>
       <c r="F220">
-        <v>81412.21185619968</v>
+        <v>91588.73833822465</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -5169,16 +5168,16 @@
         <v>2036</v>
       </c>
       <c r="C221">
-        <v>199130.49809744</v>
+        <v>221981.53886272</v>
       </c>
       <c r="D221">
-        <v>27878.26973364161</v>
+        <v>31077.41544078081</v>
       </c>
       <c r="E221">
-        <v>171252.2283637984</v>
+        <v>190904.1234219392</v>
       </c>
       <c r="F221">
-        <v>82201.06961462324</v>
+        <v>91633.97924253084</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -5189,16 +5188,16 @@
         <v>2037</v>
       </c>
       <c r="C222">
-        <v>240105.22645856</v>
+        <v>265277.54858728</v>
       </c>
       <c r="D222">
-        <v>33614.73170419841</v>
+        <v>37138.8568022192</v>
       </c>
       <c r="E222">
-        <v>206490.4947543616</v>
+        <v>228138.6917850608</v>
       </c>
       <c r="F222">
-        <v>99115.43748209358</v>
+        <v>109506.5720568292</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -5209,16 +5208,16 @@
         <v>2038</v>
       </c>
       <c r="C223">
-        <v>234551.54075472</v>
+        <v>256889.78273136</v>
       </c>
       <c r="D223">
-        <v>32837.2157056608</v>
+        <v>35964.56958239041</v>
       </c>
       <c r="E223">
-        <v>201714.3250490592</v>
+        <v>220925.2131489696</v>
       </c>
       <c r="F223">
-        <v>96822.87602354842</v>
+        <v>106044.1023115054</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -5229,16 +5228,16 @@
         <v>2039</v>
       </c>
       <c r="C224">
-        <v>207352.54081536</v>
+        <v>225171.89979168</v>
       </c>
       <c r="D224">
-        <v>29029.3557141504</v>
+        <v>31524.0659708352</v>
       </c>
       <c r="E224">
-        <v>178323.1851012096</v>
+        <v>193647.8338208448</v>
       </c>
       <c r="F224">
-        <v>85595.12884858061</v>
+        <v>92950.9602340055</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -5249,16 +5248,16 @@
         <v>2040</v>
       </c>
       <c r="C225">
-        <v>262301.5060848</v>
+        <v>282478.5450144</v>
       </c>
       <c r="D225">
-        <v>36722.21085187201</v>
+        <v>39546.996302016</v>
       </c>
       <c r="E225">
-        <v>225579.295232928</v>
+        <v>242931.548712384</v>
       </c>
       <c r="F225">
-        <v>108278.0617118054</v>
+        <v>116607.1433819443</v>
       </c>
     </row>
     <row r="226" spans="1:6">
@@ -5269,16 +5268,16 @@
         <v>2041</v>
       </c>
       <c r="C226">
-        <v>218171.55776064</v>
+        <v>233046.89124432</v>
       </c>
       <c r="D226">
-        <v>30544.01808648961</v>
+        <v>32626.5647742048</v>
       </c>
       <c r="E226">
-        <v>187627.5396741504</v>
+        <v>200420.3264701152</v>
       </c>
       <c r="F226">
-        <v>90061.21904359219</v>
+        <v>96201.75670565528</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -5289,16 +5288,16 @@
         <v>2042</v>
       </c>
       <c r="C227">
-        <v>243144.42576</v>
+        <v>257660.51088</v>
       </c>
       <c r="D227">
-        <v>34040.21960640001</v>
+        <v>36072.4715232</v>
       </c>
       <c r="E227">
-        <v>209104.2061536</v>
+        <v>221588.0393568</v>
       </c>
       <c r="F227">
-        <v>100370.018953728</v>
+        <v>106362.258891264</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -5309,16 +5308,16 @@
         <v>2043</v>
       </c>
       <c r="C228">
-        <v>238932.33171264</v>
+        <v>251230.31937432</v>
       </c>
       <c r="D228">
-        <v>33450.52643976961</v>
+        <v>35172.2447124048</v>
       </c>
       <c r="E228">
-        <v>205481.8052728704</v>
+        <v>216058.0746619152</v>
       </c>
       <c r="F228">
-        <v>98631.26653097781</v>
+        <v>103707.8758377193</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -5329,16 +5328,16 @@
         <v>2044</v>
       </c>
       <c r="C229">
-        <v>216281.41042464</v>
+        <v>225684.95000832</v>
       </c>
       <c r="D229">
-        <v>30279.39745944961</v>
+        <v>31595.8930011648</v>
       </c>
       <c r="E229">
-        <v>186002.0129651904</v>
+        <v>194089.0570071552</v>
       </c>
       <c r="F229">
-        <v>89280.9662232914</v>
+        <v>93162.74736343451</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -5349,16 +5348,16 @@
         <v>2045</v>
       </c>
       <c r="C230">
-        <v>225891.2331536</v>
+        <v>233958.7771948</v>
       </c>
       <c r="D230">
-        <v>31624.77264150401</v>
+        <v>32754.228807272</v>
       </c>
       <c r="E230">
-        <v>194266.460512096</v>
+        <v>201204.548387528</v>
       </c>
       <c r="F230">
-        <v>93247.90104580609</v>
+        <v>96578.18322601344</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -5369,16 +5368,16 @@
         <v>2046</v>
       </c>
       <c r="C231">
-        <v>251426.1040856</v>
+        <v>258508.5295528</v>
       </c>
       <c r="D231">
-        <v>35199.654571984</v>
+        <v>36191.194137392</v>
       </c>
       <c r="E231">
-        <v>216226.449513616</v>
+        <v>222317.335415408</v>
       </c>
       <c r="F231">
-        <v>103788.6957665357</v>
+        <v>106712.3209993958</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -5389,16 +5388,16 @@
         <v>2047</v>
       </c>
       <c r="C232">
-        <v>259672.25233152</v>
+        <v>265082.09092176</v>
       </c>
       <c r="D232">
-        <v>36354.1153264128</v>
+        <v>37111.4927290464</v>
       </c>
       <c r="E232">
-        <v>223318.1370051072</v>
+        <v>227970.5981927136</v>
       </c>
       <c r="F232">
-        <v>107192.7057624515</v>
+        <v>109425.8871325025</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -5409,16 +5408,16 @@
         <v>2048</v>
       </c>
       <c r="C233">
-        <v>215438.68175488</v>
+        <v>218389.89657344</v>
       </c>
       <c r="D233">
-        <v>30161.41544568321</v>
+        <v>30574.58552028161</v>
       </c>
       <c r="E233">
-        <v>185277.2663091968</v>
+        <v>187815.3110531584</v>
       </c>
       <c r="F233">
-        <v>88933.08782841447</v>
+        <v>90151.34930551604</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -5429,16 +5428,16 @@
         <v>2049</v>
       </c>
       <c r="C234">
-        <v>257803.6476832</v>
+        <v>259545.5642216</v>
       </c>
       <c r="D234">
-        <v>36092.510675648</v>
+        <v>36336.378991024</v>
       </c>
       <c r="E234">
-        <v>221711.137007552</v>
+        <v>223209.185230576</v>
       </c>
       <c r="F234">
-        <v>106421.345763625</v>
+        <v>107140.4089106765</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -7049,16 +7048,16 @@
         <v>2026</v>
       </c>
       <c r="C315">
-        <v>17727.88478743258</v>
+        <v>22159.85598429072</v>
       </c>
       <c r="D315">
         <v>0</v>
       </c>
       <c r="E315">
-        <v>17727.88478743258</v>
+        <v>22159.85598429072</v>
       </c>
       <c r="F315">
-        <v>17727.88478743258</v>
+        <v>22159.85598429072</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -7069,16 +7068,16 @@
         <v>2027</v>
       </c>
       <c r="C316">
-        <v>31509.25194635794</v>
+        <v>39083.83648212185</v>
       </c>
       <c r="D316">
         <v>0</v>
       </c>
       <c r="E316">
-        <v>31509.25194635794</v>
+        <v>39083.83648212185</v>
       </c>
       <c r="F316">
-        <v>31509.25194635794</v>
+        <v>39083.83648212185</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -7089,16 +7088,16 @@
         <v>2028</v>
       </c>
       <c r="C317">
-        <v>35385.68481359664</v>
+        <v>43586.66739844438</v>
       </c>
       <c r="D317">
         <v>0</v>
       </c>
       <c r="E317">
-        <v>35385.68481359664</v>
+        <v>43586.66739844438</v>
       </c>
       <c r="F317">
-        <v>35385.68481359664</v>
+        <v>43586.66739844438</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -7109,16 +7108,16 @@
         <v>2029</v>
       </c>
       <c r="C318">
-        <v>38628.82015764923</v>
+        <v>47180.17278046679</v>
       </c>
       <c r="D318">
         <v>0</v>
       </c>
       <c r="E318">
-        <v>38628.82015764923</v>
+        <v>47180.17278046679</v>
       </c>
       <c r="F318">
-        <v>38628.82015764923</v>
+        <v>47180.17278046679</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -7129,16 +7128,16 @@
         <v>2030</v>
       </c>
       <c r="C319">
-        <v>46206.72103610866</v>
+        <v>55844.93002132534</v>
       </c>
       <c r="D319">
         <v>0</v>
       </c>
       <c r="E319">
-        <v>46206.72103610866</v>
+        <v>55844.93002132534</v>
       </c>
       <c r="F319">
-        <v>46206.72103610866</v>
+        <v>55844.93002132534</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -7149,16 +7148,16 @@
         <v>2031</v>
       </c>
       <c r="C320">
-        <v>49523.94969728329</v>
+        <v>59311.48324581505</v>
       </c>
       <c r="D320">
         <v>0</v>
       </c>
       <c r="E320">
-        <v>49523.94969728329</v>
+        <v>59311.48324581505</v>
       </c>
       <c r="F320">
-        <v>49523.94969728329</v>
+        <v>59311.48324581505</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -7169,16 +7168,16 @@
         <v>2032</v>
       </c>
       <c r="C321">
-        <v>56039.91973889914</v>
+        <v>66432.12200916512</v>
       </c>
       <c r="D321">
         <v>0</v>
       </c>
       <c r="E321">
-        <v>56039.91973889914</v>
+        <v>66432.12200916512</v>
       </c>
       <c r="F321">
-        <v>56039.91973889914</v>
+        <v>66432.12200916512</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -7189,16 +7188,16 @@
         <v>2033</v>
       </c>
       <c r="C322">
-        <v>59190.67589713208</v>
+        <v>69531.19843097447</v>
       </c>
       <c r="D322">
         <v>0</v>
       </c>
       <c r="E322">
-        <v>59190.67589713208</v>
+        <v>69531.19843097447</v>
       </c>
       <c r="F322">
-        <v>59190.67589713208</v>
+        <v>69531.19843097447</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -7209,16 +7208,16 @@
         <v>2034</v>
       </c>
       <c r="C323">
-        <v>64237.26124379353</v>
+        <v>74735.11904564973</v>
       </c>
       <c r="D323">
         <v>0</v>
       </c>
       <c r="E323">
-        <v>64237.26124379353</v>
+        <v>74735.11904564973</v>
       </c>
       <c r="F323">
-        <v>64237.26124379353</v>
+        <v>74735.11904564973</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -7229,16 +7228,16 @@
         <v>2035</v>
       </c>
       <c r="C324">
-        <v>64593.4689178168</v>
+        <v>74526.02955124973</v>
       </c>
       <c r="D324">
         <v>0</v>
       </c>
       <c r="E324">
-        <v>64593.4689178168</v>
+        <v>74526.02955124973</v>
       </c>
       <c r="F324">
-        <v>64593.4689178168</v>
+        <v>74526.02955124973</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -7249,16 +7248,16 @@
         <v>2036</v>
       </c>
       <c r="C325">
-        <v>64068.36747125551</v>
+        <v>73311.42288617458</v>
       </c>
       <c r="D325">
         <v>0</v>
       </c>
       <c r="E325">
-        <v>64068.36747125551</v>
+        <v>73311.42288617458</v>
       </c>
       <c r="F325">
-        <v>64068.36747125551</v>
+        <v>73311.42288617458</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -7269,16 +7268,16 @@
         <v>2037</v>
       </c>
       <c r="C326">
-        <v>64149.34977472714</v>
+        <v>72783.27186393969</v>
       </c>
       <c r="D326">
         <v>0</v>
       </c>
       <c r="E326">
-        <v>64149.34977472714</v>
+        <v>72783.27186393969</v>
       </c>
       <c r="F326">
-        <v>64149.34977472714</v>
+        <v>72783.27186393969</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -7289,16 +7288,16 @@
         <v>2038</v>
       </c>
       <c r="C327">
-        <v>69156.60879107294</v>
+        <v>77708.97688594114</v>
       </c>
       <c r="D327">
         <v>0</v>
       </c>
       <c r="E327">
-        <v>69156.60879107294</v>
+        <v>77708.97688594114</v>
       </c>
       <c r="F327">
-        <v>69156.60879107294</v>
+        <v>77708.97688594114</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -7309,16 +7308,16 @@
         <v>2039</v>
       </c>
       <c r="C328">
-        <v>71761.30561652203</v>
+        <v>79952.4015727769</v>
       </c>
       <c r="D328">
         <v>0</v>
       </c>
       <c r="E328">
-        <v>71761.30561652203</v>
+        <v>79952.4015727769</v>
       </c>
       <c r="F328">
-        <v>71761.30561652203</v>
+        <v>79952.4015727769</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -7329,16 +7328,16 @@
         <v>2040</v>
       </c>
       <c r="C329">
-        <v>70369.98974421239</v>
+        <v>77829.78071097843</v>
       </c>
       <c r="D329">
         <v>0</v>
       </c>
       <c r="E329">
-        <v>70369.98974421239</v>
+        <v>77829.78071097843</v>
       </c>
       <c r="F329">
-        <v>70369.98974421239</v>
+        <v>77829.78071097843</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -7349,16 +7348,16 @@
         <v>2041</v>
       </c>
       <c r="C330">
-        <v>76110.3985685051</v>
+        <v>83411.84199374364</v>
       </c>
       <c r="D330">
         <v>0</v>
       </c>
       <c r="E330">
-        <v>76110.3985685051</v>
+        <v>83411.84199374364</v>
       </c>
       <c r="F330">
-        <v>76110.3985685051</v>
+        <v>83411.84199374364</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -7369,16 +7368,16 @@
         <v>2042</v>
       </c>
       <c r="C331">
-        <v>74666.29939770969</v>
+        <v>81265.05669760695</v>
       </c>
       <c r="D331">
         <v>0</v>
       </c>
       <c r="E331">
-        <v>74666.29939770969</v>
+        <v>81265.05669760695</v>
       </c>
       <c r="F331">
-        <v>74666.29939770969</v>
+        <v>81265.05669760695</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -7389,16 +7388,16 @@
         <v>2043</v>
       </c>
       <c r="C332">
-        <v>76877.28848125538</v>
+        <v>83013.97265483775</v>
       </c>
       <c r="D332">
         <v>0</v>
       </c>
       <c r="E332">
-        <v>76877.28848125538</v>
+        <v>83013.97265483775</v>
       </c>
       <c r="F332">
-        <v>76877.28848125538</v>
+        <v>83013.97265483775</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -7409,16 +7408,16 @@
         <v>2044</v>
       </c>
       <c r="C333">
-        <v>77921.6569157629</v>
+        <v>83524.62310052573</v>
       </c>
       <c r="D333">
         <v>0</v>
       </c>
       <c r="E333">
-        <v>77921.6569157629</v>
+        <v>83524.62310052573</v>
       </c>
       <c r="F333">
-        <v>77921.6569157629</v>
+        <v>83524.62310052573</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -7429,16 +7428,16 @@
         <v>2045</v>
       </c>
       <c r="C334">
-        <v>76096.05076170994</v>
+        <v>81040.23986011924</v>
       </c>
       <c r="D334">
         <v>0</v>
       </c>
       <c r="E334">
-        <v>76096.05076170994</v>
+        <v>81040.23986011924</v>
       </c>
       <c r="F334">
-        <v>76096.05076170994</v>
+        <v>81040.23986011924</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -7449,16 +7448,16 @@
         <v>2046</v>
       </c>
       <c r="C335">
-        <v>76266.18261778564</v>
+        <v>80654.36400413627</v>
       </c>
       <c r="D335">
         <v>0</v>
       </c>
       <c r="E335">
-        <v>76266.18261778564</v>
+        <v>80654.36400413627</v>
       </c>
       <c r="F335">
-        <v>76266.18261778564</v>
+        <v>80654.36400413627</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -7469,16 +7468,16 @@
         <v>2047</v>
       </c>
       <c r="C336">
-        <v>79513.11052894854</v>
+        <v>83447.08825189635</v>
       </c>
       <c r="D336">
         <v>0</v>
       </c>
       <c r="E336">
-        <v>79513.11052894854</v>
+        <v>83447.08825189635</v>
       </c>
       <c r="F336">
-        <v>79513.11052894854</v>
+        <v>83447.08825189635</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -7489,16 +7488,16 @@
         <v>2048</v>
       </c>
       <c r="C337">
-        <v>82632.45551803747</v>
+        <v>86092.64918270693</v>
       </c>
       <c r="D337">
         <v>0</v>
       </c>
       <c r="E337">
-        <v>82632.45551803747</v>
+        <v>86092.64918270693</v>
       </c>
       <c r="F337">
-        <v>82632.45551803747</v>
+        <v>86092.64918270693</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -7509,16 +7508,16 @@
         <v>2049</v>
       </c>
       <c r="C338">
-        <v>79551.84916998766</v>
+        <v>82432.79772250078</v>
       </c>
       <c r="D338">
         <v>0</v>
       </c>
       <c r="E338">
-        <v>79551.84916998766</v>
+        <v>82432.79772250078</v>
       </c>
       <c r="F338">
-        <v>79551.84916998766</v>
+        <v>82432.79772250078</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -7529,16 +7528,16 @@
         <v>2050</v>
       </c>
       <c r="C339">
-        <v>82766.93805428379</v>
+        <v>85147.88735175491</v>
       </c>
       <c r="D339">
         <v>0</v>
       </c>
       <c r="E339">
-        <v>82766.93805428379</v>
+        <v>85147.88735175491</v>
       </c>
       <c r="F339">
-        <v>82766.93805428379</v>
+        <v>85147.88735175491</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -7549,10 +7548,10 @@
         <v>2025</v>
       </c>
       <c r="C340">
-        <v>21257.45408080001</v>
+        <v>26571.81760100001</v>
       </c>
       <c r="D340">
-        <v>21257.45408080001</v>
+        <v>26571.81760100001</v>
       </c>
       <c r="E340">
         <v>0</v>
@@ -7569,13 +7568,13 @@
         <v>2026</v>
       </c>
       <c r="C341">
-        <v>43889.26208440664</v>
+        <v>54498.57681779229</v>
       </c>
       <c r="D341">
-        <v>24684.05356468801</v>
+        <v>30492.06616814401</v>
       </c>
       <c r="E341">
-        <v>19205.20851971863</v>
+        <v>24006.51064964828</v>
       </c>
       <c r="F341">
         <v>0</v>
@@ -7589,13 +7588,13 @@
         <v>2027</v>
       </c>
       <c r="C342">
-        <v>53210.93355564778</v>
+        <v>65635.44447051201</v>
       </c>
       <c r="D342">
-        <v>19075.91061376</v>
+        <v>23294.62161488</v>
       </c>
       <c r="E342">
-        <v>34135.02294188778</v>
+        <v>42340.822855632</v>
       </c>
       <c r="F342">
         <v>0</v>
@@ -7609,13 +7608,13 @@
         <v>2028</v>
       </c>
       <c r="C343">
-        <v>58306.54813885877</v>
+        <v>71336.0896906593</v>
       </c>
       <c r="D343">
-        <v>19972.05625746241</v>
+        <v>24117.20000901121</v>
       </c>
       <c r="E343">
-        <v>38334.49188139635</v>
+        <v>47218.88968164809</v>
       </c>
       <c r="F343">
         <v>0</v>
@@ -7629,13 +7628,13 @@
         <v>2029</v>
       </c>
       <c r="C344">
-        <v>68370.11182439519</v>
+        <v>82791.1761447233</v>
       </c>
       <c r="D344">
-        <v>26522.2233202752</v>
+        <v>31679.32229921761</v>
       </c>
       <c r="E344">
-        <v>41847.88850412</v>
+        <v>51111.8538455057</v>
       </c>
       <c r="F344">
         <v>0</v>
@@ -7649,13 +7648,13 @@
         <v>2030</v>
       </c>
       <c r="C345">
-        <v>74809.21362374705</v>
+        <v>89750.95805493713</v>
       </c>
       <c r="D345">
-        <v>24751.93250129601</v>
+        <v>29252.28386516801</v>
       </c>
       <c r="E345">
-        <v>50057.28112245105</v>
+        <v>60498.67418976912</v>
       </c>
       <c r="F345">
         <v>0</v>
@@ -7669,13 +7668,13 @@
         <v>2031</v>
       </c>
       <c r="C346">
-        <v>83589.86884900625</v>
+        <v>99271.95468904098</v>
       </c>
       <c r="D346">
-        <v>29938.92334361601</v>
+        <v>35017.84783940801</v>
       </c>
       <c r="E346">
-        <v>53650.94550539023</v>
+        <v>64254.10684963297</v>
       </c>
       <c r="F346">
         <v>0</v>
@@ -7689,13 +7688,13 @@
         <v>2032</v>
       </c>
       <c r="C347">
-        <v>89429.38115239727</v>
+        <v>105222.2531367171</v>
       </c>
       <c r="D347">
-        <v>28719.4681019232</v>
+        <v>33254.1209601216</v>
       </c>
       <c r="E347">
-        <v>60709.91305047407</v>
+        <v>71968.13217659554</v>
       </c>
       <c r="F347">
         <v>0</v>
@@ -7709,13 +7708,13 @@
         <v>2033</v>
       </c>
       <c r="C348">
-        <v>96362.1718421875</v>
+        <v>112289.0767729162</v>
       </c>
       <c r="D348">
-        <v>32238.93962029441</v>
+        <v>36963.61180602721</v>
       </c>
       <c r="E348">
-        <v>64123.23222189309</v>
+        <v>75325.46496688901</v>
       </c>
       <c r="F348">
         <v>0</v>
@@ -7729,13 +7728,13 @@
         <v>2034</v>
       </c>
       <c r="C349">
-        <v>98317.6879786302</v>
+        <v>113585.5973156608</v>
       </c>
       <c r="D349">
-        <v>28727.32163118721</v>
+        <v>32622.55168287361</v>
       </c>
       <c r="E349">
-        <v>69590.36634744299</v>
+        <v>80963.04563278721</v>
       </c>
       <c r="F349">
         <v>0</v>
@@ -7749,13 +7748,13 @@
         <v>2035</v>
       </c>
       <c r="C350">
-        <v>97586.98875948554</v>
+        <v>111798.6041246859</v>
       </c>
       <c r="D350">
-        <v>27610.730765184</v>
+        <v>31062.07211083201</v>
       </c>
       <c r="E350">
-        <v>69976.25799430154</v>
+        <v>80736.53201385387</v>
       </c>
       <c r="F350">
         <v>0</v>
@@ -7769,13 +7768,13 @@
         <v>2036</v>
       </c>
       <c r="C351">
-        <v>97285.66782750173</v>
+        <v>110498.1235674699</v>
       </c>
       <c r="D351">
-        <v>27878.26973364161</v>
+        <v>31077.41544078081</v>
       </c>
       <c r="E351">
-        <v>69407.39809386013</v>
+        <v>79420.70812668913</v>
       </c>
       <c r="F351">
         <v>0</v>
@@ -7789,13 +7788,13 @@
         <v>2037</v>
       </c>
       <c r="C352">
-        <v>103109.8606268195</v>
+        <v>115987.4013214872</v>
       </c>
       <c r="D352">
-        <v>33614.73170419841</v>
+        <v>37138.8568022192</v>
       </c>
       <c r="E352">
-        <v>69495.12892262108</v>
+        <v>78848.54451926802</v>
       </c>
       <c r="F352">
         <v>0</v>
@@ -7809,13 +7808,13 @@
         <v>2038</v>
       </c>
       <c r="C353">
-        <v>107756.8752293232</v>
+        <v>120149.29454216</v>
       </c>
       <c r="D353">
-        <v>32837.2157056608</v>
+        <v>35964.56958239041</v>
       </c>
       <c r="E353">
-        <v>74919.65952366235</v>
+        <v>84184.72495976958</v>
       </c>
       <c r="F353">
         <v>0</v>
@@ -7829,13 +7828,13 @@
         <v>2039</v>
       </c>
       <c r="C354">
-        <v>106770.7701320493</v>
+        <v>118139.1676746768</v>
       </c>
       <c r="D354">
-        <v>29029.3557141504</v>
+        <v>31524.0659708352</v>
       </c>
       <c r="E354">
-        <v>77741.41441789886</v>
+        <v>86615.10170384165</v>
       </c>
       <c r="F354">
         <v>0</v>
@@ -7849,13 +7848,13 @@
         <v>2040</v>
       </c>
       <c r="C355">
-        <v>112956.3664081021</v>
+        <v>123862.5920722426</v>
       </c>
       <c r="D355">
-        <v>36722.21085187201</v>
+        <v>39546.996302016</v>
       </c>
       <c r="E355">
-        <v>76234.15555623011</v>
+        <v>84315.59577022665</v>
       </c>
       <c r="F355">
         <v>0</v>
@@ -7869,13 +7868,13 @@
         <v>2041</v>
       </c>
       <c r="C356">
-        <v>112996.9498690368</v>
+        <v>122989.3936007604</v>
       </c>
       <c r="D356">
-        <v>30544.01808648961</v>
+        <v>32626.5647742048</v>
       </c>
       <c r="E356">
-        <v>82452.93178254721</v>
+        <v>90362.8288265556</v>
       </c>
       <c r="F356">
         <v>0</v>
@@ -7889,13 +7888,13 @@
         <v>2042</v>
       </c>
       <c r="C357">
-        <v>114928.7106205855</v>
+        <v>124109.6162789409</v>
       </c>
       <c r="D357">
-        <v>34040.21960640001</v>
+        <v>36072.4715232</v>
       </c>
       <c r="E357">
-        <v>80888.49101418551</v>
+        <v>88037.14475574088</v>
       </c>
       <c r="F357">
         <v>0</v>
@@ -7909,13 +7908,13 @@
         <v>2043</v>
       </c>
       <c r="C358">
-        <v>116734.2556277963</v>
+        <v>125104.0484218124</v>
       </c>
       <c r="D358">
-        <v>33450.52643976961</v>
+        <v>35172.2447124048</v>
       </c>
       <c r="E358">
-        <v>83283.72918802666</v>
+        <v>89931.80370940758</v>
       </c>
       <c r="F358">
         <v>0</v>
@@ -7929,13 +7928,13 @@
         <v>2044</v>
       </c>
       <c r="C359">
-        <v>114694.5257848594</v>
+        <v>122080.9013600677</v>
       </c>
       <c r="D359">
-        <v>30279.39745944961</v>
+        <v>31595.8930011648</v>
       </c>
       <c r="E359">
-        <v>84415.12832540981</v>
+        <v>90485.00835890288</v>
       </c>
       <c r="F359">
         <v>0</v>
@@ -7949,13 +7948,13 @@
         <v>2045</v>
       </c>
       <c r="C360">
-        <v>114062.1609666898</v>
+        <v>120547.8219890679</v>
       </c>
       <c r="D360">
-        <v>31624.77264150401</v>
+        <v>32754.228807272</v>
       </c>
       <c r="E360">
-        <v>82437.38832518576</v>
+        <v>87793.59318179585</v>
       </c>
       <c r="F360">
         <v>0</v>
@@ -7969,13 +7968,13 @@
         <v>2046</v>
       </c>
       <c r="C361">
-        <v>117821.3524079185</v>
+        <v>123566.755141873</v>
       </c>
       <c r="D361">
-        <v>35199.654571984</v>
+        <v>36191.194137392</v>
       </c>
       <c r="E361">
-        <v>82621.69783593446</v>
+        <v>87375.56100448096</v>
       </c>
       <c r="F361">
         <v>0</v>
@@ -7989,13 +7988,13 @@
         <v>2047</v>
       </c>
       <c r="C362">
-        <v>122493.3183994404</v>
+        <v>127512.5050019341</v>
       </c>
       <c r="D362">
-        <v>36354.1153264128</v>
+        <v>37111.4927290464</v>
       </c>
       <c r="E362">
-        <v>86139.2030730276</v>
+        <v>90401.01227288772</v>
       </c>
       <c r="F362">
         <v>0</v>
@@ -8009,13 +8008,13 @@
         <v>2048</v>
       </c>
       <c r="C363">
-        <v>119679.9089235571</v>
+        <v>123841.6221348808</v>
       </c>
       <c r="D363">
-        <v>30161.41544568321</v>
+        <v>30574.58552028161</v>
       </c>
       <c r="E363">
-        <v>89518.49347787393</v>
+        <v>93267.03661459917</v>
       </c>
       <c r="F363">
         <v>0</v>
@@ -8029,13 +8028,13 @@
         <v>2049</v>
       </c>
       <c r="C364">
-        <v>122273.6806098013</v>
+        <v>125638.5765237332</v>
       </c>
       <c r="D364">
-        <v>36092.510675648</v>
+        <v>36336.378991024</v>
       </c>
       <c r="E364">
-        <v>86181.16993415329</v>
+        <v>89302.19753270919</v>
       </c>
       <c r="F364">
         <v>0</v>
@@ -8049,13 +8048,13 @@
         <v>2050</v>
       </c>
       <c r="C365">
-        <v>125618.8391048608</v>
+        <v>128198.2008437878</v>
       </c>
       <c r="D365">
         <v>35954.65621272</v>
       </c>
       <c r="E365">
-        <v>89664.18289214079</v>
+        <v>92243.54463106781</v>
       </c>
       <c r="F365">
         <v>0</v>
@@ -8089,16 +8088,16 @@
         <v>2026</v>
       </c>
       <c r="C367">
-        <v>89885.90933920002</v>
+        <v>86428.75898000001</v>
       </c>
       <c r="D367">
-        <v>12584.027307488</v>
+        <v>12100.0262572</v>
       </c>
       <c r="E367">
-        <v>77301.88203171201</v>
+        <v>74328.73272280001</v>
       </c>
       <c r="F367">
-        <v>37104.90337522177</v>
+        <v>35677.79170694401</v>
       </c>
     </row>
     <row r="368" spans="1:6">
@@ -8109,16 +8108,16 @@
         <v>2027</v>
       </c>
       <c r="C368">
-        <v>70748.56958400001</v>
+        <v>65507.9348</v>
       </c>
       <c r="D368">
-        <v>9904.799741760002</v>
+        <v>9171.110872000001</v>
       </c>
       <c r="E368">
-        <v>60843.76984224001</v>
+        <v>56336.823928</v>
       </c>
       <c r="F368">
-        <v>29205.0095242752</v>
+        <v>27041.67548544</v>
       </c>
     </row>
     <row r="369" spans="1:6">
@@ -8129,16 +8128,16 @@
         <v>2028</v>
       </c>
       <c r="C369">
-        <v>75366.25002816001</v>
+        <v>67291.294668</v>
       </c>
       <c r="D369">
-        <v>10551.2750039424</v>
+        <v>9420.781253520001</v>
       </c>
       <c r="E369">
-        <v>64814.97502421761</v>
+        <v>57870.51341448</v>
       </c>
       <c r="F369">
-        <v>31111.18801162445</v>
+        <v>27777.8464389504</v>
       </c>
     </row>
     <row r="370" spans="1:6">
@@ -8149,16 +8148,16 @@
         <v>2029</v>
       </c>
       <c r="C370">
-        <v>101738.68733968</v>
+        <v>87705.76494800001</v>
       </c>
       <c r="D370">
-        <v>14243.4162275552</v>
+        <v>12278.80709272</v>
       </c>
       <c r="E370">
-        <v>87495.2711121248</v>
+        <v>75426.95785528001</v>
       </c>
       <c r="F370">
-        <v>41997.73013381991</v>
+        <v>36204.9397705344</v>
       </c>
     </row>
     <row r="371" spans="1:6">
@@ -8169,16 +8168,16 @@
         <v>2030</v>
       </c>
       <c r="C371">
-        <v>96436.10065440003</v>
+        <v>80363.41721200001</v>
       </c>
       <c r="D371">
-        <v>13501.054091616</v>
+        <v>11250.87840968</v>
       </c>
       <c r="E371">
-        <v>82935.04656278402</v>
+        <v>69112.53880232001</v>
       </c>
       <c r="F371">
-        <v>39808.82235013633</v>
+        <v>33174.0186251136</v>
       </c>
     </row>
     <row r="372" spans="1:6">
@@ -8189,16 +8188,16 @@
         <v>2031</v>
       </c>
       <c r="C372">
-        <v>118380.9468944</v>
+        <v>95468.50556000002</v>
       </c>
       <c r="D372">
-        <v>16573.332565216</v>
+        <v>13365.5907784</v>
       </c>
       <c r="E372">
-        <v>101807.614329184</v>
+        <v>82102.91478160002</v>
       </c>
       <c r="F372">
-        <v>48867.65487800832</v>
+        <v>39409.39909516801</v>
       </c>
     </row>
     <row r="373" spans="1:6">
@@ -8209,16 +8208,16 @@
         <v>2032</v>
       </c>
       <c r="C373">
-        <v>115165.78687488</v>
+        <v>89973.27099600001</v>
       </c>
       <c r="D373">
-        <v>16123.2101624832</v>
+        <v>12596.25793944</v>
       </c>
       <c r="E373">
-        <v>99042.57671239681</v>
+        <v>77377.01305656</v>
       </c>
       <c r="F373">
-        <v>47540.43682195047</v>
+        <v>37140.9662671488</v>
       </c>
     </row>
     <row r="374" spans="1:6">
@@ -8229,16 +8228,16 @@
         <v>2033</v>
       </c>
       <c r="C374">
-        <v>131020.32111696</v>
+        <v>99257.81902800001</v>
       </c>
       <c r="D374">
-        <v>18342.84495637441</v>
+        <v>13896.09466392</v>
       </c>
       <c r="E374">
-        <v>112677.4761605856</v>
+        <v>85361.72436408002</v>
       </c>
       <c r="F374">
-        <v>54085.1885570811</v>
+        <v>40973.6276947584</v>
       </c>
     </row>
     <row r="375" spans="1:6">
@@ -8249,16 +8248,16 @@
         <v>2034</v>
       </c>
       <c r="C375">
-        <v>118248.05514048</v>
+        <v>86947.09936800001</v>
       </c>
       <c r="D375">
-        <v>16554.7277196672</v>
+        <v>12172.59391152</v>
       </c>
       <c r="E375">
-        <v>101693.3274208128</v>
+        <v>74774.50545648001</v>
       </c>
       <c r="F375">
-        <v>48812.79716199015</v>
+        <v>35891.76261911041</v>
       </c>
     </row>
     <row r="376" spans="1:6">
@@ -8269,16 +8268,16 @@
         <v>2035</v>
       </c>
       <c r="C376">
-        <v>115044.7115216</v>
+        <v>82174.793944</v>
       </c>
       <c r="D376">
-        <v>16106.259613024</v>
+        <v>11504.47115216</v>
       </c>
       <c r="E376">
-        <v>98938.45190857601</v>
+        <v>70670.32279184001</v>
       </c>
       <c r="F376">
-        <v>47490.45691611648</v>
+        <v>33921.7549400832</v>
       </c>
     </row>
     <row r="377" spans="1:6">
@@ -8289,16 +8288,16 @@
         <v>2036</v>
       </c>
       <c r="C377">
-        <v>117519.63822144</v>
+        <v>81610.85987600002</v>
       </c>
       <c r="D377">
-        <v>16452.7493510016</v>
+        <v>11425.52038264</v>
       </c>
       <c r="E377">
-        <v>101066.8888704384</v>
+        <v>70185.33949336001</v>
       </c>
       <c r="F377">
-        <v>48512.10665781044</v>
+        <v>33688.96295681281</v>
       </c>
     </row>
     <row r="378" spans="1:6">
@@ -8309,16 +8308,16 @@
         <v>2037</v>
       </c>
       <c r="C378">
-        <v>143288.60288656</v>
+        <v>96816.62357200001</v>
       </c>
       <c r="D378">
-        <v>20060.40440411841</v>
+        <v>13554.32730008</v>
       </c>
       <c r="E378">
-        <v>123228.1984824416</v>
+        <v>83262.29627192001</v>
       </c>
       <c r="F378">
-        <v>59149.53527157198</v>
+        <v>39965.90221052161</v>
       </c>
     </row>
     <row r="379" spans="1:6">
@@ -8329,16 +8328,16 @@
         <v>2038</v>
       </c>
       <c r="C379">
-        <v>141475.53251872</v>
+        <v>93076.00823600001</v>
       </c>
       <c r="D379">
-        <v>19806.5745526208</v>
+        <v>13030.64115304</v>
       </c>
       <c r="E379">
-        <v>121668.9579660992</v>
+        <v>80045.36708296</v>
       </c>
       <c r="F379">
-        <v>58401.09982372762</v>
+        <v>38421.7761998208</v>
       </c>
     </row>
     <row r="380" spans="1:6">
@@ -8349,16 +8348,16 @@
         <v>2039</v>
       </c>
       <c r="C380">
-        <v>126355.45455936</v>
+        <v>80997.08625600001</v>
       </c>
       <c r="D380">
-        <v>17689.7636383104</v>
+        <v>11339.59207584</v>
       </c>
       <c r="E380">
-        <v>108665.6909210496</v>
+        <v>69657.49418016001</v>
       </c>
       <c r="F380">
-        <v>52159.53164210381</v>
+        <v>33435.59720647681</v>
       </c>
     </row>
     <row r="381" spans="1:6">
@@ -8369,16 +8368,16 @@
         <v>2040</v>
       </c>
       <c r="C381">
-        <v>161416.3114368</v>
+        <v>100885.194648</v>
       </c>
       <c r="D381">
-        <v>22598.283601152</v>
+        <v>14123.92725072</v>
       </c>
       <c r="E381">
-        <v>138818.027835648</v>
+        <v>86761.26739728</v>
       </c>
       <c r="F381">
-        <v>66632.65336111105</v>
+        <v>41645.4083506944</v>
       </c>
     </row>
     <row r="382" spans="1:6">
@@ -8389,16 +8388,16 @@
         <v>2041</v>
       </c>
       <c r="C382">
-        <v>135530.81618464</v>
+        <v>82640.741576</v>
       </c>
       <c r="D382">
-        <v>18974.3142658496</v>
+        <v>11569.70382064</v>
       </c>
       <c r="E382">
-        <v>116556.5019187904</v>
+        <v>71071.03775536</v>
       </c>
       <c r="F382">
-        <v>55947.1209210194</v>
+        <v>34114.0981225728</v>
       </c>
     </row>
     <row r="383" spans="1:6">
@@ -8409,16 +8408,16 @@
         <v>2042</v>
       </c>
       <c r="C383">
-        <v>152418.89376</v>
+        <v>90725.53200000001</v>
       </c>
       <c r="D383">
-        <v>21338.6451264</v>
+        <v>12701.57448</v>
       </c>
       <c r="E383">
-        <v>131080.2486336</v>
+        <v>78023.95752000001</v>
       </c>
       <c r="F383">
-        <v>62918.51934412801</v>
+        <v>37451.4996096</v>
       </c>
     </row>
     <row r="384" spans="1:6">
@@ -8429,16 +8428,16 @@
         <v>2043</v>
       </c>
       <c r="C384">
-        <v>151089.56270064</v>
+        <v>87842.769012</v>
       </c>
       <c r="D384">
-        <v>21152.53877808961</v>
+        <v>12297.98766168</v>
       </c>
       <c r="E384">
-        <v>129937.0239225504</v>
+        <v>75544.78135032</v>
       </c>
       <c r="F384">
-        <v>62369.7714828242</v>
+        <v>36261.4950481536</v>
       </c>
     </row>
     <row r="385" spans="1:6">
@@ -8449,16 +8448,16 @@
         <v>2044</v>
       </c>
       <c r="C385">
-        <v>137918.58056064</v>
+        <v>78362.82986400001</v>
       </c>
       <c r="D385">
-        <v>19308.6012784896</v>
+        <v>10970.79618096</v>
       </c>
       <c r="E385">
-        <v>118609.9792821504</v>
+        <v>67392.03368304</v>
       </c>
       <c r="F385">
-        <v>56932.79005543219</v>
+        <v>32348.1761678592</v>
       </c>
     </row>
     <row r="386" spans="1:6">
@@ -8469,16 +8468,16 @@
         <v>2045</v>
       </c>
       <c r="C386">
-        <v>145215.7927416</v>
+        <v>80675.44041200001</v>
       </c>
       <c r="D386">
-        <v>20330.210983824</v>
+        <v>11294.56165768</v>
       </c>
       <c r="E386">
-        <v>124885.581757776</v>
+        <v>69380.87875432</v>
       </c>
       <c r="F386">
-        <v>59945.07924373249</v>
+        <v>33302.8218020736</v>
       </c>
     </row>
     <row r="387" spans="1:6">
@@ -8489,16 +8488,16 @@
         <v>2046</v>
       </c>
       <c r="C387">
-        <v>162895.7857456</v>
+        <v>88530.31834</v>
       </c>
       <c r="D387">
-        <v>22805.410004384</v>
+        <v>12394.2445676</v>
       </c>
       <c r="E387">
-        <v>140090.375741216</v>
+        <v>76136.07377239999</v>
       </c>
       <c r="F387">
-        <v>67243.38035578368</v>
+        <v>36545.315410752</v>
       </c>
     </row>
     <row r="388" spans="1:6">
@@ -8509,16 +8508,16 @@
         <v>2047</v>
       </c>
       <c r="C388">
-        <v>169508.27582752</v>
+        <v>90163.97650400002</v>
       </c>
       <c r="D388">
-        <v>23731.1586158528</v>
+        <v>12622.95671056</v>
       </c>
       <c r="E388">
-        <v>145777.1172116672</v>
+        <v>77541.01979344002</v>
       </c>
       <c r="F388">
-        <v>69973.01626160026</v>
+        <v>37219.68950085121</v>
       </c>
     </row>
     <row r="389" spans="1:6">
@@ -8529,16 +8528,16 @@
         <v>2048</v>
       </c>
       <c r="C389">
-        <v>141658.31129088</v>
+        <v>73780.37046400002</v>
       </c>
       <c r="D389">
-        <v>19832.16358072321</v>
+        <v>10329.25186496</v>
       </c>
       <c r="E389">
-        <v>121826.1477101568</v>
+        <v>63451.11859904002</v>
       </c>
       <c r="F389">
-        <v>58476.55090087528</v>
+        <v>30456.53692753921</v>
       </c>
     </row>
     <row r="390" spans="1:6">
@@ -8549,16 +8548,16 @@
         <v>2049</v>
       </c>
       <c r="C390">
-        <v>170707.8207632</v>
+        <v>87095.82692000001</v>
       </c>
       <c r="D390">
-        <v>23899.094906848</v>
+        <v>12193.4157688</v>
       </c>
       <c r="E390">
-        <v>146808.725856352</v>
+        <v>74902.41115120001</v>
       </c>
       <c r="F390">
-        <v>70468.18841104896</v>
+        <v>35953.157352576</v>
       </c>
     </row>
     <row r="391" spans="1:6">
@@ -8569,16 +8568,16 @@
         <v>2050</v>
       </c>
       <c r="C391">
-        <v>171212.648632</v>
+        <v>85606.32431600001</v>
       </c>
       <c r="D391">
-        <v>23969.77080848001</v>
+        <v>11984.88540424</v>
       </c>
       <c r="E391">
-        <v>147242.87782352</v>
+        <v>73621.43891176001</v>
       </c>
       <c r="F391">
-        <v>70676.58135528961</v>
+        <v>35338.29067764481</v>
       </c>
     </row>
     <row r="392" spans="1:6">
@@ -8609,16 +8608,16 @@
         <v>2026</v>
       </c>
       <c r="C393">
-        <v>22471.47733480001</v>
+        <v>21607.189745</v>
       </c>
       <c r="D393">
         <v>0</v>
       </c>
       <c r="E393">
-        <v>22471.47733480001</v>
+        <v>21607.189745</v>
       </c>
       <c r="F393">
-        <v>22471.47733480001</v>
+        <v>21607.189745</v>
       </c>
     </row>
     <row r="394" spans="1:6">
@@ -8629,16 +8628,16 @@
         <v>2027</v>
       </c>
       <c r="C394">
-        <v>17687.142396</v>
+        <v>16376.9837</v>
       </c>
       <c r="D394">
         <v>0</v>
       </c>
       <c r="E394">
-        <v>17687.142396</v>
+        <v>16376.9837</v>
       </c>
       <c r="F394">
-        <v>17687.142396</v>
+        <v>16376.9837</v>
       </c>
     </row>
     <row r="395" spans="1:6">
@@ -8649,16 +8648,16 @@
         <v>2028</v>
       </c>
       <c r="C395">
-        <v>18841.56250704</v>
+        <v>16822.823667</v>
       </c>
       <c r="D395">
         <v>0</v>
       </c>
       <c r="E395">
-        <v>18841.56250704</v>
+        <v>16822.823667</v>
       </c>
       <c r="F395">
-        <v>18841.56250704</v>
+        <v>16822.823667</v>
       </c>
     </row>
     <row r="396" spans="1:6">
@@ -8669,16 +8668,16 @@
         <v>2029</v>
       </c>
       <c r="C396">
-        <v>25434.67183492</v>
+        <v>21926.441237</v>
       </c>
       <c r="D396">
         <v>0</v>
       </c>
       <c r="E396">
-        <v>25434.67183492</v>
+        <v>21926.441237</v>
       </c>
       <c r="F396">
-        <v>25434.67183492</v>
+        <v>21926.441237</v>
       </c>
     </row>
     <row r="397" spans="1:6">
@@ -8689,16 +8688,16 @@
         <v>2030</v>
       </c>
       <c r="C397">
-        <v>24109.02516360001</v>
+        <v>20090.854303</v>
       </c>
       <c r="D397">
         <v>0</v>
       </c>
       <c r="E397">
-        <v>24109.02516360001</v>
+        <v>20090.854303</v>
       </c>
       <c r="F397">
-        <v>24109.02516360001</v>
+        <v>20090.854303</v>
       </c>
     </row>
     <row r="398" spans="1:6">
@@ -8709,16 +8708,16 @@
         <v>2031</v>
       </c>
       <c r="C398">
-        <v>29595.2367236</v>
+        <v>23867.12639</v>
       </c>
       <c r="D398">
         <v>0</v>
       </c>
       <c r="E398">
-        <v>29595.2367236</v>
+        <v>23867.12639</v>
       </c>
       <c r="F398">
-        <v>29595.2367236</v>
+        <v>23867.12639</v>
       </c>
     </row>
     <row r="399" spans="1:6">
@@ -8729,16 +8728,16 @@
         <v>2032</v>
       </c>
       <c r="C399">
-        <v>28791.44671872</v>
+        <v>22493.317749</v>
       </c>
       <c r="D399">
         <v>0</v>
       </c>
       <c r="E399">
-        <v>28791.44671872</v>
+        <v>22493.317749</v>
       </c>
       <c r="F399">
-        <v>28791.44671872</v>
+        <v>22493.317749</v>
       </c>
     </row>
     <row r="400" spans="1:6">
@@ -8749,16 +8748,16 @@
         <v>2033</v>
       </c>
       <c r="C400">
-        <v>32755.08027924001</v>
+        <v>24814.454757</v>
       </c>
       <c r="D400">
         <v>0</v>
       </c>
       <c r="E400">
-        <v>32755.08027924001</v>
+        <v>24814.454757</v>
       </c>
       <c r="F400">
-        <v>32755.08027924001</v>
+        <v>24814.454757</v>
       </c>
     </row>
     <row r="401" spans="1:6">
@@ -8769,16 +8768,16 @@
         <v>2034</v>
       </c>
       <c r="C401">
-        <v>29562.01378512001</v>
+        <v>21736.774842</v>
       </c>
       <c r="D401">
         <v>0</v>
       </c>
       <c r="E401">
-        <v>29562.01378512001</v>
+        <v>21736.774842</v>
       </c>
       <c r="F401">
-        <v>29562.01378512001</v>
+        <v>21736.774842</v>
       </c>
     </row>
     <row r="402" spans="1:6">
@@ -8789,16 +8788,16 @@
         <v>2035</v>
       </c>
       <c r="C402">
-        <v>28761.1778804</v>
+        <v>20543.698486</v>
       </c>
       <c r="D402">
         <v>0</v>
       </c>
       <c r="E402">
-        <v>28761.1778804</v>
+        <v>20543.698486</v>
       </c>
       <c r="F402">
-        <v>28761.1778804</v>
+        <v>20543.698486</v>
       </c>
     </row>
     <row r="403" spans="1:6">
@@ -8809,16 +8808,16 @@
         <v>2036</v>
       </c>
       <c r="C403">
-        <v>29379.90955536001</v>
+        <v>20402.714969</v>
       </c>
       <c r="D403">
         <v>0</v>
       </c>
       <c r="E403">
-        <v>29379.90955536001</v>
+        <v>20402.714969</v>
       </c>
       <c r="F403">
-        <v>29379.90955536001</v>
+        <v>20402.714969</v>
       </c>
     </row>
     <row r="404" spans="1:6">
@@ -8829,16 +8828,16 @@
         <v>2037</v>
       </c>
       <c r="C404">
-        <v>35822.15072164001</v>
+        <v>24204.155893</v>
       </c>
       <c r="D404">
         <v>0</v>
       </c>
       <c r="E404">
-        <v>35822.15072164001</v>
+        <v>24204.155893</v>
       </c>
       <c r="F404">
-        <v>35822.15072164001</v>
+        <v>24204.155893</v>
       </c>
     </row>
     <row r="405" spans="1:6">
@@ -8849,16 +8848,16 @@
         <v>2038</v>
       </c>
       <c r="C405">
-        <v>35368.88312968001</v>
+        <v>23269.002059</v>
       </c>
       <c r="D405">
         <v>0</v>
       </c>
       <c r="E405">
-        <v>35368.88312968001</v>
+        <v>23269.002059</v>
       </c>
       <c r="F405">
-        <v>35368.88312968001</v>
+        <v>23269.002059</v>
       </c>
     </row>
     <row r="406" spans="1:6">
@@ -8869,16 +8868,16 @@
         <v>2039</v>
       </c>
       <c r="C406">
-        <v>31588.86363984</v>
+        <v>20249.271564</v>
       </c>
       <c r="D406">
         <v>0</v>
       </c>
       <c r="E406">
-        <v>31588.86363984</v>
+        <v>20249.271564</v>
       </c>
       <c r="F406">
-        <v>31588.86363984</v>
+        <v>20249.271564</v>
       </c>
     </row>
     <row r="407" spans="1:6">
@@ -8889,16 +8888,16 @@
         <v>2040</v>
       </c>
       <c r="C407">
-        <v>40354.07785920001</v>
+        <v>25221.298662</v>
       </c>
       <c r="D407">
         <v>0</v>
       </c>
       <c r="E407">
-        <v>40354.07785920001</v>
+        <v>25221.298662</v>
       </c>
       <c r="F407">
-        <v>40354.07785920001</v>
+        <v>25221.298662</v>
       </c>
     </row>
     <row r="408" spans="1:6">
@@ -8909,16 +8908,16 @@
         <v>2041</v>
       </c>
       <c r="C408">
-        <v>33882.70404616</v>
+        <v>20660.185394</v>
       </c>
       <c r="D408">
         <v>0</v>
       </c>
       <c r="E408">
-        <v>33882.70404616</v>
+        <v>20660.185394</v>
       </c>
       <c r="F408">
-        <v>33882.70404616</v>
+        <v>20660.185394</v>
       </c>
     </row>
     <row r="409" spans="1:6">
@@ -8929,16 +8928,16 @@
         <v>2042</v>
       </c>
       <c r="C409">
-        <v>38104.72344</v>
+        <v>22681.383</v>
       </c>
       <c r="D409">
         <v>0</v>
       </c>
       <c r="E409">
-        <v>38104.72344</v>
+        <v>22681.383</v>
       </c>
       <c r="F409">
-        <v>38104.72344</v>
+        <v>22681.383</v>
       </c>
     </row>
     <row r="410" spans="1:6">
@@ -8949,16 +8948,16 @@
         <v>2043</v>
       </c>
       <c r="C410">
-        <v>37772.39067516001</v>
+        <v>21960.692253</v>
       </c>
       <c r="D410">
         <v>0</v>
       </c>
       <c r="E410">
-        <v>37772.39067516001</v>
+        <v>21960.692253</v>
       </c>
       <c r="F410">
-        <v>37772.39067516001</v>
+        <v>21960.692253</v>
       </c>
     </row>
     <row r="411" spans="1:6">
@@ -8969,16 +8968,16 @@
         <v>2044</v>
       </c>
       <c r="C411">
-        <v>34479.64514016</v>
+        <v>19590.707466</v>
       </c>
       <c r="D411">
         <v>0</v>
       </c>
       <c r="E411">
-        <v>34479.64514016</v>
+        <v>19590.707466</v>
       </c>
       <c r="F411">
-        <v>34479.64514016</v>
+        <v>19590.707466</v>
       </c>
     </row>
     <row r="412" spans="1:6">
@@ -8989,16 +8988,16 @@
         <v>2045</v>
       </c>
       <c r="C412">
-        <v>36303.9481854</v>
+        <v>20168.860103</v>
       </c>
       <c r="D412">
         <v>0</v>
       </c>
       <c r="E412">
-        <v>36303.9481854</v>
+        <v>20168.860103</v>
       </c>
       <c r="F412">
-        <v>36303.9481854</v>
+        <v>20168.860103</v>
       </c>
     </row>
     <row r="413" spans="1:6">
@@ -9009,16 +9008,16 @@
         <v>2046</v>
       </c>
       <c r="C413">
-        <v>40723.9464364</v>
+        <v>22132.579585</v>
       </c>
       <c r="D413">
         <v>0</v>
       </c>
       <c r="E413">
-        <v>40723.9464364</v>
+        <v>22132.579585</v>
       </c>
       <c r="F413">
-        <v>40723.9464364</v>
+        <v>22132.579585</v>
       </c>
     </row>
     <row r="414" spans="1:6">
@@ -9029,16 +9028,16 @@
         <v>2047</v>
       </c>
       <c r="C414">
-        <v>42377.06895688</v>
+        <v>22540.99412600001</v>
       </c>
       <c r="D414">
         <v>0</v>
       </c>
       <c r="E414">
-        <v>42377.06895688</v>
+        <v>22540.99412600001</v>
       </c>
       <c r="F414">
-        <v>42377.06895688</v>
+        <v>22540.99412600001</v>
       </c>
     </row>
     <row r="415" spans="1:6">
@@ -9049,16 +9048,16 @@
         <v>2048</v>
       </c>
       <c r="C415">
-        <v>35414.57782272001</v>
+        <v>18445.09261600001</v>
       </c>
       <c r="D415">
         <v>0</v>
       </c>
       <c r="E415">
-        <v>35414.57782272001</v>
+        <v>18445.09261600001</v>
       </c>
       <c r="F415">
-        <v>35414.57782272001</v>
+        <v>18445.09261600001</v>
       </c>
     </row>
     <row r="416" spans="1:6">
@@ -9069,16 +9068,16 @@
         <v>2049</v>
       </c>
       <c r="C416">
-        <v>42676.9551908</v>
+        <v>21773.95673</v>
       </c>
       <c r="D416">
         <v>0</v>
       </c>
       <c r="E416">
-        <v>42676.9551908</v>
+        <v>21773.95673</v>
       </c>
       <c r="F416">
-        <v>42676.9551908</v>
+        <v>21773.95673</v>
       </c>
     </row>
     <row r="417" spans="1:6">
@@ -9089,16 +9088,16 @@
         <v>2050</v>
       </c>
       <c r="C417">
-        <v>42803.16215800001</v>
+        <v>21401.581079</v>
       </c>
       <c r="D417">
         <v>0</v>
       </c>
       <c r="E417">
-        <v>42803.16215800001</v>
+        <v>21401.581079</v>
       </c>
       <c r="F417">
-        <v>42803.16215800001</v>
+        <v>21401.581079</v>
       </c>
     </row>
     <row r="418" spans="1:6">
@@ -9129,13 +9128,13 @@
         <v>2026</v>
       </c>
       <c r="C419">
-        <v>44942.95466960001</v>
+        <v>43214.37949000001</v>
       </c>
       <c r="D419">
-        <v>10715.28208157723</v>
+        <v>10303.15584767041</v>
       </c>
       <c r="E419">
-        <v>34227.67258802278</v>
+        <v>32911.2236423296</v>
       </c>
       <c r="F419">
         <v>0</v>
@@ -9149,13 +9148,13 @@
         <v>2027</v>
       </c>
       <c r="C420">
-        <v>35374.28479200001</v>
+        <v>32753.9674</v>
       </c>
       <c r="D420">
-        <v>8433.923465132537</v>
+        <v>7809.188393641237</v>
       </c>
       <c r="E420">
-        <v>26940.36132686747</v>
+        <v>24944.77900635876</v>
       </c>
       <c r="F420">
         <v>0</v>
@@ -9169,13 +9168,13 @@
         <v>2028</v>
       </c>
       <c r="C421">
-        <v>37683.12501408</v>
+        <v>33645.647334</v>
       </c>
       <c r="D421">
-        <v>8984.396268773393</v>
+        <v>8021.782382833386</v>
       </c>
       <c r="E421">
-        <v>28698.72874530661</v>
+        <v>25623.86495116662</v>
       </c>
       <c r="F421">
         <v>0</v>
@@ -9189,13 +9188,13 @@
         <v>2029</v>
       </c>
       <c r="C422">
-        <v>50869.34366984</v>
+        <v>43852.88247400001</v>
       </c>
       <c r="D422">
-        <v>12128.2494827989</v>
+        <v>10455.38748517146</v>
       </c>
       <c r="E422">
-        <v>38741.0941870411</v>
+        <v>33397.49498882854</v>
       </c>
       <c r="F422">
         <v>0</v>
@@ -9209,13 +9208,13 @@
         <v>2030</v>
       </c>
       <c r="C423">
-        <v>48218.05032720001</v>
+        <v>40181.70860600001</v>
       </c>
       <c r="D423">
-        <v>11496.12913699057</v>
+        <v>9580.107614158811</v>
       </c>
       <c r="E423">
-        <v>36721.92119020944</v>
+        <v>30601.60099184119</v>
       </c>
       <c r="F423">
         <v>0</v>
@@ -9229,13 +9228,13 @@
         <v>2031</v>
       </c>
       <c r="C424">
-        <v>59190.47344720001</v>
+        <v>47734.25278000001</v>
       </c>
       <c r="D424">
-        <v>14112.17006517519</v>
+        <v>11380.78231062516</v>
       </c>
       <c r="E424">
-        <v>45078.30338202481</v>
+        <v>36353.47046937485</v>
       </c>
       <c r="F424">
         <v>0</v>
@@ -9249,13 +9248,13 @@
         <v>2032</v>
       </c>
       <c r="C425">
-        <v>57582.89343744001</v>
+        <v>44986.635498</v>
       </c>
       <c r="D425">
-        <v>13728.89145343463</v>
+        <v>10725.69644799581</v>
       </c>
       <c r="E425">
-        <v>43854.00198400536</v>
+        <v>34260.93905000419</v>
       </c>
       <c r="F425">
         <v>0</v>
@@ -9269,13 +9268,13 @@
         <v>2033</v>
       </c>
       <c r="C426">
-        <v>65510.16055848001</v>
+        <v>49628.90951400001</v>
       </c>
       <c r="D426">
-        <v>15618.90745176891</v>
+        <v>11832.50564527948</v>
       </c>
       <c r="E426">
-        <v>49891.2531067111</v>
+        <v>37796.40386872052</v>
       </c>
       <c r="F426">
         <v>0</v>
@@ -9289,13 +9288,13 @@
         <v>2034</v>
       </c>
       <c r="C427">
-        <v>59124.02757024001</v>
+        <v>43473.54968400001</v>
       </c>
       <c r="D427">
-        <v>14096.32806457647</v>
+        <v>10364.94710630623</v>
       </c>
       <c r="E427">
-        <v>45027.69950566354</v>
+        <v>33108.60257769377</v>
       </c>
       <c r="F427">
         <v>0</v>
@@ -9309,13 +9308,13 @@
         <v>2035</v>
       </c>
       <c r="C428">
-        <v>57522.3557608</v>
+        <v>41087.396972</v>
       </c>
       <c r="D428">
-        <v>13714.45808369894</v>
+        <v>9796.041488356384</v>
       </c>
       <c r="E428">
-        <v>43807.89767710106</v>
+        <v>31291.35548364362</v>
       </c>
       <c r="F428">
         <v>0</v>
@@ -9329,13 +9328,13 @@
         <v>2036</v>
       </c>
       <c r="C429">
-        <v>58759.81911072001</v>
+        <v>40805.42993800001</v>
       </c>
       <c r="D429">
-        <v>14009.49362280593</v>
+        <v>9728.81501583745</v>
       </c>
       <c r="E429">
-        <v>44750.32548791408</v>
+        <v>31076.61492216256</v>
       </c>
       <c r="F429">
         <v>0</v>
@@ -9349,13 +9348,13 @@
         <v>2037</v>
       </c>
       <c r="C430">
-        <v>71644.30144328001</v>
+        <v>48408.31178600001</v>
       </c>
       <c r="D430">
-        <v>17081.40697793442</v>
+        <v>11541.49120130704</v>
       </c>
       <c r="E430">
-        <v>54562.89446534559</v>
+        <v>36866.82058469296</v>
       </c>
       <c r="F430">
         <v>0</v>
@@ -9369,13 +9368,13 @@
         <v>2038</v>
       </c>
       <c r="C431">
-        <v>70737.76625936001</v>
+        <v>46538.004118</v>
       </c>
       <c r="D431">
-        <v>16865.27120573189</v>
+        <v>11095.57316166571</v>
       </c>
       <c r="E431">
-        <v>53872.49505362812</v>
+        <v>35442.43095633429</v>
       </c>
       <c r="F431">
         <v>0</v>
@@ -9389,13 +9388,13 @@
         <v>2039</v>
       </c>
       <c r="C432">
-        <v>63177.72727968</v>
+        <v>40498.543128</v>
       </c>
       <c r="D432">
-        <v>15062.80960055875</v>
+        <v>9655.647179845355</v>
       </c>
       <c r="E432">
-        <v>48114.91767912124</v>
+        <v>30842.89594815465</v>
       </c>
       <c r="F432">
         <v>0</v>
@@ -9409,13 +9408,13 @@
         <v>2040</v>
       </c>
       <c r="C433">
-        <v>80708.15571840001</v>
+        <v>50442.597324</v>
       </c>
       <c r="D433">
-        <v>19242.40765130391</v>
+        <v>12026.50478206495</v>
       </c>
       <c r="E433">
-        <v>61465.74806709609</v>
+        <v>38416.09254193505</v>
       </c>
       <c r="F433">
         <v>0</v>
@@ -9429,13 +9428,13 @@
         <v>2041</v>
       </c>
       <c r="C434">
-        <v>67765.40809232001</v>
+        <v>41320.370788</v>
       </c>
       <c r="D434">
-        <v>16156.60270715502</v>
+        <v>9851.58701655794</v>
       </c>
       <c r="E434">
-        <v>51608.80538516498</v>
+        <v>31468.78377144206</v>
       </c>
       <c r="F434">
         <v>0</v>
@@ -9449,13 +9448,13 @@
         <v>2042</v>
       </c>
       <c r="C435">
-        <v>76209.44688</v>
+        <v>45362.766</v>
       </c>
       <c r="D435">
-        <v>18169.82720881362</v>
+        <v>10815.37333857954</v>
       </c>
       <c r="E435">
-        <v>58039.61967118637</v>
+        <v>34547.39266142046</v>
       </c>
       <c r="F435">
         <v>0</v>
@@ -9469,13 +9468,13 @@
         <v>2043</v>
       </c>
       <c r="C436">
-        <v>75544.78135032002</v>
+        <v>43921.384506</v>
       </c>
       <c r="D436">
-        <v>18011.35790716712</v>
+        <v>10471.71971346925</v>
       </c>
       <c r="E436">
-        <v>57533.4234431529</v>
+        <v>33449.66479253075</v>
       </c>
       <c r="F436">
         <v>0</v>
@@ -9489,13 +9488,13 @@
         <v>2044</v>
       </c>
       <c r="C437">
-        <v>68959.29028032</v>
+        <v>39181.41493200001</v>
       </c>
       <c r="D437">
-        <v>16441.24764228751</v>
+        <v>9341.617978572449</v>
       </c>
       <c r="E437">
-        <v>52518.04263803249</v>
+        <v>29839.79695342755</v>
       </c>
       <c r="F437">
         <v>0</v>
@@ -9509,13 +9508,13 @@
         <v>2045</v>
       </c>
       <c r="C438">
-        <v>72607.89637080001</v>
+        <v>40337.72020600001</v>
       </c>
       <c r="D438">
-        <v>17311.14691240601</v>
+        <v>9617.303840225561</v>
       </c>
       <c r="E438">
-        <v>55296.74945839399</v>
+        <v>30720.41636577444</v>
       </c>
       <c r="F438">
         <v>0</v>
@@ -9529,13 +9528,13 @@
         <v>2046</v>
       </c>
       <c r="C439">
-        <v>81447.8928728</v>
+        <v>44265.15917</v>
       </c>
       <c r="D439">
-        <v>19418.77550103456</v>
+        <v>10553.68233751878</v>
       </c>
       <c r="E439">
-        <v>62029.11737176544</v>
+        <v>33711.47683248122</v>
       </c>
       <c r="F439">
         <v>0</v>
@@ -9549,13 +9548,13 @@
         <v>2047</v>
       </c>
       <c r="C440">
-        <v>84754.13791376</v>
+        <v>45081.98825200001</v>
       </c>
       <c r="D440">
-        <v>20207.04918052777</v>
+        <v>10748.43041517435</v>
       </c>
       <c r="E440">
-        <v>64547.08873323222</v>
+        <v>34333.55783682566</v>
       </c>
       <c r="F440">
         <v>0</v>
@@ -9569,13 +9568,13 @@
         <v>2048</v>
       </c>
       <c r="C441">
-        <v>70829.15564544001</v>
+        <v>36890.18523200001</v>
       </c>
       <c r="D441">
-        <v>16887.06022824517</v>
+        <v>8795.343868877693</v>
       </c>
       <c r="E441">
-        <v>53942.09541719484</v>
+        <v>28094.84136312232</v>
       </c>
       <c r="F441">
         <v>0</v>
@@ -9589,13 +9588,13 @@
         <v>2049</v>
       </c>
       <c r="C442">
-        <v>85353.9103816</v>
+        <v>43547.91346</v>
       </c>
       <c r="D442">
-        <v>20350.0467031632</v>
+        <v>10382.67688936898</v>
       </c>
       <c r="E442">
-        <v>65003.86367843679</v>
+        <v>33165.23657063102</v>
       </c>
       <c r="F442">
         <v>0</v>
@@ -9609,13 +9608,13 @@
         <v>2050</v>
       </c>
       <c r="C443">
-        <v>85606.32431600001</v>
+        <v>42803.16215800001</v>
       </c>
       <c r="D443">
-        <v>20410.22713696646</v>
+        <v>10205.11356848323</v>
       </c>
       <c r="E443">
-        <v>65196.09717903355</v>
+        <v>32598.04858951677</v>
       </c>
       <c r="F443">
         <v>0</v>
@@ -9669,16 +9668,16 @@
         <v>2027</v>
       </c>
       <c r="C446">
-        <v>197.3170434072485</v>
+        <v>193.1243259068967</v>
       </c>
       <c r="D446">
         <v>0</v>
       </c>
       <c r="E446">
-        <v>197.3170434072485</v>
+        <v>193.1243259068967</v>
       </c>
       <c r="F446">
-        <v>197.3170434072485</v>
+        <v>193.1243259068967</v>
       </c>
     </row>
     <row r="447" spans="1:6">
@@ -9689,16 +9688,16 @@
         <v>2028</v>
       </c>
       <c r="C447">
-        <v>275.0751037463625</v>
+        <v>264.6982214982827</v>
       </c>
       <c r="D447">
         <v>0</v>
       </c>
       <c r="E447">
-        <v>275.0751037463625</v>
+        <v>264.6982214982827</v>
       </c>
       <c r="F447">
-        <v>275.0751037463625</v>
+        <v>264.6982214982827</v>
       </c>
     </row>
     <row r="448" spans="1:6">
@@ -9709,16 +9708,16 @@
         <v>2029</v>
       </c>
       <c r="C448">
-        <v>355.3119520812536</v>
+        <v>335.5652323218044</v>
       </c>
       <c r="D448">
         <v>0</v>
       </c>
       <c r="E448">
-        <v>355.3119520812536</v>
+        <v>335.5652323218044</v>
       </c>
       <c r="F448">
-        <v>355.3119520812536</v>
+        <v>335.5652323218044</v>
       </c>
     </row>
     <row r="449" spans="1:6">
@@ -9729,16 +9728,16 @@
         <v>2030</v>
       </c>
       <c r="C449">
-        <v>464.3325180599163</v>
+        <v>428.3704882484225</v>
       </c>
       <c r="D449">
         <v>0</v>
       </c>
       <c r="E449">
-        <v>464.3325180599163</v>
+        <v>428.3704882484225</v>
       </c>
       <c r="F449">
-        <v>464.3325180599163</v>
+        <v>428.3704882484225</v>
       </c>
     </row>
     <row r="450" spans="1:6">
@@ -9749,16 +9748,16 @@
         <v>2031</v>
       </c>
       <c r="C450">
-        <v>562.5683674437217</v>
+        <v>508.57464215398</v>
       </c>
       <c r="D450">
         <v>0</v>
       </c>
       <c r="E450">
-        <v>562.5683674437217</v>
+        <v>508.57464215398</v>
       </c>
       <c r="F450">
-        <v>562.5683674437217</v>
+        <v>508.57464215398</v>
       </c>
     </row>
     <row r="451" spans="1:6">
@@ -9769,16 +9768,16 @@
         <v>2032</v>
       </c>
       <c r="C451">
-        <v>683.5372757726325</v>
+        <v>603.9436545154259</v>
       </c>
       <c r="D451">
         <v>0</v>
       </c>
       <c r="E451">
-        <v>683.5372757726325</v>
+        <v>603.9436545154259</v>
       </c>
       <c r="F451">
-        <v>683.5372757726325</v>
+        <v>603.9436545154259</v>
       </c>
     </row>
     <row r="452" spans="1:6">
@@ -9789,16 +9788,16 @@
         <v>2033</v>
       </c>
       <c r="C452">
-        <v>795.8243747270338</v>
+        <v>688.8967323045487</v>
       </c>
       <c r="D452">
         <v>0</v>
       </c>
       <c r="E452">
-        <v>795.8243747270338</v>
+        <v>688.8967323045487</v>
       </c>
       <c r="F452">
-        <v>795.8243747270338</v>
+        <v>688.8967323045487</v>
       </c>
     </row>
     <row r="453" spans="1:6">
@@ -9809,16 +9808,16 @@
         <v>2034</v>
       </c>
       <c r="C453">
-        <v>922.9467163231312</v>
+        <v>781.8116323739041</v>
       </c>
       <c r="D453">
         <v>0</v>
       </c>
       <c r="E453">
-        <v>922.9467163231312</v>
+        <v>781.8116323739041</v>
       </c>
       <c r="F453">
-        <v>922.9467163231312</v>
+        <v>781.8116323739041</v>
       </c>
     </row>
     <row r="454" spans="1:6">
@@ -9829,16 +9828,16 @@
         <v>2035</v>
       </c>
       <c r="C454">
-        <v>1029.611671632517</v>
+        <v>856.1964813568322</v>
       </c>
       <c r="D454">
         <v>0</v>
       </c>
       <c r="E454">
-        <v>1029.611671632517</v>
+        <v>856.1964813568322</v>
       </c>
       <c r="F454">
-        <v>1029.611671632517</v>
+        <v>856.1964813568322</v>
       </c>
     </row>
     <row r="455" spans="1:6">
@@ -9849,16 +9848,16 @@
         <v>2036</v>
       </c>
       <c r="C455">
-        <v>1128.296920514584</v>
+        <v>921.9775823974328</v>
       </c>
       <c r="D455">
         <v>0</v>
       </c>
       <c r="E455">
-        <v>1128.296920514584</v>
+        <v>921.9775823974328</v>
       </c>
       <c r="F455">
-        <v>1128.296920514584</v>
+        <v>921.9775823974328</v>
       </c>
     </row>
     <row r="456" spans="1:6">
@@ -9869,16 +9868,16 @@
         <v>2037</v>
       </c>
       <c r="C456">
-        <v>1226.244734694915</v>
+        <v>984.6307690358315</v>
       </c>
       <c r="D456">
         <v>0</v>
       </c>
       <c r="E456">
-        <v>1226.244734694915</v>
+        <v>984.6307690358315</v>
       </c>
       <c r="F456">
-        <v>1226.244734694915</v>
+        <v>984.6307690358315</v>
       </c>
     </row>
     <row r="457" spans="1:6">
@@ -9889,16 +9888,16 @@
         <v>2038</v>
       </c>
       <c r="C457">
-        <v>1351.762243946173</v>
+        <v>1063.426271390358</v>
       </c>
       <c r="D457">
         <v>0</v>
       </c>
       <c r="E457">
-        <v>1351.762243946173</v>
+        <v>1063.426271390358</v>
       </c>
       <c r="F457">
-        <v>1351.762243946173</v>
+        <v>1063.426271390358</v>
       </c>
     </row>
     <row r="458" spans="1:6">
@@ -9909,16 +9908,16 @@
         <v>2039</v>
       </c>
       <c r="C458">
-        <v>1470.29735474965</v>
+        <v>1134.742435520101</v>
       </c>
       <c r="D458">
         <v>0</v>
       </c>
       <c r="E458">
-        <v>1470.29735474965</v>
+        <v>1134.742435520101</v>
       </c>
       <c r="F458">
-        <v>1470.29735474965</v>
+        <v>1134.742435520101</v>
       </c>
     </row>
     <row r="459" spans="1:6">
@@ -9929,16 +9928,16 @@
         <v>2040</v>
       </c>
       <c r="C459">
-        <v>1566.031668823128</v>
+        <v>1188.793681886802</v>
       </c>
       <c r="D459">
         <v>0</v>
       </c>
       <c r="E459">
-        <v>1566.031668823128</v>
+        <v>1188.793681886802</v>
       </c>
       <c r="F459">
-        <v>1566.031668823128</v>
+        <v>1188.793681886802</v>
       </c>
     </row>
     <row r="460" spans="1:6">
@@ -9949,16 +9948,16 @@
         <v>2041</v>
       </c>
       <c r="C460">
-        <v>1700.787451441924</v>
+        <v>1265.073213557852</v>
       </c>
       <c r="D460">
         <v>0</v>
       </c>
       <c r="E460">
-        <v>1700.787451441924</v>
+        <v>1265.073213557852</v>
       </c>
       <c r="F460">
-        <v>1700.787451441924</v>
+        <v>1265.073213557852</v>
       </c>
     </row>
     <row r="461" spans="1:6">
@@ -9969,16 +9968,16 @@
         <v>2042</v>
       </c>
       <c r="C461">
-        <v>1799.079408261046</v>
+        <v>1316.438888527626</v>
       </c>
       <c r="D461">
         <v>0</v>
       </c>
       <c r="E461">
-        <v>1799.079408261046</v>
+        <v>1316.438888527626</v>
       </c>
       <c r="F461">
-        <v>1799.079408261046</v>
+        <v>1316.438888527626</v>
       </c>
     </row>
     <row r="462" spans="1:6">
@@ -9989,16 +9988,16 @@
         <v>2043</v>
       </c>
       <c r="C462">
-        <v>1914.30960458761</v>
+        <v>1375.860642994901</v>
       </c>
       <c r="D462">
         <v>0</v>
       </c>
       <c r="E462">
-        <v>1914.30960458761</v>
+        <v>1375.860642994901</v>
       </c>
       <c r="F462">
-        <v>1914.30960458761</v>
+        <v>1375.860642994901</v>
       </c>
     </row>
     <row r="463" spans="1:6">
@@ -10009,16 +10008,16 @@
         <v>2044</v>
       </c>
       <c r="C463">
-        <v>2023.716454572856</v>
+        <v>1429.71972390658</v>
       </c>
       <c r="D463">
         <v>0</v>
       </c>
       <c r="E463">
-        <v>2023.716454572856</v>
+        <v>1429.71972390658</v>
       </c>
       <c r="F463">
-        <v>2023.716454572856</v>
+        <v>1429.71972390658</v>
       </c>
     </row>
     <row r="464" spans="1:6">
@@ -10029,16 +10028,16 @@
         <v>2045</v>
       </c>
       <c r="C464">
-        <v>2113.206606073921</v>
+        <v>1470.257014548178</v>
       </c>
       <c r="D464">
         <v>0</v>
       </c>
       <c r="E464">
-        <v>2113.206606073921</v>
+        <v>1470.257014548178</v>
       </c>
       <c r="F464">
-        <v>2113.206606073921</v>
+        <v>1470.257014548178</v>
       </c>
     </row>
     <row r="465" spans="1:6">
@@ -10049,16 +10048,16 @@
         <v>2046</v>
       </c>
       <c r="C465">
-        <v>2208.4454420464</v>
+        <v>1512.331409113228</v>
       </c>
       <c r="D465">
         <v>0</v>
       </c>
       <c r="E465">
-        <v>2208.4454420464</v>
+        <v>1512.331409113228</v>
       </c>
       <c r="F465">
-        <v>2208.4454420464</v>
+        <v>1512.331409113228</v>
       </c>
     </row>
     <row r="466" spans="1:6">
@@ -10069,16 +10068,16 @@
         <v>2047</v>
       </c>
       <c r="C466">
-        <v>2321.810942076787</v>
+        <v>1562.60970898755</v>
       </c>
       <c r="D466">
         <v>0</v>
       </c>
       <c r="E466">
-        <v>2321.810942076787</v>
+        <v>1562.60970898755</v>
       </c>
       <c r="F466">
-        <v>2321.810942076787</v>
+        <v>1562.60970898755</v>
       </c>
     </row>
     <row r="467" spans="1:6">
@@ -10089,16 +10088,16 @@
         <v>2048</v>
       </c>
       <c r="C467">
-        <v>2439.16208562011</v>
+        <v>1613.220020883527</v>
       </c>
       <c r="D467">
         <v>0</v>
       </c>
       <c r="E467">
-        <v>2439.16208562011</v>
+        <v>1613.220020883527</v>
       </c>
       <c r="F467">
-        <v>2439.16208562011</v>
+        <v>1613.220020883527</v>
       </c>
     </row>
     <row r="468" spans="1:6">
@@ -10109,16 +10108,16 @@
         <v>2049</v>
       </c>
       <c r="C468">
-        <v>2518.568909655689</v>
+        <v>1642.308989594855</v>
       </c>
       <c r="D468">
         <v>0</v>
       </c>
       <c r="E468">
-        <v>2518.568909655689</v>
+        <v>1642.308989594855</v>
       </c>
       <c r="F468">
-        <v>2518.568909655689</v>
+        <v>1642.308989594855</v>
       </c>
     </row>
     <row r="469" spans="1:6">
@@ -10129,16 +10128,16 @@
         <v>2050</v>
       </c>
       <c r="C469">
-        <v>2630.618237688377</v>
+        <v>1686.785941997329</v>
       </c>
       <c r="D469">
         <v>0</v>
       </c>
       <c r="E469">
-        <v>2630.618237688377</v>
+        <v>1686.785941997329</v>
       </c>
       <c r="F469">
-        <v>2630.618237688377</v>
+        <v>1686.785941997329</v>
       </c>
     </row>
     <row r="470" spans="1:6">
@@ -10149,10 +10148,10 @@
         <v>2025</v>
       </c>
       <c r="C470">
-        <v>0</v>
+        <v>2657.181760100001</v>
       </c>
       <c r="D470">
-        <v>0</v>
+        <v>2657.181760100001</v>
       </c>
       <c r="E470">
         <v>0</v>
@@ -10169,13 +10168,13 @@
         <v>2026</v>
       </c>
       <c r="C471">
-        <v>0</v>
+        <v>3124.751914017218</v>
       </c>
       <c r="D471">
-        <v>0</v>
+        <v>3025.006564300001</v>
       </c>
       <c r="E471">
-        <v>0</v>
+        <v>99.74534971721717</v>
       </c>
       <c r="F471">
         <v>0</v>
@@ -10189,13 +10188,13 @@
         <v>2027</v>
       </c>
       <c r="C472">
-        <v>0</v>
+        <v>2501.995737732472</v>
       </c>
       <c r="D472">
-        <v>0</v>
+        <v>2292.777718</v>
       </c>
       <c r="E472">
-        <v>0</v>
+        <v>209.2180197324715</v>
       </c>
       <c r="F472">
         <v>0</v>
@@ -10209,13 +10208,13 @@
         <v>2028</v>
       </c>
       <c r="C473">
-        <v>0</v>
+        <v>2641.95172000314</v>
       </c>
       <c r="D473">
-        <v>0</v>
+        <v>2355.19531338</v>
       </c>
       <c r="E473">
-        <v>0</v>
+        <v>286.7564066231396</v>
       </c>
       <c r="F473">
         <v>0</v>
@@ -10229,13 +10228,13 @@
         <v>2029</v>
       </c>
       <c r="C474">
-        <v>0</v>
+        <v>3433.230774861956</v>
       </c>
       <c r="D474">
-        <v>0</v>
+        <v>3069.701773180001</v>
       </c>
       <c r="E474">
-        <v>0</v>
+        <v>363.5290016819548</v>
       </c>
       <c r="F474">
         <v>0</v>
@@ -10249,13 +10248,13 @@
         <v>2030</v>
       </c>
       <c r="C475">
-        <v>0</v>
+        <v>3276.787631355792</v>
       </c>
       <c r="D475">
-        <v>0</v>
+        <v>2812.719602420001</v>
       </c>
       <c r="E475">
-        <v>0</v>
+        <v>464.0680289357911</v>
       </c>
       <c r="F475">
         <v>0</v>
@@ -10269,13 +10268,13 @@
         <v>2031</v>
       </c>
       <c r="C476">
-        <v>0</v>
+        <v>3892.353556933479</v>
       </c>
       <c r="D476">
-        <v>0</v>
+        <v>3341.397694600001</v>
       </c>
       <c r="E476">
-        <v>0</v>
+        <v>550.9558623334783</v>
       </c>
       <c r="F476">
         <v>0</v>
@@ -10289,13 +10288,13 @@
         <v>2032</v>
       </c>
       <c r="C477">
-        <v>0</v>
+        <v>3803.336777251712</v>
       </c>
       <c r="D477">
-        <v>0</v>
+        <v>3149.06448486</v>
       </c>
       <c r="E477">
-        <v>0</v>
+        <v>654.2722923917114</v>
       </c>
       <c r="F477">
         <v>0</v>
@@ -10309,13 +10308,13 @@
         <v>2033</v>
       </c>
       <c r="C478">
-        <v>0</v>
+        <v>4220.328459309929</v>
       </c>
       <c r="D478">
-        <v>0</v>
+        <v>3474.023665980001</v>
       </c>
       <c r="E478">
-        <v>0</v>
+        <v>746.3047933299277</v>
       </c>
       <c r="F478">
         <v>0</v>
@@ -10329,13 +10328,13 @@
         <v>2034</v>
       </c>
       <c r="C479">
-        <v>0</v>
+        <v>3890.111079618397</v>
       </c>
       <c r="D479">
-        <v>0</v>
+        <v>3043.14847788</v>
       </c>
       <c r="E479">
-        <v>0</v>
+        <v>846.9626017383962</v>
       </c>
       <c r="F479">
         <v>0</v>
@@ -10349,13 +10348,13 @@
         <v>2035</v>
       </c>
       <c r="C480">
-        <v>0</v>
+        <v>3803.663976176569</v>
       </c>
       <c r="D480">
-        <v>0</v>
+        <v>2876.117788040001</v>
       </c>
       <c r="E480">
-        <v>0</v>
+        <v>927.5461881365684</v>
       </c>
       <c r="F480">
         <v>0</v>
@@ -10369,13 +10368,13 @@
         <v>2036</v>
       </c>
       <c r="C481">
-        <v>0</v>
+        <v>3855.18914325722</v>
       </c>
       <c r="D481">
-        <v>0</v>
+        <v>2856.380095660001</v>
       </c>
       <c r="E481">
-        <v>0</v>
+        <v>998.809047597219</v>
       </c>
       <c r="F481">
         <v>0</v>
@@ -10389,13 +10388,13 @@
         <v>2037</v>
       </c>
       <c r="C482">
-        <v>0</v>
+        <v>4455.265158142151</v>
       </c>
       <c r="D482">
-        <v>0</v>
+        <v>3388.581825020001</v>
       </c>
       <c r="E482">
-        <v>0</v>
+        <v>1066.683333122151</v>
       </c>
       <c r="F482">
         <v>0</v>
@@ -10409,13 +10408,13 @@
         <v>2038</v>
       </c>
       <c r="C483">
-        <v>0</v>
+        <v>4409.705415599555</v>
       </c>
       <c r="D483">
-        <v>0</v>
+        <v>3257.66028826</v>
       </c>
       <c r="E483">
-        <v>0</v>
+        <v>1152.045127339554</v>
       </c>
       <c r="F483">
         <v>0</v>
@@ -10429,13 +10428,13 @@
         <v>2039</v>
       </c>
       <c r="C484">
-        <v>0</v>
+        <v>4064.202324106777</v>
       </c>
       <c r="D484">
-        <v>0</v>
+        <v>2834.898018960001</v>
       </c>
       <c r="E484">
-        <v>0</v>
+        <v>1229.304305146776</v>
       </c>
       <c r="F484">
         <v>0</v>
@@ -10449,13 +10448,13 @@
         <v>2040</v>
       </c>
       <c r="C485">
-        <v>0</v>
+        <v>4818.841634724036</v>
       </c>
       <c r="D485">
-        <v>0</v>
+        <v>3530.981812680001</v>
       </c>
       <c r="E485">
-        <v>0</v>
+        <v>1287.859822044036</v>
       </c>
       <c r="F485">
         <v>0</v>
@@ -10469,13 +10468,13 @@
         <v>2041</v>
       </c>
       <c r="C486">
-        <v>0</v>
+        <v>4262.92193651434</v>
       </c>
       <c r="D486">
-        <v>0</v>
+        <v>2892.42595516</v>
       </c>
       <c r="E486">
-        <v>0</v>
+        <v>1370.49598135434</v>
       </c>
       <c r="F486">
         <v>0</v>
@@ -10489,13 +10488,13 @@
         <v>2042</v>
       </c>
       <c r="C487">
-        <v>0</v>
+        <v>4601.535749238263</v>
       </c>
       <c r="D487">
-        <v>0</v>
+        <v>3175.393620000001</v>
       </c>
       <c r="E487">
-        <v>0</v>
+        <v>1426.142129238262</v>
       </c>
       <c r="F487">
         <v>0</v>
@@ -10509,13 +10508,13 @@
         <v>2043</v>
       </c>
       <c r="C488">
-        <v>0</v>
+        <v>4565.012611997809</v>
       </c>
       <c r="D488">
-        <v>0</v>
+        <v>3074.49691542</v>
       </c>
       <c r="E488">
-        <v>0</v>
+        <v>1490.515696577809</v>
       </c>
       <c r="F488">
         <v>0</v>
@@ -10529,13 +10528,13 @@
         <v>2044</v>
       </c>
       <c r="C489">
-        <v>0</v>
+        <v>4291.56207947213</v>
       </c>
       <c r="D489">
-        <v>0</v>
+        <v>2742.699045240001</v>
       </c>
       <c r="E489">
-        <v>0</v>
+        <v>1548.863034232129</v>
       </c>
       <c r="F489">
         <v>0</v>
@@ -10549,13 +10548,13 @@
         <v>2045</v>
       </c>
       <c r="C490">
-        <v>0</v>
+        <v>4416.418846847194</v>
       </c>
       <c r="D490">
-        <v>0</v>
+        <v>2823.640414420001</v>
       </c>
       <c r="E490">
-        <v>0</v>
+        <v>1592.778432427194</v>
       </c>
       <c r="F490">
         <v>0</v>
@@ -10569,13 +10568,13 @@
         <v>2046</v>
       </c>
       <c r="C491">
-        <v>0</v>
+        <v>4736.92016843933</v>
       </c>
       <c r="D491">
-        <v>0</v>
+        <v>3098.5611419</v>
       </c>
       <c r="E491">
-        <v>0</v>
+        <v>1638.35902653933</v>
       </c>
       <c r="F491">
         <v>0</v>
@@ -10589,13 +10588,13 @@
         <v>2047</v>
       </c>
       <c r="C492">
-        <v>0</v>
+        <v>4848.566362376514</v>
       </c>
       <c r="D492">
-        <v>0</v>
+        <v>3155.739177640001</v>
       </c>
       <c r="E492">
-        <v>0</v>
+        <v>1692.827184736513</v>
       </c>
       <c r="F492">
         <v>0</v>
@@ -10609,13 +10608,13 @@
         <v>2048</v>
       </c>
       <c r="C493">
-        <v>0</v>
+        <v>4329.967988863822</v>
       </c>
       <c r="D493">
-        <v>0</v>
+        <v>2582.312966240001</v>
       </c>
       <c r="E493">
-        <v>0</v>
+        <v>1747.655022623821</v>
       </c>
       <c r="F493">
         <v>0</v>
@@ -10629,13 +10628,13 @@
         <v>2049</v>
       </c>
       <c r="C494">
-        <v>0</v>
+        <v>4827.522014261093</v>
       </c>
       <c r="D494">
-        <v>0</v>
+        <v>3048.3539422</v>
       </c>
       <c r="E494">
-        <v>0</v>
+        <v>1779.168072061093</v>
       </c>
       <c r="F494">
         <v>0</v>
@@ -10649,13 +10648,13 @@
         <v>2050</v>
       </c>
       <c r="C495">
-        <v>0</v>
+        <v>4823.572788223774</v>
       </c>
       <c r="D495">
-        <v>0</v>
+        <v>2996.221351060001</v>
       </c>
       <c r="E495">
-        <v>0</v>
+        <v>1827.351437163773</v>
       </c>
       <c r="F495">
         <v>0</v>
@@ -10689,16 +10688,16 @@
         <v>2026</v>
       </c>
       <c r="C497">
-        <v>22471.47733480001</v>
+        <v>21607.189745</v>
       </c>
       <c r="D497">
-        <v>3146.006826872001</v>
+        <v>3025.006564300001</v>
       </c>
       <c r="E497">
-        <v>19325.470507928</v>
+        <v>18582.1831807</v>
       </c>
       <c r="F497">
-        <v>9276.225843805441</v>
+        <v>8919.447926736002</v>
       </c>
     </row>
     <row r="498" spans="1:6">
@@ -10709,16 +10708,16 @@
         <v>2027</v>
       </c>
       <c r="C498">
-        <v>17687.142396</v>
+        <v>16376.9837</v>
       </c>
       <c r="D498">
-        <v>2476.19993544</v>
+        <v>2292.777718</v>
       </c>
       <c r="E498">
-        <v>15210.94246056</v>
+        <v>14084.205982</v>
       </c>
       <c r="F498">
-        <v>7301.252381068801</v>
+        <v>6760.418871360001</v>
       </c>
     </row>
     <row r="499" spans="1:6">
@@ -10729,16 +10728,16 @@
         <v>2028</v>
       </c>
       <c r="C499">
-        <v>18841.56250704</v>
+        <v>16822.823667</v>
       </c>
       <c r="D499">
-        <v>2637.818750985601</v>
+        <v>2355.19531338</v>
       </c>
       <c r="E499">
-        <v>16203.7437560544</v>
+        <v>14467.62835362</v>
       </c>
       <c r="F499">
-        <v>7777.797002906113</v>
+        <v>6944.4616097376</v>
       </c>
     </row>
     <row r="500" spans="1:6">
@@ -10749,16 +10748,16 @@
         <v>2029</v>
       </c>
       <c r="C500">
-        <v>25434.67183492</v>
+        <v>21926.441237</v>
       </c>
       <c r="D500">
-        <v>3560.854056888801</v>
+        <v>3069.701773180001</v>
       </c>
       <c r="E500">
-        <v>21873.8177780312</v>
+        <v>18856.73946382</v>
       </c>
       <c r="F500">
-        <v>10499.43253345498</v>
+        <v>9051.2349426336</v>
       </c>
     </row>
     <row r="501" spans="1:6">
@@ -10769,16 +10768,16 @@
         <v>2030</v>
       </c>
       <c r="C501">
-        <v>24109.02516360001</v>
+        <v>20090.854303</v>
       </c>
       <c r="D501">
-        <v>3375.263522904001</v>
+        <v>2812.719602420001</v>
       </c>
       <c r="E501">
-        <v>20733.761640696</v>
+        <v>17278.13470058</v>
       </c>
       <c r="F501">
-        <v>9952.205587534083</v>
+        <v>8293.504656278401</v>
       </c>
     </row>
     <row r="502" spans="1:6">
@@ -10789,16 +10788,16 @@
         <v>2031</v>
       </c>
       <c r="C502">
-        <v>29595.2367236</v>
+        <v>23867.12639</v>
       </c>
       <c r="D502">
-        <v>4143.333141304</v>
+        <v>3341.397694600001</v>
       </c>
       <c r="E502">
-        <v>25451.903582296</v>
+        <v>20525.7286954</v>
       </c>
       <c r="F502">
-        <v>12216.91371950208</v>
+        <v>9852.349773792002</v>
       </c>
     </row>
     <row r="503" spans="1:6">
@@ -10809,16 +10808,16 @@
         <v>2032</v>
       </c>
       <c r="C503">
-        <v>28791.44671872</v>
+        <v>22493.317749</v>
       </c>
       <c r="D503">
-        <v>4030.802540620801</v>
+        <v>3149.06448486</v>
       </c>
       <c r="E503">
-        <v>24760.6441780992</v>
+        <v>19344.25326414</v>
       </c>
       <c r="F503">
-        <v>11885.10920548762</v>
+        <v>9285.241566787201</v>
       </c>
     </row>
     <row r="504" spans="1:6">
@@ -10829,16 +10828,16 @@
         <v>2033</v>
       </c>
       <c r="C504">
-        <v>32755.08027924001</v>
+        <v>24814.454757</v>
       </c>
       <c r="D504">
-        <v>4585.711239093602</v>
+        <v>3474.023665980001</v>
       </c>
       <c r="E504">
-        <v>28169.3690401464</v>
+        <v>21340.43109102</v>
       </c>
       <c r="F504">
-        <v>13521.29713927027</v>
+        <v>10243.4069236896</v>
       </c>
     </row>
     <row r="505" spans="1:6">
@@ -10849,16 +10848,16 @@
         <v>2034</v>
       </c>
       <c r="C505">
-        <v>29562.01378512001</v>
+        <v>21736.774842</v>
       </c>
       <c r="D505">
-        <v>4138.681929916801</v>
+        <v>3043.14847788</v>
       </c>
       <c r="E505">
-        <v>25423.3318552032</v>
+        <v>18693.62636412</v>
       </c>
       <c r="F505">
-        <v>12203.19929049754</v>
+        <v>8972.940654777602</v>
       </c>
     </row>
     <row r="506" spans="1:6">
@@ -10869,16 +10868,16 @@
         <v>2035</v>
       </c>
       <c r="C506">
-        <v>28761.1778804</v>
+        <v>20543.698486</v>
       </c>
       <c r="D506">
-        <v>4026.564903256001</v>
+        <v>2876.117788040001</v>
       </c>
       <c r="E506">
-        <v>24734.612977144</v>
+        <v>17667.58069796</v>
       </c>
       <c r="F506">
-        <v>11872.61422902912</v>
+        <v>8480.4387350208</v>
       </c>
     </row>
     <row r="507" spans="1:6">
@@ -10889,16 +10888,16 @@
         <v>2036</v>
       </c>
       <c r="C507">
-        <v>29379.90955536001</v>
+        <v>20402.714969</v>
       </c>
       <c r="D507">
-        <v>4113.187337750401</v>
+        <v>2856.380095660001</v>
       </c>
       <c r="E507">
-        <v>25266.7222176096</v>
+        <v>17546.33487334</v>
       </c>
       <c r="F507">
-        <v>12128.02666445261</v>
+        <v>8422.240739203202</v>
       </c>
     </row>
     <row r="508" spans="1:6">
@@ -10909,16 +10908,16 @@
         <v>2037</v>
       </c>
       <c r="C508">
-        <v>35822.15072164001</v>
+        <v>24204.155893</v>
       </c>
       <c r="D508">
-        <v>5015.101101029602</v>
+        <v>3388.581825020001</v>
       </c>
       <c r="E508">
-        <v>30807.0496206104</v>
+        <v>20815.57406798</v>
       </c>
       <c r="F508">
-        <v>14787.38381789299</v>
+        <v>9991.475552630402</v>
       </c>
     </row>
     <row r="509" spans="1:6">
@@ -10929,16 +10928,16 @@
         <v>2038</v>
       </c>
       <c r="C509">
-        <v>35368.88312968001</v>
+        <v>23269.002059</v>
       </c>
       <c r="D509">
-        <v>4951.643638155201</v>
+        <v>3257.66028826</v>
       </c>
       <c r="E509">
-        <v>30417.2394915248</v>
+        <v>20011.34177074</v>
       </c>
       <c r="F509">
-        <v>14600.27495593191</v>
+        <v>9605.4440499552</v>
       </c>
     </row>
     <row r="510" spans="1:6">
@@ -10949,16 +10948,16 @@
         <v>2039</v>
       </c>
       <c r="C510">
-        <v>31588.86363984</v>
+        <v>20249.271564</v>
       </c>
       <c r="D510">
-        <v>4422.440909577601</v>
+        <v>2834.898018960001</v>
       </c>
       <c r="E510">
-        <v>27166.4227302624</v>
+        <v>17414.37354504</v>
       </c>
       <c r="F510">
-        <v>13039.88291052595</v>
+        <v>8358.899301619202</v>
       </c>
     </row>
     <row r="511" spans="1:6">
@@ -10969,16 +10968,16 @@
         <v>2040</v>
       </c>
       <c r="C511">
-        <v>40354.07785920001</v>
+        <v>25221.298662</v>
       </c>
       <c r="D511">
-        <v>5649.570900288001</v>
+        <v>3530.981812680001</v>
       </c>
       <c r="E511">
-        <v>34704.506958912</v>
+        <v>21690.31684932</v>
       </c>
       <c r="F511">
-        <v>16658.16334027776</v>
+        <v>10411.3520876736</v>
       </c>
     </row>
     <row r="512" spans="1:6">
@@ -10989,16 +10988,16 @@
         <v>2041</v>
       </c>
       <c r="C512">
-        <v>33882.70404616</v>
+        <v>20660.185394</v>
       </c>
       <c r="D512">
-        <v>4743.578566462401</v>
+        <v>2892.42595516</v>
       </c>
       <c r="E512">
-        <v>29139.1254796976</v>
+        <v>17767.75943884</v>
       </c>
       <c r="F512">
-        <v>13986.78023025485</v>
+        <v>8528.524530643201</v>
       </c>
     </row>
     <row r="513" spans="1:6">
@@ -11009,16 +11008,16 @@
         <v>2042</v>
       </c>
       <c r="C513">
-        <v>38104.72344</v>
+        <v>22681.383</v>
       </c>
       <c r="D513">
-        <v>5334.661281600001</v>
+        <v>3175.393620000001</v>
       </c>
       <c r="E513">
-        <v>32770.0621584</v>
+        <v>19505.98938</v>
       </c>
       <c r="F513">
-        <v>15729.629836032</v>
+        <v>9362.874902400001</v>
       </c>
     </row>
     <row r="514" spans="1:6">
@@ -11029,16 +11028,16 @@
         <v>2043</v>
       </c>
       <c r="C514">
-        <v>37772.39067516001</v>
+        <v>21960.692253</v>
       </c>
       <c r="D514">
-        <v>5288.134694522401</v>
+        <v>3074.49691542</v>
       </c>
       <c r="E514">
-        <v>32484.2559806376</v>
+        <v>18886.19533758</v>
       </c>
       <c r="F514">
-        <v>15592.44287070605</v>
+        <v>9065.3737620384</v>
       </c>
     </row>
     <row r="515" spans="1:6">
@@ -11049,16 +11048,16 @@
         <v>2044</v>
       </c>
       <c r="C515">
-        <v>34479.64514016</v>
+        <v>19590.707466</v>
       </c>
       <c r="D515">
-        <v>4827.1503196224</v>
+        <v>2742.699045240001</v>
       </c>
       <c r="E515">
-        <v>29652.4948205376</v>
+        <v>16848.00842076</v>
       </c>
       <c r="F515">
-        <v>14233.19751385805</v>
+        <v>8087.044041964801</v>
       </c>
     </row>
     <row r="516" spans="1:6">
@@ -11069,16 +11068,16 @@
         <v>2045</v>
       </c>
       <c r="C516">
-        <v>36303.9481854</v>
+        <v>20168.860103</v>
       </c>
       <c r="D516">
-        <v>5082.552745956001</v>
+        <v>2823.640414420001</v>
       </c>
       <c r="E516">
-        <v>31221.395439444</v>
+        <v>17345.21968858</v>
       </c>
       <c r="F516">
-        <v>14986.26981093312</v>
+        <v>8325.705450518401</v>
       </c>
     </row>
     <row r="517" spans="1:6">
@@ -11089,16 +11088,16 @@
         <v>2046</v>
       </c>
       <c r="C517">
-        <v>40723.9464364</v>
+        <v>22132.579585</v>
       </c>
       <c r="D517">
-        <v>5701.352501096001</v>
+        <v>3098.5611419</v>
       </c>
       <c r="E517">
-        <v>35022.593935304</v>
+        <v>19034.0184431</v>
       </c>
       <c r="F517">
-        <v>16810.84508894592</v>
+        <v>9136.328852688001</v>
       </c>
     </row>
     <row r="518" spans="1:6">
@@ -11109,16 +11108,16 @@
         <v>2047</v>
       </c>
       <c r="C518">
-        <v>42377.06895688</v>
+        <v>22540.99412600001</v>
       </c>
       <c r="D518">
-        <v>5932.789653963201</v>
+        <v>3155.739177640001</v>
       </c>
       <c r="E518">
-        <v>36444.2793029168</v>
+        <v>19385.25494836001</v>
       </c>
       <c r="F518">
-        <v>17493.25406540007</v>
+        <v>9304.922375212802</v>
       </c>
     </row>
     <row r="519" spans="1:6">
@@ -11129,16 +11128,16 @@
         <v>2048</v>
       </c>
       <c r="C519">
-        <v>35414.57782272001</v>
+        <v>18445.09261600001</v>
       </c>
       <c r="D519">
-        <v>4958.040895180801</v>
+        <v>2582.312966240001</v>
       </c>
       <c r="E519">
-        <v>30456.5369275392</v>
+        <v>15862.77964976</v>
       </c>
       <c r="F519">
-        <v>14619.13772521882</v>
+        <v>7614.134231884802</v>
       </c>
     </row>
     <row r="520" spans="1:6">
@@ -11149,16 +11148,16 @@
         <v>2049</v>
       </c>
       <c r="C520">
-        <v>42676.9551908</v>
+        <v>21773.95673</v>
       </c>
       <c r="D520">
-        <v>5974.773726712</v>
+        <v>3048.3539422</v>
       </c>
       <c r="E520">
-        <v>36702.181464088</v>
+        <v>18725.6027878</v>
       </c>
       <c r="F520">
-        <v>17617.04710276224</v>
+        <v>8988.289338144001</v>
       </c>
     </row>
     <row r="521" spans="1:6">
@@ -11169,16 +11168,16 @@
         <v>2050</v>
       </c>
       <c r="C521">
-        <v>42803.16215800001</v>
+        <v>21401.581079</v>
       </c>
       <c r="D521">
-        <v>5992.442702120002</v>
+        <v>2996.221351060001</v>
       </c>
       <c r="E521">
-        <v>36810.71945588</v>
+        <v>18405.35972794</v>
       </c>
       <c r="F521">
-        <v>17669.1453388224</v>
+        <v>8834.572669411202</v>
       </c>
     </row>
   </sheetData>
@@ -11239,16 +11238,16 @@
         <v>2026</v>
       </c>
       <c r="C3">
-        <v>-85294.39533570211</v>
+        <v>-81726.71172864398</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>-85294.39533570211</v>
+        <v>-81726.71172864398</v>
       </c>
       <c r="F3">
-        <v>-85294.39533570211</v>
+        <v>-81726.71172864398</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -11259,16 +11258,16 @@
         <v>2027</v>
       </c>
       <c r="C4">
-        <v>-46333.82263269241</v>
+        <v>-40073.58951042886</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>-46333.82263269241</v>
+        <v>-40073.58951042886</v>
       </c>
       <c r="F4">
-        <v>-46333.82263269241</v>
+        <v>-40073.58951042886</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -11279,16 +11278,16 @@
         <v>2028</v>
       </c>
       <c r="C5">
-        <v>-44386.81094628043</v>
+        <v>-38214.94408372077</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>-44386.81094628043</v>
+        <v>-38214.94408372077</v>
       </c>
       <c r="F5">
-        <v>-44386.81094628043</v>
+        <v>-38214.94408372077</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -11299,16 +11298,16 @@
         <v>2029</v>
       </c>
       <c r="C6">
-        <v>-65194.88056186266</v>
+        <v>-60171.50525672454</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>-65194.88056186266</v>
+        <v>-60171.50525672454</v>
       </c>
       <c r="F6">
-        <v>-65194.88056186266</v>
+        <v>-60171.50525672454</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -11319,16 +11318,16 @@
         <v>2030</v>
       </c>
       <c r="C7">
-        <v>-48646.38596464036</v>
+        <v>-43062.30986983521</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>-48646.38596464036</v>
+        <v>-43062.30986983521</v>
       </c>
       <c r="F7">
-        <v>-48646.38596464036</v>
+        <v>-43062.30986983521</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -11339,16 +11338,16 @@
         <v>2031</v>
       </c>
       <c r="C8">
-        <v>-62980.27009618114</v>
+        <v>-58974.84060653916</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-62980.27009618114</v>
+        <v>-58974.84060653916</v>
       </c>
       <c r="F8">
-        <v>-62980.27009618114</v>
+        <v>-58974.84060653916</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -11359,16 +11358,16 @@
         <v>2032</v>
       </c>
       <c r="C9">
-        <v>-49678.21333502984</v>
+        <v>-45663.73365574115</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>-49678.21333502984</v>
+        <v>-45663.73365574115</v>
       </c>
       <c r="F9">
-        <v>-49678.21333502984</v>
+        <v>-45663.73365574115</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -11379,16 +11378,16 @@
         <v>2033</v>
       </c>
       <c r="C10">
-        <v>-57221.8938197167</v>
+        <v>-54928.92445053672</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>-57221.8938197167</v>
+        <v>-54928.92445053672</v>
       </c>
       <c r="F10">
-        <v>-57221.8938197167</v>
+        <v>-54928.92445053672</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -11399,16 +11398,16 @@
         <v>2034</v>
       </c>
       <c r="C11">
-        <v>-37359.46394108958</v>
+        <v>-34827.98016630264</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-37359.46394108958</v>
+        <v>-34827.98016630264</v>
       </c>
       <c r="F11">
-        <v>-37359.46394108958</v>
+        <v>-34827.98016630264</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -11419,16 +11418,16 @@
         <v>2035</v>
       </c>
       <c r="C12">
-        <v>-31126.23279245861</v>
+        <v>-29584.56674370135</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>-31126.23279245861</v>
+        <v>-29584.56674370135</v>
       </c>
       <c r="F12">
-        <v>-31126.23279245861</v>
+        <v>-29584.56674370135</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -11439,16 +11438,16 @@
         <v>2036</v>
       </c>
       <c r="C13">
-        <v>-30746.36778821348</v>
+        <v>-30686.82629777159</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-30746.36778821348</v>
+        <v>-30686.82629777159</v>
       </c>
       <c r="F13">
-        <v>-30746.36778821348</v>
+        <v>-30686.82629777159</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -11459,16 +11458,16 @@
         <v>2037</v>
       </c>
       <c r="C14">
-        <v>-48274.72562828875</v>
+        <v>-51500.41233337525</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-48274.72562828875</v>
+        <v>-51500.41233337525</v>
       </c>
       <c r="F14">
-        <v>-48274.72562828875</v>
+        <v>-51500.41233337525</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -11479,16 +11478,16 @@
         <v>2038</v>
       </c>
       <c r="C15">
-        <v>-38588.62484262709</v>
+        <v>-42424.47379099473</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-38588.62484262709</v>
+        <v>-42424.47379099473</v>
       </c>
       <c r="F15">
-        <v>-38588.62484262709</v>
+        <v>-42424.47379099473</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -11499,16 +11498,16 @@
         <v>2039</v>
       </c>
       <c r="C16">
-        <v>-21566.09004537063</v>
+        <v>-25050.14108418528</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-21566.09004537063</v>
+        <v>-25050.14108418528</v>
       </c>
       <c r="F16">
-        <v>-21566.09004537063</v>
+        <v>-25050.14108418528</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -11519,16 +11518,16 @@
         <v>2040</v>
       </c>
       <c r="C17">
-        <v>-45962.45178840321</v>
+        <v>-54012.67800577352</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-45962.45178840321</v>
+        <v>-54012.67800577352</v>
       </c>
       <c r="F17">
-        <v>-45962.45178840321</v>
+        <v>-54012.67800577352</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -11539,16 +11538,16 @@
         <v>2041</v>
       </c>
       <c r="C18">
-        <v>-18621.96549812105</v>
+        <v>-24978.75496292661</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-18621.96549812105</v>
+        <v>-24978.75496292661</v>
       </c>
       <c r="F18">
-        <v>-18621.96549812105</v>
+        <v>-24978.75496292661</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -11559,16 +11558,16 @@
         <v>2042</v>
       </c>
       <c r="C19">
-        <v>-29243.65825489321</v>
+        <v>-38550.88191472943</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-29243.65825489321</v>
+        <v>-38550.88191472943</v>
       </c>
       <c r="F19">
-        <v>-29243.65825489321</v>
+        <v>-38550.88191472943</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -11579,16 +11578,16 @@
         <v>2043</v>
       </c>
       <c r="C20">
-        <v>-23405.38455686992</v>
+        <v>-33618.84776704025</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-23405.38455686992</v>
+        <v>-33618.84776704025</v>
       </c>
       <c r="F20">
-        <v>-23405.38455686992</v>
+        <v>-33618.84776704025</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -11599,16 +11598,16 @@
         <v>2044</v>
       </c>
       <c r="C21">
-        <v>-11085.90612479788</v>
+        <v>-20965.87434486131</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>-11085.90612479788</v>
+        <v>-20965.87434486131</v>
       </c>
       <c r="F21">
-        <v>-11085.90612479788</v>
+        <v>-20965.87434486131</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -11619,16 +11618,16 @@
         <v>2045</v>
       </c>
       <c r="C22">
-        <v>-15367.80230690318</v>
+        <v>-27201.65088241961</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>-15367.80230690318</v>
+        <v>-27201.65088241961</v>
       </c>
       <c r="F22">
-        <v>-15367.80230690318</v>
+        <v>-27201.65088241961</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -11639,16 +11638,16 @@
         <v>2046</v>
       </c>
       <c r="C23">
-        <v>-24059.06215391582</v>
+        <v>-38958.36165189836</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>-24059.06215391582</v>
+        <v>-38958.36165189836</v>
       </c>
       <c r="F23">
-        <v>-24059.06215391582</v>
+        <v>-38958.36165189836</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -11659,16 +11658,16 @@
         <v>2047</v>
       </c>
       <c r="C24">
-        <v>-22433.58634944842</v>
+        <v>-39094.88469046989</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>-22433.58634944842</v>
+        <v>-39094.88469046989</v>
       </c>
       <c r="F24">
-        <v>-22433.58634944842</v>
+        <v>-39094.88469046989</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -11679,16 +11678,16 @@
         <v>2048</v>
       </c>
       <c r="C25">
-        <v>-121.6935106776655</v>
+        <v>-14456.92711746477</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-121.6935106776655</v>
+        <v>-14456.92711746477</v>
       </c>
       <c r="F25">
-        <v>-121.6935106776655</v>
+        <v>-14456.92711746477</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -11699,16 +11698,16 @@
         <v>2049</v>
       </c>
       <c r="C26">
-        <v>-18346.19211280911</v>
+        <v>-37244.50194115681</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>-18346.19211280911</v>
+        <v>-37244.50194115681</v>
       </c>
       <c r="F26">
-        <v>-18346.19211280911</v>
+        <v>-37244.50194115681</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -11719,16 +11718,16 @@
         <v>2050</v>
       </c>
       <c r="C27">
-        <v>-13152.44363660697</v>
+        <v>-33116.90771382692</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>-13152.44363660697</v>
+        <v>-33116.90771382692</v>
       </c>
       <c r="F27">
-        <v>-13152.44363660697</v>
+        <v>-33116.90771382692</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -11779,16 +11778,16 @@
         <v>2027</v>
       </c>
       <c r="C30">
-        <v>-176002.9876376301</v>
+        <v>-172435.304030572</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>-176002.9876376301</v>
+        <v>-172435.304030572</v>
       </c>
       <c r="F30">
-        <v>-176002.9876376301</v>
+        <v>-172435.304030572</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -11799,16 +11798,16 @@
         <v>2028</v>
       </c>
       <c r="C31">
-        <v>-222336.8102703225</v>
+        <v>-212508.8935410008</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>-222336.8102703225</v>
+        <v>-212508.8935410008</v>
       </c>
       <c r="F31">
-        <v>-222336.8102703225</v>
+        <v>-212508.8935410008</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -11819,16 +11818,16 @@
         <v>2029</v>
       </c>
       <c r="C32">
-        <v>-266723.621216603</v>
+        <v>-250723.8376247216</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>-266723.621216603</v>
+        <v>-250723.8376247216</v>
       </c>
       <c r="F32">
-        <v>-266723.621216603</v>
+        <v>-250723.8376247216</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -11839,16 +11838,16 @@
         <v>2030</v>
       </c>
       <c r="C33">
-        <v>-331918.5017784656</v>
+        <v>-310895.3428814461</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>-331918.5017784656</v>
+        <v>-310895.3428814461</v>
       </c>
       <c r="F33">
-        <v>-331918.5017784656</v>
+        <v>-310895.3428814461</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -11859,16 +11858,16 @@
         <v>2031</v>
       </c>
       <c r="C34">
-        <v>-380564.887743106</v>
+        <v>-353957.6527512813</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>-380564.887743106</v>
+        <v>-353957.6527512813</v>
       </c>
       <c r="F34">
-        <v>-380564.887743106</v>
+        <v>-353957.6527512813</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -11879,16 +11878,16 @@
         <v>2032</v>
       </c>
       <c r="C35">
-        <v>-443545.1578392871</v>
+        <v>-412932.4933578205</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>-443545.1578392871</v>
+        <v>-412932.4933578205</v>
       </c>
       <c r="F35">
-        <v>-443545.1578392871</v>
+        <v>-412932.4933578205</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -11899,16 +11898,16 @@
         <v>2033</v>
       </c>
       <c r="C36">
-        <v>-493223.371174317</v>
+        <v>-458596.2270135616</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>-493223.371174317</v>
+        <v>-458596.2270135616</v>
       </c>
       <c r="F36">
-        <v>-493223.371174317</v>
+        <v>-458596.2270135616</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -11919,16 +11918,16 @@
         <v>2034</v>
       </c>
       <c r="C37">
-        <v>-550445.2649940336</v>
+        <v>-513525.1514640984</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>-550445.2649940336</v>
+        <v>-513525.1514640984</v>
       </c>
       <c r="F37">
-        <v>-550445.2649940336</v>
+        <v>-513525.1514640984</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -11939,16 +11938,16 @@
         <v>2035</v>
       </c>
       <c r="C38">
-        <v>-587804.7289351232</v>
+        <v>-548353.131630401</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>-587804.7289351232</v>
+        <v>-548353.131630401</v>
       </c>
       <c r="F38">
-        <v>-587804.7289351232</v>
+        <v>-548353.131630401</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -11959,16 +11958,16 @@
         <v>2036</v>
       </c>
       <c r="C39">
-        <v>-618930.9617275818</v>
+        <v>-577937.6983741024</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>-618930.9617275818</v>
+        <v>-577937.6983741024</v>
       </c>
       <c r="F39">
-        <v>-618930.9617275818</v>
+        <v>-577937.6983741024</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -11979,16 +11978,16 @@
         <v>2037</v>
       </c>
       <c r="C40">
-        <v>-649677.3295157952</v>
+        <v>-608624.524671874</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>-649677.3295157952</v>
+        <v>-608624.524671874</v>
       </c>
       <c r="F40">
-        <v>-649677.3295157952</v>
+        <v>-608624.524671874</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -11999,16 +11998,16 @@
         <v>2038</v>
       </c>
       <c r="C41">
-        <v>-697952.0551440839</v>
+        <v>-660124.9370052493</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>-697952.0551440839</v>
+        <v>-660124.9370052493</v>
       </c>
       <c r="F41">
-        <v>-697952.0551440839</v>
+        <v>-660124.9370052493</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -12019,16 +12018,16 @@
         <v>2039</v>
       </c>
       <c r="C42">
-        <v>-736540.679986711</v>
+        <v>-702549.410796244</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>-736540.679986711</v>
+        <v>-702549.410796244</v>
       </c>
       <c r="F42">
-        <v>-736540.679986711</v>
+        <v>-702549.410796244</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -12039,16 +12038,16 @@
         <v>2040</v>
       </c>
       <c r="C43">
-        <v>-758106.7700320816</v>
+        <v>-727599.5518804293</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>-758106.7700320816</v>
+        <v>-727599.5518804293</v>
       </c>
       <c r="F43">
-        <v>-758106.7700320816</v>
+        <v>-727599.5518804293</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -12059,16 +12058,16 @@
         <v>2041</v>
       </c>
       <c r="C44">
-        <v>-804069.2218204848</v>
+        <v>-781612.2298862028</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>-804069.2218204848</v>
+        <v>-781612.2298862028</v>
       </c>
       <c r="F44">
-        <v>-804069.2218204848</v>
+        <v>-781612.2298862028</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -12079,16 +12078,16 @@
         <v>2042</v>
       </c>
       <c r="C45">
-        <v>-822691.1873186058</v>
+        <v>-806590.9848491295</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>-822691.1873186058</v>
+        <v>-806590.9848491295</v>
       </c>
       <c r="F45">
-        <v>-822691.1873186058</v>
+        <v>-806590.9848491295</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -12099,16 +12098,16 @@
         <v>2043</v>
       </c>
       <c r="C46">
-        <v>-851934.8455734991</v>
+        <v>-845141.8667638588</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>-851934.8455734991</v>
+        <v>-845141.8667638588</v>
       </c>
       <c r="F46">
-        <v>-851934.8455734991</v>
+        <v>-845141.8667638588</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -12119,16 +12118,16 @@
         <v>2044</v>
       </c>
       <c r="C47">
-        <v>-875340.2301303691</v>
+        <v>-878760.7145308991</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>-875340.2301303691</v>
+        <v>-878760.7145308991</v>
       </c>
       <c r="F47">
-        <v>-875340.2301303691</v>
+        <v>-878760.7145308991</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -12139,16 +12138,16 @@
         <v>2045</v>
       </c>
       <c r="C48">
-        <v>-886426.136255167</v>
+        <v>-899726.5888757603</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>-886426.136255167</v>
+        <v>-899726.5888757603</v>
       </c>
       <c r="F48">
-        <v>-886426.136255167</v>
+        <v>-899726.5888757603</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -12159,16 +12158,16 @@
         <v>2046</v>
       </c>
       <c r="C49">
-        <v>-901793.9385620701</v>
+        <v>-926928.23975818</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>-901793.9385620701</v>
+        <v>-926928.23975818</v>
       </c>
       <c r="F49">
-        <v>-901793.9385620701</v>
+        <v>-926928.23975818</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -12179,16 +12178,16 @@
         <v>2047</v>
       </c>
       <c r="C50">
-        <v>-925853.0007159859</v>
+        <v>-965886.6014100784</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>-925853.0007159859</v>
+        <v>-965886.6014100784</v>
       </c>
       <c r="F50">
-        <v>-925853.0007159859</v>
+        <v>-965886.6014100784</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -12199,16 +12198,16 @@
         <v>2048</v>
       </c>
       <c r="C51">
-        <v>-948286.5870654343</v>
+        <v>-1004981.486100548</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>-948286.5870654343</v>
+        <v>-1004981.486100548</v>
       </c>
       <c r="F51">
-        <v>-948286.5870654343</v>
+        <v>-1004981.486100548</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -12219,16 +12218,16 @@
         <v>2049</v>
       </c>
       <c r="C52">
-        <v>-948408.280576112</v>
+        <v>-1019438.413218013</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>-948408.280576112</v>
+        <v>-1019438.413218013</v>
       </c>
       <c r="F52">
-        <v>-948408.280576112</v>
+        <v>-1019438.413218013</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -12239,16 +12238,16 @@
         <v>2050</v>
       </c>
       <c r="C53">
-        <v>-966754.472688921</v>
+        <v>-1056682.91515917</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>-966754.472688921</v>
+        <v>-1056682.91515917</v>
       </c>
       <c r="F53">
-        <v>-966754.472688921</v>
+        <v>-1056682.91515917</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -12259,10 +12258,10 @@
         <v>2025</v>
       </c>
       <c r="C54">
-        <v>-96812.52048227197</v>
+        <v>-88840.97520197195</v>
       </c>
       <c r="D54">
-        <v>-6892.744145124161</v>
+        <v>1078.801135175847</v>
       </c>
       <c r="E54">
         <v>-89919.77633714781</v>
@@ -12279,13 +12278,13 @@
         <v>2026</v>
       </c>
       <c r="C55">
-        <v>-89811.18476715055</v>
+        <v>-77805.69329934765</v>
       </c>
       <c r="D55">
-        <v>-7192.755892532965</v>
+        <v>1228.137041316222</v>
       </c>
       <c r="E55">
-        <v>-82618.4288746175</v>
+        <v>-79033.83034066384</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -12299,13 +12298,13 @@
         <v>2027</v>
       </c>
       <c r="C56">
-        <v>-47585.3368258946</v>
+        <v>-35279.1475652979</v>
       </c>
       <c r="D56">
-        <v>-4955.897660735165</v>
+        <v>930.8559868935263</v>
       </c>
       <c r="E56">
-        <v>-42629.43916515942</v>
+        <v>-36210.00355219145</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -12319,13 +12318,13 @@
         <v>2028</v>
       </c>
       <c r="C57">
-        <v>-44678.20249447785</v>
+        <v>-33044.18690275418</v>
       </c>
       <c r="D57">
-        <v>-4581.528642542384</v>
+        <v>956.1965364464122</v>
       </c>
       <c r="E57">
-        <v>-40096.67385193545</v>
+        <v>-34000.38343920058</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -12339,13 +12338,13 @@
         <v>2029</v>
       </c>
       <c r="C58">
-        <v>-65133.4985130917</v>
+        <v>-54295.66461374168</v>
       </c>
       <c r="D58">
-        <v>-5307.656450463794</v>
+        <v>1246.282304031163</v>
       </c>
       <c r="E58">
-        <v>-59825.84206262784</v>
+        <v>-55541.94691777276</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -12359,13 +12358,13 @@
         <v>2030</v>
       </c>
       <c r="C59">
-        <v>-46854.57332984393</v>
+        <v>-36672.38298849808</v>
       </c>
       <c r="D59">
-        <v>-4255.101101736262</v>
+        <v>1141.948341723983</v>
       </c>
       <c r="E59">
-        <v>-42599.47222810768</v>
+        <v>-37814.33133022208</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -12379,13 +12378,13 @@
         <v>2031</v>
       </c>
       <c r="C60">
-        <v>-60153.62294648559</v>
+        <v>-52035.40421671746</v>
       </c>
       <c r="D60">
-        <v>-4332.345052127072</v>
+        <v>1356.589383714891</v>
       </c>
       <c r="E60">
-        <v>-55821.27789435856</v>
+        <v>-53391.9936004323</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -12399,13 +12398,13 @@
         <v>2032</v>
       </c>
       <c r="C61">
-        <v>-45297.31476718112</v>
+        <v>-38297.36394504947</v>
       </c>
       <c r="D61">
-        <v>-3402.019266010218</v>
+        <v>1278.503071609346</v>
       </c>
       <c r="E61">
-        <v>-41895.29550117085</v>
+        <v>-39575.86701665894</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -12419,13 +12418,13 @@
         <v>2033</v>
       </c>
       <c r="C62">
-        <v>-51447.81087099673</v>
+        <v>-47181.82852543809</v>
       </c>
       <c r="D62">
-        <v>-3001.859986415526</v>
+        <v>1410.434058807848</v>
       </c>
       <c r="E62">
-        <v>-48445.95088458125</v>
+        <v>-48592.262584246</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -12439,13 +12438,13 @@
         <v>2034</v>
       </c>
       <c r="C63">
-        <v>-30441.92443904351</v>
+        <v>-26934.38190863444</v>
       </c>
       <c r="D63">
-        <v>-1971.495967985262</v>
+        <v>1235.501603310899</v>
       </c>
       <c r="E63">
-        <v>-28470.4284710582</v>
+        <v>-28169.88351194537</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -12459,13 +12458,13 @@
         <v>2035</v>
       </c>
       <c r="C64">
-        <v>-23426.90181020665</v>
+        <v>-21846.58125762973</v>
       </c>
       <c r="D64">
-        <v>-1241.35479029626</v>
+        <v>1167.687748049211</v>
       </c>
       <c r="E64">
-        <v>-22185.54701991036</v>
+        <v>-23014.26900567894</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -12479,13 +12478,13 @@
         <v>2036</v>
       </c>
       <c r="C65">
-        <v>-22223.97006515472</v>
+        <v>-23110.7143546493</v>
       </c>
       <c r="D65">
-        <v>-615.1724732893344</v>
+        <v>1159.6747225414</v>
       </c>
       <c r="E65">
-        <v>-21608.79759186535</v>
+        <v>-24270.38907719066</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -12499,13 +12498,13 @@
         <v>2037</v>
       </c>
       <c r="C66">
-        <v>-37867.53922982974</v>
+        <v>-43770.72303429985</v>
       </c>
       <c r="D66">
-        <v>2.953891710727476</v>
+        <v>1375.745038124151</v>
       </c>
       <c r="E66">
-        <v>-37870.49312154041</v>
+        <v>-45146.46807242389</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -12519,13 +12518,13 @@
         <v>2038</v>
       </c>
       <c r="C67">
-        <v>-27005.27047135064</v>
+        <v>-34402.90788427426</v>
       </c>
       <c r="D67">
-        <v>707.2764144624089</v>
+        <v>1322.592535385847</v>
       </c>
       <c r="E67">
-        <v>-27712.54688581306</v>
+        <v>-35725.50041966012</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -12539,13 +12538,13 @@
         <v>2039</v>
       </c>
       <c r="C68">
-        <v>-9833.931979468383</v>
+        <v>-17080.51626441407</v>
       </c>
       <c r="D68">
-        <v>1228.50718630894</v>
+        <v>1150.95304124034</v>
       </c>
       <c r="E68">
-        <v>-11062.43916577735</v>
+        <v>-18231.46930565435</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -12559,13 +12558,13 @@
         <v>2040</v>
       </c>
       <c r="C69">
-        <v>-31446.66647525923</v>
+        <v>-45987.15757079457</v>
       </c>
       <c r="D69">
-        <v>2293.69492194106</v>
+        <v>1433.559315526072</v>
       </c>
       <c r="E69">
-        <v>-33740.36139720021</v>
+        <v>-47420.71688632073</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -12579,13 +12578,13 @@
         <v>2041</v>
       </c>
       <c r="C70">
-        <v>-4609.419294735126</v>
+        <v>-16799.09093081724</v>
       </c>
       <c r="D70">
-        <v>2504.35248274311</v>
+        <v>1174.30943502122</v>
       </c>
       <c r="E70">
-        <v>-7113.771777478221</v>
+        <v>-17973.40036583837</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -12599,13 +12598,13 @@
         <v>2042</v>
       </c>
       <c r="C71">
-        <v>-13434.12487855059</v>
+        <v>-30498.36435095692</v>
       </c>
       <c r="D71">
-        <v>3436.001408554061</v>
+        <v>1289.193075119969</v>
       </c>
       <c r="E71">
-        <v>-16870.12628710468</v>
+        <v>-31787.55742607691</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -12619,13 +12618,13 @@
         <v>2043</v>
       </c>
       <c r="C72">
-        <v>-6824.678090330795</v>
+        <v>-25513.26952863694</v>
       </c>
       <c r="D72">
-        <v>3991.652669189833</v>
+        <v>1248.229663547158</v>
       </c>
       <c r="E72">
-        <v>-10816.33075952064</v>
+        <v>-26761.49919218407</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -12639,13 +12638,13 @@
         <v>2044</v>
       </c>
       <c r="C73">
-        <v>5116.960828153067</v>
+        <v>-12982.97686548653</v>
       </c>
       <c r="D73">
-        <v>4153.956287294684</v>
+        <v>1113.521210534847</v>
       </c>
       <c r="E73">
-        <v>963.004540858441</v>
+        <v>-14096.49807602132</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -12659,13 +12658,13 @@
         <v>2045</v>
       </c>
       <c r="C74">
-        <v>1916.847590776801</v>
+        <v>-19451.24870479782</v>
       </c>
       <c r="D74">
-        <v>4887.129872266873</v>
+        <v>1146.383380274419</v>
       </c>
       <c r="E74">
-        <v>-2970.282281490043</v>
+        <v>-20597.63208507228</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -12679,13 +12678,13 @@
         <v>2046</v>
       </c>
       <c r="C75">
-        <v>-4511.965961933718</v>
+        <v>-31212.3767623399</v>
       </c>
       <c r="D75">
-        <v>6032.991544485601</v>
+        <v>1257.999088277822</v>
       </c>
       <c r="E75">
-        <v>-10544.95750641939</v>
+        <v>-32470.37585061777</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -12699,13 +12698,13 @@
         <v>2047</v>
       </c>
       <c r="C76">
-        <v>-1353.034335205855</v>
+        <v>-31157.43103209563</v>
       </c>
       <c r="D76">
-        <v>6826.715223724823</v>
+        <v>1281.213038645001</v>
       </c>
       <c r="E76">
-        <v>-8179.749558930751</v>
+        <v>-32438.64407074067</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -12719,13 +12718,13 @@
         <v>2048</v>
       </c>
       <c r="C77">
-        <v>18946.6864686124</v>
+        <v>-6500.602744640142</v>
       </c>
       <c r="D77">
-        <v>6144.63903375958</v>
+        <v>1048.405715230503</v>
       </c>
       <c r="E77">
-        <v>12802.04743485275</v>
+        <v>-7549.008459870645</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -12739,13 +12738,13 @@
         <v>2049</v>
       </c>
       <c r="C78">
-        <v>4079.765233053768</v>
+        <v>-29533.81376035319</v>
       </c>
       <c r="D78">
-        <v>7912.762528279723</v>
+        <v>1237.614972061492</v>
       </c>
       <c r="E78">
-        <v>-3832.99729522597</v>
+        <v>-30771.42873241473</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -12759,13 +12758,13 @@
         <v>2050</v>
       </c>
       <c r="C79">
-        <v>10153.02824343997</v>
+        <v>-25247.1993874092</v>
       </c>
       <c r="D79">
-        <v>8425.341701605808</v>
+        <v>1216.449484182565</v>
       </c>
       <c r="E79">
-        <v>1727.686541834206</v>
+        <v>-26463.64887159172</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -12799,10 +12798,10 @@
         <v>2026</v>
       </c>
       <c r="C81">
-        <v>-96812.52048227197</v>
+        <v>-88840.97520197195</v>
       </c>
       <c r="D81">
-        <v>-6892.744145124161</v>
+        <v>1078.801135175847</v>
       </c>
       <c r="E81">
         <v>-89919.77633714781</v>
@@ -12819,13 +12818,13 @@
         <v>2027</v>
       </c>
       <c r="C82">
-        <v>-186623.7052494225</v>
+        <v>-166646.6685013196</v>
       </c>
       <c r="D82">
-        <v>-14085.50003765713</v>
+        <v>2306.938176492069</v>
       </c>
       <c r="E82">
-        <v>-172538.2052117653</v>
+        <v>-168953.6066778117</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -12839,13 +12838,13 @@
         <v>2028</v>
       </c>
       <c r="C83">
-        <v>-234209.0420753171</v>
+        <v>-201925.8160666175</v>
       </c>
       <c r="D83">
-        <v>-19041.39769839229</v>
+        <v>3237.794163385595</v>
       </c>
       <c r="E83">
-        <v>-215167.6443769247</v>
+        <v>-205163.6102300031</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -12859,13 +12858,13 @@
         <v>2029</v>
       </c>
       <c r="C84">
-        <v>-278887.244569795</v>
+        <v>-234970.0029693717</v>
       </c>
       <c r="D84">
-        <v>-23622.92634093467</v>
+        <v>4193.990699832008</v>
       </c>
       <c r="E84">
-        <v>-255264.3182288602</v>
+        <v>-239163.9936692037</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -12879,13 +12878,13 @@
         <v>2030</v>
       </c>
       <c r="C85">
-        <v>-344020.7430828867</v>
+        <v>-289265.6675831134</v>
       </c>
       <c r="D85">
-        <v>-28930.58279139847</v>
+        <v>5440.273003863171</v>
       </c>
       <c r="E85">
-        <v>-315090.160291488</v>
+        <v>-294705.9405869765</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -12899,13 +12898,13 @@
         <v>2031</v>
       </c>
       <c r="C86">
-        <v>-390875.3164127306</v>
+        <v>-325938.0505716114</v>
       </c>
       <c r="D86">
-        <v>-33185.68389313473</v>
+        <v>6582.221345587153</v>
       </c>
       <c r="E86">
-        <v>-357689.6325195957</v>
+        <v>-332520.2719171986</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -12919,13 +12918,13 @@
         <v>2032</v>
       </c>
       <c r="C87">
-        <v>-451028.9393592162</v>
+        <v>-377973.4547883289</v>
       </c>
       <c r="D87">
-        <v>-37518.0289452618</v>
+        <v>7938.810729302044</v>
       </c>
       <c r="E87">
-        <v>-413510.9104139543</v>
+        <v>-385912.2655176308</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -12939,13 +12938,13 @@
         <v>2033</v>
       </c>
       <c r="C88">
-        <v>-496326.2541263973</v>
+        <v>-416270.8187333784</v>
       </c>
       <c r="D88">
-        <v>-40920.04821127202</v>
+        <v>9217.31380091139</v>
       </c>
       <c r="E88">
-        <v>-455406.2059151251</v>
+        <v>-425488.1325342898</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -12959,13 +12958,13 @@
         <v>2034</v>
       </c>
       <c r="C89">
-        <v>-547774.0649973941</v>
+        <v>-463452.6472588165</v>
       </c>
       <c r="D89">
-        <v>-43921.90819768755</v>
+        <v>10627.74785971924</v>
       </c>
       <c r="E89">
-        <v>-503852.1567997064</v>
+        <v>-474080.3951185358</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -12979,13 +12978,13 @@
         <v>2035</v>
       </c>
       <c r="C90">
-        <v>-578215.9894364376</v>
+        <v>-490387.0291674509</v>
       </c>
       <c r="D90">
-        <v>-45893.40416567281</v>
+        <v>11863.24946303014</v>
       </c>
       <c r="E90">
-        <v>-532322.5852707645</v>
+        <v>-502250.2786304812</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -12999,13 +12998,13 @@
         <v>2036</v>
       </c>
       <c r="C91">
-        <v>-601642.8912466443</v>
+        <v>-512233.6104250806</v>
       </c>
       <c r="D91">
-        <v>-47134.75895596907</v>
+        <v>13030.93721107935</v>
       </c>
       <c r="E91">
-        <v>-554508.1322906748</v>
+        <v>-525264.5476361602</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -13019,13 +13018,13 @@
         <v>2037</v>
       </c>
       <c r="C92">
-        <v>-623866.861311799</v>
+        <v>-535344.3247797299</v>
       </c>
       <c r="D92">
-        <v>-47749.9314292584</v>
+        <v>14190.61193362075</v>
       </c>
       <c r="E92">
-        <v>-576116.9298825401</v>
+        <v>-549534.9367133508</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -13039,13 +13038,13 @@
         <v>2038</v>
       </c>
       <c r="C93">
-        <v>-661734.4005416287</v>
+        <v>-579115.0478140297</v>
       </c>
       <c r="D93">
-        <v>-47746.97753754767</v>
+        <v>15566.3569717449</v>
       </c>
       <c r="E93">
-        <v>-613987.4230040805</v>
+        <v>-594681.4047857746</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -13059,13 +13058,13 @@
         <v>2039</v>
       </c>
       <c r="C94">
-        <v>-688739.6710129794</v>
+        <v>-613517.955698304</v>
       </c>
       <c r="D94">
-        <v>-47039.70112308527</v>
+        <v>16888.94950713075</v>
       </c>
       <c r="E94">
-        <v>-641699.9698898937</v>
+        <v>-630406.9052054348</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -13079,13 +13078,13 @@
         <v>2040</v>
       </c>
       <c r="C95">
-        <v>-698573.6029924478</v>
+        <v>-630598.4719627181</v>
       </c>
       <c r="D95">
-        <v>-45811.19393677633</v>
+        <v>18039.90254837109</v>
       </c>
       <c r="E95">
-        <v>-652762.409055671</v>
+        <v>-648638.3745110892</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -13099,13 +13098,13 @@
         <v>2041</v>
       </c>
       <c r="C96">
-        <v>-730020.269467707</v>
+        <v>-676585.6295335126</v>
       </c>
       <c r="D96">
-        <v>-43517.49901483527</v>
+        <v>19473.46186389716</v>
       </c>
       <c r="E96">
-        <v>-686502.7704528712</v>
+        <v>-696059.0913974099</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -13119,13 +13118,13 @@
         <v>2042</v>
       </c>
       <c r="C97">
-        <v>-734629.6887624422</v>
+        <v>-693384.7204643299</v>
       </c>
       <c r="D97">
-        <v>-41013.14653209216</v>
+        <v>20647.77129891838</v>
       </c>
       <c r="E97">
-        <v>-693616.5422303495</v>
+        <v>-714032.4917632483</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -13139,13 +13138,13 @@
         <v>2043</v>
       </c>
       <c r="C98">
-        <v>-748063.8136409929</v>
+        <v>-723883.0848152868</v>
       </c>
       <c r="D98">
-        <v>-37577.1451235381</v>
+        <v>21936.96437403835</v>
       </c>
       <c r="E98">
-        <v>-710486.6685174542</v>
+        <v>-745820.0491893252</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -13159,13 +13158,13 @@
         <v>2044</v>
       </c>
       <c r="C99">
-        <v>-754888.4917313237</v>
+        <v>-749396.3543439237</v>
       </c>
       <c r="D99">
-        <v>-33585.49245434826</v>
+        <v>23185.1940375855</v>
       </c>
       <c r="E99">
-        <v>-721302.9992769748</v>
+        <v>-772581.5483815093</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -13179,13 +13178,13 @@
         <v>2045</v>
       </c>
       <c r="C100">
-        <v>-749771.5309031706</v>
+        <v>-762379.3312094102</v>
       </c>
       <c r="D100">
-        <v>-29431.53616705358</v>
+        <v>24298.71524812035</v>
       </c>
       <c r="E100">
-        <v>-720339.9947361164</v>
+        <v>-786678.0464575306</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -13199,13 +13198,13 @@
         <v>2046</v>
       </c>
       <c r="C101">
-        <v>-747854.6833123937</v>
+        <v>-781830.579914208</v>
       </c>
       <c r="D101">
-        <v>-24544.40629478671</v>
+        <v>25445.09862839477</v>
       </c>
       <c r="E101">
-        <v>-723310.2770176064</v>
+        <v>-807275.6785426028</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -13219,13 +13218,13 @@
         <v>2047</v>
       </c>
       <c r="C102">
-        <v>-752366.6492743274</v>
+        <v>-813042.9566765479</v>
       </c>
       <c r="D102">
-        <v>-18511.4147503011</v>
+        <v>26703.09771667259</v>
       </c>
       <c r="E102">
-        <v>-733855.2345240258</v>
+        <v>-839746.0543932206</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -13239,13 +13238,13 @@
         <v>2048</v>
       </c>
       <c r="C103">
-        <v>-753719.6836095334</v>
+        <v>-844200.3877086435</v>
       </c>
       <c r="D103">
-        <v>-11684.69952657628</v>
+        <v>27984.31075531759</v>
       </c>
       <c r="E103">
-        <v>-742034.9840829566</v>
+        <v>-872184.6984639612</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -13259,13 +13258,13 @@
         <v>2049</v>
       </c>
       <c r="C104">
-        <v>-734772.997140921</v>
+        <v>-850700.9904532835</v>
       </c>
       <c r="D104">
-        <v>-5540.060492816701</v>
+        <v>29032.7164705481</v>
       </c>
       <c r="E104">
-        <v>-729232.9366481039</v>
+        <v>-879733.706923832</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -13279,13 +13278,13 @@
         <v>2050</v>
       </c>
       <c r="C105">
-        <v>-730693.2319078671</v>
+        <v>-880234.8042136368</v>
       </c>
       <c r="D105">
-        <v>2372.702035463022</v>
+        <v>30270.33144260959</v>
       </c>
       <c r="E105">
-        <v>-733065.9339433298</v>
+        <v>-910505.1356562467</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -13299,16 +13298,16 @@
         <v>2025</v>
       </c>
       <c r="C106">
-        <v>130581.5036392</v>
+        <v>163226.879549</v>
       </c>
       <c r="D106">
         <v>0</v>
       </c>
       <c r="E106">
-        <v>130581.5036392</v>
+        <v>163226.879549</v>
       </c>
       <c r="F106">
-        <v>62679.12174681602</v>
+        <v>78348.90218352001</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -13319,16 +13318,16 @@
         <v>2026</v>
       </c>
       <c r="C107">
-        <v>114697.5214473608</v>
+        <v>141142.039827517</v>
       </c>
       <c r="D107">
         <v>0</v>
       </c>
       <c r="E107">
-        <v>114697.5214473608</v>
+        <v>141142.039827517</v>
       </c>
       <c r="F107">
-        <v>55054.81029473319</v>
+        <v>67748.17911720817</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -13339,16 +13338,16 @@
         <v>2027</v>
       </c>
       <c r="C108">
-        <v>51536.31888199427</v>
+        <v>61670.87343936614</v>
       </c>
       <c r="D108">
         <v>0</v>
       </c>
       <c r="E108">
-        <v>51536.31888199427</v>
+        <v>61670.87343936613</v>
       </c>
       <c r="F108">
-        <v>24737.43306335725</v>
+        <v>29602.01925089575</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -13359,16 +13358,16 @@
         <v>2028</v>
       </c>
       <c r="C109">
-        <v>48965.31174370463</v>
+        <v>57342.95726097634</v>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>48965.31174370465</v>
+        <v>57342.95726097636</v>
       </c>
       <c r="F109">
-        <v>23503.34963697823</v>
+        <v>27524.61948526865</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -13379,16 +13378,16 @@
         <v>2029</v>
       </c>
       <c r="C110">
-        <v>82445.52030563558</v>
+        <v>96309.52464064992</v>
       </c>
       <c r="D110">
         <v>0</v>
       </c>
       <c r="E110">
-        <v>82445.52030563558</v>
+        <v>96309.52464064992</v>
       </c>
       <c r="F110">
-        <v>39573.84974670508</v>
+        <v>46228.57182751197</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -13399,16 +13398,16 @@
         <v>2030</v>
       </c>
       <c r="C111">
-        <v>55783.58320654432</v>
+        <v>63348.99667493757</v>
       </c>
       <c r="D111">
         <v>0</v>
       </c>
       <c r="E111">
-        <v>55783.58320654431</v>
+        <v>63348.99667493756</v>
       </c>
       <c r="F111">
-        <v>26776.11993914128</v>
+        <v>30407.51840397003</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -13419,16 +13418,16 @@
         <v>2031</v>
       </c>
       <c r="C112">
-        <v>80735.6339081105</v>
+        <v>91544.04663234399</v>
       </c>
       <c r="D112">
         <v>0</v>
       </c>
       <c r="E112">
-        <v>80735.63390811048</v>
+        <v>91544.04663234402</v>
       </c>
       <c r="F112">
-        <v>38753.10427589304</v>
+        <v>43941.14238352513</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -13439,16 +13438,16 @@
         <v>2032</v>
       </c>
       <c r="C113">
-        <v>59669.75697958359</v>
+        <v>65875.06028355777</v>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>59669.75697958359</v>
+        <v>65875.06028355777</v>
       </c>
       <c r="F113">
-        <v>28641.48335020012</v>
+        <v>31620.02893610773</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -13459,16 +13458,16 @@
         <v>2033</v>
       </c>
       <c r="C114">
-        <v>74725.29240564044</v>
+        <v>82205.52341058938</v>
       </c>
       <c r="D114">
         <v>0</v>
       </c>
       <c r="E114">
-        <v>74725.29240564044</v>
+        <v>82205.52341058938</v>
       </c>
       <c r="F114">
-        <v>35868.14035470742</v>
+        <v>39458.6512370829</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -13479,16 +13478,16 @@
         <v>2034</v>
       </c>
       <c r="C115">
-        <v>42640.2052860563</v>
+        <v>44697.50994492948</v>
       </c>
       <c r="D115">
         <v>0</v>
       </c>
       <c r="E115">
-        <v>42640.2052860563</v>
+        <v>44697.50994492951</v>
       </c>
       <c r="F115">
-        <v>20467.29853730703</v>
+        <v>21454.80477356617</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -13499,16 +13498,16 @@
         <v>2035</v>
       </c>
       <c r="C116">
-        <v>35039.04778829764</v>
+        <v>35547.30997286443</v>
       </c>
       <c r="D116">
         <v>0</v>
       </c>
       <c r="E116">
-        <v>35039.04778829764</v>
+        <v>35547.30997286443</v>
       </c>
       <c r="F116">
-        <v>16818.74293838287</v>
+        <v>17062.70878697492</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -13519,16 +13518,16 @@
         <v>2036</v>
       </c>
       <c r="C117">
-        <v>37776.46279868277</v>
+        <v>38171.99240907552</v>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>37776.46279868277</v>
+        <v>38171.99240907552</v>
       </c>
       <c r="F117">
-        <v>18132.70214336773</v>
+        <v>18322.55635635626</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -13539,16 +13538,16 @@
         <v>2037</v>
       </c>
       <c r="C118">
-        <v>72846.01605701339</v>
+        <v>76506.87540185312</v>
       </c>
       <c r="D118">
         <v>0</v>
       </c>
       <c r="E118">
-        <v>72846.01605701339</v>
+        <v>76506.87540185312</v>
       </c>
       <c r="F118">
-        <v>34966.08770736644</v>
+        <v>36723.30019288951</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -13559,16 +13558,16 @@
         <v>2038</v>
       </c>
       <c r="C119">
-        <v>57638.05673432391</v>
+        <v>59031.51130325891</v>
       </c>
       <c r="D119">
         <v>0</v>
       </c>
       <c r="E119">
-        <v>57638.05673432391</v>
+        <v>59031.51130325891</v>
       </c>
       <c r="F119">
-        <v>27666.26723247548</v>
+        <v>28335.12542556429</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -13579,16 +13578,16 @@
         <v>2039</v>
       </c>
       <c r="C120">
-        <v>28820.46506678869</v>
+        <v>27080.33054422622</v>
       </c>
       <c r="D120">
         <v>0</v>
       </c>
       <c r="E120">
-        <v>28820.46506678869</v>
+        <v>27080.33054422625</v>
       </c>
       <c r="F120">
-        <v>13833.82323205858</v>
+        <v>12998.5586612286</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -13599,16 +13598,16 @@
         <v>2040</v>
       </c>
       <c r="C121">
-        <v>78975.14993248548</v>
+        <v>80786.17223117891</v>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121">
-        <v>78975.14993248551</v>
+        <v>80786.17223117891</v>
       </c>
       <c r="F121">
-        <v>37908.07196759304</v>
+        <v>38777.36267096587</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -13619,16 +13618,16 @@
         <v>2041</v>
       </c>
       <c r="C122">
-        <v>29064.2093230981</v>
+        <v>26645.65564981592</v>
       </c>
       <c r="D122">
         <v>0</v>
       </c>
       <c r="E122">
-        <v>29064.2093230981</v>
+        <v>26645.65564981592</v>
       </c>
       <c r="F122">
-        <v>13950.82047508709</v>
+        <v>12789.91471191164</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -13639,16 +13638,16 @@
         <v>2042</v>
       </c>
       <c r="C123">
-        <v>53549.41574170484</v>
+        <v>52285.83790345213</v>
       </c>
       <c r="D123">
         <v>0</v>
       </c>
       <c r="E123">
-        <v>53549.41574170484</v>
+        <v>52285.83790345216</v>
       </c>
       <c r="F123">
-        <v>25703.71955601833</v>
+        <v>25097.20219365704</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -13659,16 +13658,16 @@
         <v>2043</v>
       </c>
       <c r="C124">
-        <v>45320.7876035884</v>
+        <v>43112.29829766985</v>
       </c>
       <c r="D124">
         <v>0</v>
       </c>
       <c r="E124">
-        <v>45320.7876035884</v>
+        <v>43112.29829766985</v>
       </c>
       <c r="F124">
-        <v>21753.97804972243</v>
+        <v>20693.90318288154</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -13679,16 +13678,16 @@
         <v>2044</v>
       </c>
       <c r="C125">
-        <v>23665.22772401772</v>
+        <v>20079.4255477266</v>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125">
-        <v>23665.22772401772</v>
+        <v>20079.4255477266</v>
       </c>
       <c r="F125">
-        <v>11359.3093075285</v>
+        <v>9638.124262908779</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -13699,16 +13698,16 @@
         <v>2045</v>
       </c>
       <c r="C126">
-        <v>35733.02142520034</v>
+        <v>32370.7153456129</v>
       </c>
       <c r="D126">
         <v>0</v>
       </c>
       <c r="E126">
-        <v>35733.02142520034</v>
+        <v>32370.7153456129</v>
       </c>
       <c r="F126">
-        <v>17151.85028409616</v>
+        <v>15537.9433658942</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -13719,16 +13718,16 @@
         <v>2046</v>
       </c>
       <c r="C127">
-        <v>57338.56905989588</v>
+        <v>54287.41040679076</v>
       </c>
       <c r="D127">
         <v>0</v>
       </c>
       <c r="E127">
-        <v>57338.56905989588</v>
+        <v>54287.41040679073</v>
       </c>
       <c r="F127">
-        <v>27522.51314875003</v>
+        <v>26057.95699525956</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -13739,16 +13738,16 @@
         <v>2047</v>
       </c>
       <c r="C128">
-        <v>57665.82340313104</v>
+        <v>54122.49766792954</v>
       </c>
       <c r="D128">
         <v>0</v>
       </c>
       <c r="E128">
-        <v>57665.82340313104</v>
+        <v>54122.49766792954</v>
       </c>
       <c r="F128">
-        <v>27679.59523350291</v>
+        <v>25978.79888060619</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -13759,16 +13758,16 @@
         <v>2048</v>
       </c>
       <c r="C129">
-        <v>13126.31731328543</v>
+        <v>8455.625255852327</v>
       </c>
       <c r="D129">
         <v>0</v>
       </c>
       <c r="E129">
-        <v>13126.31731328543</v>
+        <v>8455.625255852327</v>
       </c>
       <c r="F129">
-        <v>6300.632310376997</v>
+        <v>4058.70012280911</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -13779,16 +13778,16 @@
         <v>2049</v>
       </c>
       <c r="C130">
-        <v>55978.11790341104</v>
+        <v>51474.18997536603</v>
       </c>
       <c r="D130">
         <v>0</v>
       </c>
       <c r="E130">
-        <v>55978.11790341104</v>
+        <v>51474.18997536603</v>
       </c>
       <c r="F130">
-        <v>26869.49659363729</v>
+        <v>24707.6111881757</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -13799,16 +13798,16 @@
         <v>2050</v>
       </c>
       <c r="C131">
-        <v>48433.19578885543</v>
+        <v>43472.88475245729</v>
       </c>
       <c r="D131">
         <v>0</v>
       </c>
       <c r="E131">
-        <v>48433.19578885543</v>
+        <v>43472.88475245729</v>
       </c>
       <c r="F131">
-        <v>23247.93397865062</v>
+        <v>20866.9846811795</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -13839,16 +13838,16 @@
         <v>2026</v>
       </c>
       <c r="C133">
-        <v>130581.5036392</v>
+        <v>163226.879549</v>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>130581.5036392</v>
+        <v>163226.879549</v>
       </c>
       <c r="F133">
-        <v>62679.12174681602</v>
+        <v>78348.90218352001</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -13859,16 +13858,16 @@
         <v>2027</v>
       </c>
       <c r="C134">
-        <v>245279.0250865608</v>
+        <v>304368.9193765171</v>
       </c>
       <c r="D134">
         <v>0</v>
       </c>
       <c r="E134">
-        <v>245279.0250865608</v>
+        <v>304368.9193765171</v>
       </c>
       <c r="F134">
-        <v>117733.9320415492</v>
+        <v>146097.0813007282</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -13879,16 +13878,16 @@
         <v>2028</v>
       </c>
       <c r="C135">
-        <v>296815.3439685551</v>
+        <v>366039.7928158832</v>
       </c>
       <c r="D135">
         <v>0</v>
       </c>
       <c r="E135">
-        <v>296815.3439685551</v>
+        <v>366039.7928158832</v>
       </c>
       <c r="F135">
-        <v>142471.3651049065</v>
+        <v>175699.1005516239</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -13899,16 +13898,16 @@
         <v>2029</v>
       </c>
       <c r="C136">
-        <v>345780.6557122597</v>
+        <v>423382.7500768595</v>
       </c>
       <c r="D136">
         <v>0</v>
       </c>
       <c r="E136">
-        <v>345780.6557122598</v>
+        <v>423382.7500768595</v>
       </c>
       <c r="F136">
-        <v>165974.7147418847</v>
+        <v>203223.7200368926</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -13919,16 +13918,16 @@
         <v>2030</v>
       </c>
       <c r="C137">
-        <v>428226.1760178953</v>
+        <v>519692.2747175094</v>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>428226.1760178953</v>
+        <v>519692.2747175095</v>
       </c>
       <c r="F137">
-        <v>205548.5644885898</v>
+        <v>249452.2918644046</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -13939,16 +13938,16 @@
         <v>2031</v>
       </c>
       <c r="C138">
-        <v>484009.7592244396</v>
+        <v>583041.2713924469</v>
       </c>
       <c r="D138">
         <v>0</v>
       </c>
       <c r="E138">
-        <v>484009.7592244396</v>
+        <v>583041.2713924471</v>
       </c>
       <c r="F138">
-        <v>232324.684427731</v>
+        <v>279859.8102683746</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -13959,16 +13958,16 @@
         <v>2032</v>
       </c>
       <c r="C139">
-        <v>564745.3931325502</v>
+        <v>674585.318024791</v>
       </c>
       <c r="D139">
         <v>0</v>
       </c>
       <c r="E139">
-        <v>564745.3931325501</v>
+        <v>674585.3180247911</v>
       </c>
       <c r="F139">
-        <v>271077.788703624</v>
+        <v>323800.9526518998</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -13979,16 +13978,16 @@
         <v>2033</v>
       </c>
       <c r="C140">
-        <v>624415.1501121337</v>
+        <v>740460.3783083487</v>
       </c>
       <c r="D140">
         <v>0</v>
       </c>
       <c r="E140">
-        <v>624415.1501121337</v>
+        <v>740460.3783083488</v>
       </c>
       <c r="F140">
-        <v>299719.2720538242</v>
+        <v>355420.9815880075</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -13999,16 +13998,16 @@
         <v>2034</v>
       </c>
       <c r="C141">
-        <v>699140.4425177742</v>
+        <v>822665.901718938</v>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>699140.4425177742</v>
+        <v>822665.9017189383</v>
       </c>
       <c r="F141">
-        <v>335587.4124085316</v>
+        <v>394879.6328250904</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -14019,16 +14018,16 @@
         <v>2035</v>
       </c>
       <c r="C142">
-        <v>741780.6478038304</v>
+        <v>867363.4116638675</v>
       </c>
       <c r="D142">
         <v>0</v>
       </c>
       <c r="E142">
-        <v>741780.6478038304</v>
+        <v>867363.4116638678</v>
       </c>
       <c r="F142">
-        <v>356054.7109458386</v>
+        <v>416334.4375986566</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -14039,16 +14038,16 @@
         <v>2036</v>
       </c>
       <c r="C143">
-        <v>776819.6955921281</v>
+        <v>902910.721636732</v>
       </c>
       <c r="D143">
         <v>0</v>
       </c>
       <c r="E143">
-        <v>776819.6955921281</v>
+        <v>902910.7216367322</v>
       </c>
       <c r="F143">
-        <v>372873.4538842215</v>
+        <v>433397.1463856315</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -14059,16 +14058,16 @@
         <v>2037</v>
       </c>
       <c r="C144">
-        <v>814596.1583908108</v>
+        <v>941082.7140458075</v>
       </c>
       <c r="D144">
         <v>0</v>
       </c>
       <c r="E144">
-        <v>814596.1583908108</v>
+        <v>941082.7140458077</v>
       </c>
       <c r="F144">
-        <v>391006.1560275892</v>
+        <v>451719.7027419878</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -14079,16 +14078,16 @@
         <v>2038</v>
       </c>
       <c r="C145">
-        <v>887442.1744478242</v>
+        <v>1017589.589447661</v>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>887442.1744478242</v>
+        <v>1017589.589447661</v>
       </c>
       <c r="F145">
-        <v>425972.2437349557</v>
+        <v>488443.0029348773</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -14099,16 +14098,16 @@
         <v>2039</v>
       </c>
       <c r="C146">
-        <v>945080.2311821482</v>
+        <v>1076621.100750919</v>
       </c>
       <c r="D146">
         <v>0</v>
       </c>
       <c r="E146">
-        <v>945080.2311821482</v>
+        <v>1076621.10075092</v>
       </c>
       <c r="F146">
-        <v>453638.5109674311</v>
+        <v>516778.1283604416</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -14119,16 +14118,16 @@
         <v>2040</v>
       </c>
       <c r="C147">
-        <v>973900.6962489369</v>
+        <v>1103701.431295146</v>
       </c>
       <c r="D147">
         <v>0</v>
       </c>
       <c r="E147">
-        <v>973900.6962489369</v>
+        <v>1103701.431295146</v>
       </c>
       <c r="F147">
-        <v>467472.3341994897</v>
+        <v>529776.6870216702</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -14139,16 +14138,16 @@
         <v>2041</v>
       </c>
       <c r="C148">
-        <v>1052875.846181422</v>
+        <v>1184487.603526325</v>
       </c>
       <c r="D148">
         <v>0</v>
       </c>
       <c r="E148">
-        <v>1052875.846181422</v>
+        <v>1184487.603526325</v>
       </c>
       <c r="F148">
-        <v>505380.4061670827</v>
+        <v>568554.049692636</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -14159,16 +14158,16 @@
         <v>2042</v>
       </c>
       <c r="C149">
-        <v>1081940.055504521</v>
+        <v>1211133.259176141</v>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>1081940.055504521</v>
+        <v>1211133.259176141</v>
       </c>
       <c r="F149">
-        <v>519331.2266421698</v>
+        <v>581343.9644045476</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -14179,16 +14178,16 @@
         <v>2043</v>
       </c>
       <c r="C150">
-        <v>1135489.471246226</v>
+        <v>1263419.097079593</v>
       </c>
       <c r="D150">
         <v>0</v>
       </c>
       <c r="E150">
-        <v>1135489.471246226</v>
+        <v>1263419.097079593</v>
       </c>
       <c r="F150">
-        <v>545034.9461981881</v>
+        <v>606441.1665982046</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -14199,16 +14198,16 @@
         <v>2044</v>
       </c>
       <c r="C151">
-        <v>1180810.258849814</v>
+        <v>1306531.395377262</v>
       </c>
       <c r="D151">
         <v>0</v>
       </c>
       <c r="E151">
-        <v>1180810.258849814</v>
+        <v>1306531.395377263</v>
       </c>
       <c r="F151">
-        <v>566788.9242479105</v>
+        <v>627135.0697810862</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -14219,16 +14218,16 @@
         <v>2045</v>
       </c>
       <c r="C152">
-        <v>1204475.486573832</v>
+        <v>1326610.820924989</v>
       </c>
       <c r="D152">
         <v>0</v>
       </c>
       <c r="E152">
-        <v>1204475.486573832</v>
+        <v>1326610.82092499</v>
       </c>
       <c r="F152">
-        <v>578148.233555439</v>
+        <v>636773.194043995</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -14239,16 +14238,16 @@
         <v>2046</v>
       </c>
       <c r="C153">
-        <v>1240208.507999032</v>
+        <v>1358981.536270602</v>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>1240208.507999032</v>
+        <v>1358981.536270603</v>
       </c>
       <c r="F153">
-        <v>595300.0838395352</v>
+        <v>652311.1374098891</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -14259,16 +14258,16 @@
         <v>2047</v>
       </c>
       <c r="C154">
-        <v>1297547.077058928</v>
+        <v>1413268.946677393</v>
       </c>
       <c r="D154">
         <v>0</v>
       </c>
       <c r="E154">
-        <v>1297547.077058928</v>
+        <v>1413268.946677393</v>
       </c>
       <c r="F154">
-        <v>622822.5969882853</v>
+        <v>678369.0944051486</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -14279,16 +14278,16 @@
         <v>2048</v>
       </c>
       <c r="C155">
-        <v>1355212.900462059</v>
+        <v>1467391.444345322</v>
       </c>
       <c r="D155">
         <v>0</v>
       </c>
       <c r="E155">
-        <v>1355212.900462059</v>
+        <v>1467391.444345323</v>
       </c>
       <c r="F155">
-        <v>650502.1922217882</v>
+        <v>704347.8932857548</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -14299,16 +14298,16 @@
         <v>2049</v>
       </c>
       <c r="C156">
-        <v>1368339.217775344</v>
+        <v>1475847.069601175</v>
       </c>
       <c r="D156">
         <v>0</v>
       </c>
       <c r="E156">
-        <v>1368339.217775344</v>
+        <v>1475847.069601175</v>
       </c>
       <c r="F156">
-        <v>656802.8245321652</v>
+        <v>708406.593408564</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -14319,16 +14318,16 @@
         <v>2050</v>
       </c>
       <c r="C157">
-        <v>1424317.335678755</v>
+        <v>1527321.259576541</v>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>1424317.335678755</v>
+        <v>1527321.259576541</v>
       </c>
       <c r="F157">
-        <v>683672.3211258025</v>
+        <v>733114.2045967397</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -14339,10 +14338,10 @@
         <v>2025</v>
       </c>
       <c r="C158">
-        <v>18979.869715</v>
+        <v>16322.6879549</v>
       </c>
       <c r="D158">
-        <v>2657.181760100001</v>
+        <v>0</v>
       </c>
       <c r="E158">
         <v>16322.6879549</v>
@@ -14359,16 +14358,16 @@
         <v>2026</v>
       </c>
       <c r="C159">
-        <v>22379.40470429181</v>
+        <v>18390.36520047459</v>
       </c>
       <c r="D159">
-        <v>3146.006826872001</v>
+        <v>0</v>
       </c>
       <c r="E159">
-        <v>19233.3978774198</v>
+        <v>18390.36520047459</v>
       </c>
       <c r="F159">
-        <v>9184.153213297241</v>
+        <v>8827.375296227801</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -14379,16 +14378,16 @@
         <v>2027</v>
       </c>
       <c r="C160">
-        <v>17489.82535259275</v>
+        <v>13681.86363636063</v>
       </c>
       <c r="D160">
-        <v>2476.19993544</v>
+        <v>0</v>
       </c>
       <c r="E160">
-        <v>15013.62541715275</v>
+        <v>13681.86363636063</v>
       </c>
       <c r="F160">
-        <v>7103.935337661553</v>
+        <v>6567.294545453104</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -14399,16 +14398,16 @@
         <v>2028</v>
       </c>
       <c r="C161">
-        <v>18566.48740329364</v>
+        <v>13916.17372549858</v>
       </c>
       <c r="D161">
-        <v>2637.818750985601</v>
+        <v>0</v>
       </c>
       <c r="E161">
-        <v>15928.66865230804</v>
+        <v>13916.17372549858</v>
       </c>
       <c r="F161">
-        <v>7502.72189915975</v>
+        <v>6679.763388239317</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -14419,16 +14418,16 @@
         <v>2029</v>
       </c>
       <c r="C162">
-        <v>25079.35988283875</v>
+        <v>18157.64522981624</v>
       </c>
       <c r="D162">
-        <v>3560.854056888801</v>
+        <v>0</v>
       </c>
       <c r="E162">
-        <v>21518.50582594995</v>
+        <v>18157.64522981624</v>
       </c>
       <c r="F162">
-        <v>10144.12058137372</v>
+        <v>8715.669710311797</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -14439,16 +14438,16 @@
         <v>2030</v>
       </c>
       <c r="C163">
-        <v>23644.69264554009</v>
+        <v>16385.69618339579</v>
       </c>
       <c r="D163">
-        <v>3375.263522904001</v>
+        <v>0</v>
       </c>
       <c r="E163">
-        <v>20269.42912263609</v>
+        <v>16385.69618339579</v>
       </c>
       <c r="F163">
-        <v>9487.873069474166</v>
+        <v>7865.134168029978</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -14459,16 +14458,16 @@
         <v>2031</v>
       </c>
       <c r="C164">
-        <v>29032.66835615628</v>
+        <v>19466.19819091255</v>
       </c>
       <c r="D164">
-        <v>4143.333141304</v>
+        <v>0</v>
       </c>
       <c r="E164">
-        <v>24889.33521485228</v>
+        <v>19466.19819091255</v>
       </c>
       <c r="F164">
-        <v>11654.34535205836</v>
+        <v>9343.775131638022</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -14479,16 +14478,16 @@
         <v>2032</v>
       </c>
       <c r="C165">
-        <v>28107.90944294737</v>
+        <v>18086.03731723286</v>
       </c>
       <c r="D165">
-        <v>4030.802540620801</v>
+        <v>0</v>
       </c>
       <c r="E165">
-        <v>24077.10690232657</v>
+        <v>18086.03731723286</v>
       </c>
       <c r="F165">
-        <v>11201.57192971498</v>
+        <v>8681.297912271775</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -14499,16 +14498,16 @@
         <v>2033</v>
       </c>
       <c r="C166">
-        <v>31959.25590451297</v>
+        <v>19905.22956538553</v>
       </c>
       <c r="D166">
-        <v>4585.711239093602</v>
+        <v>0</v>
       </c>
       <c r="E166">
-        <v>27373.54466541937</v>
+        <v>19905.22956538553</v>
       </c>
       <c r="F166">
-        <v>12725.47276454324</v>
+        <v>9554.510191385052</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -14519,16 +14518,16 @@
         <v>2034</v>
       </c>
       <c r="C167">
-        <v>28639.06706879687</v>
+        <v>17064.8521300077</v>
       </c>
       <c r="D167">
-        <v>4138.681929916801</v>
+        <v>0</v>
       </c>
       <c r="E167">
-        <v>24500.38513888007</v>
+        <v>17064.8521300077</v>
       </c>
       <c r="F167">
-        <v>11280.25257417441</v>
+        <v>8191.129022403697</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -14539,16 +14538,16 @@
         <v>2035</v>
       </c>
       <c r="C168">
-        <v>27731.56620876749</v>
+        <v>15883.8380284666</v>
       </c>
       <c r="D168">
-        <v>4026.564903256001</v>
+        <v>0</v>
       </c>
       <c r="E168">
-        <v>23705.00130551149</v>
+        <v>15883.8380284666</v>
       </c>
       <c r="F168">
-        <v>10843.0025573966</v>
+        <v>7624.242253663968</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -14559,16 +14558,16 @@
         <v>2036</v>
       </c>
       <c r="C169">
-        <v>28251.61263484542</v>
+        <v>15625.54824334535</v>
       </c>
       <c r="D169">
-        <v>4113.187337750401</v>
+        <v>0</v>
       </c>
       <c r="E169">
-        <v>24138.42529709502</v>
+        <v>15625.54824334535</v>
       </c>
       <c r="F169">
-        <v>10999.72974393803</v>
+        <v>7500.26315680577</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -14579,16 +14578,16 @@
         <v>2037</v>
       </c>
       <c r="C170">
-        <v>34595.90598694509</v>
+        <v>18764.25996582202</v>
       </c>
       <c r="D170">
-        <v>5015.101101029602</v>
+        <v>0</v>
       </c>
       <c r="E170">
-        <v>29580.80488591549</v>
+        <v>18764.25996582202</v>
       </c>
       <c r="F170">
-        <v>13561.13908319808</v>
+        <v>9006.84478359457</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -14599,16 +14598,16 @@
         <v>2038</v>
       </c>
       <c r="C171">
-        <v>34017.12088573384</v>
+        <v>17795.87037201009</v>
       </c>
       <c r="D171">
-        <v>4951.643638155201</v>
+        <v>0</v>
       </c>
       <c r="E171">
-        <v>29065.47724757863</v>
+        <v>17795.87037201009</v>
       </c>
       <c r="F171">
-        <v>13248.51271198573</v>
+        <v>8542.017778564843</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -14619,16 +14618,16 @@
         <v>2039</v>
       </c>
       <c r="C172">
-        <v>30118.56628509035</v>
+        <v>15050.32680437312</v>
       </c>
       <c r="D172">
-        <v>4422.440909577601</v>
+        <v>0</v>
       </c>
       <c r="E172">
-        <v>25696.12537551275</v>
+        <v>15050.32680437312</v>
       </c>
       <c r="F172">
-        <v>11569.5855557763</v>
+        <v>7224.156866099101</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -14639,16 +14638,16 @@
         <v>2040</v>
       </c>
       <c r="C173">
-        <v>38788.04619037688</v>
+        <v>19213.66334538916</v>
       </c>
       <c r="D173">
-        <v>5649.570900288001</v>
+        <v>0</v>
       </c>
       <c r="E173">
-        <v>33138.47529008888</v>
+        <v>19213.66334538916</v>
       </c>
       <c r="F173">
-        <v>15092.13167145463</v>
+        <v>9222.558405786798</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -14659,16 +14658,16 @@
         <v>2041</v>
       </c>
       <c r="C174">
-        <v>32181.91659471808</v>
+        <v>15132.19024392781</v>
       </c>
       <c r="D174">
-        <v>4743.578566462401</v>
+        <v>0</v>
       </c>
       <c r="E174">
-        <v>27438.33802825568</v>
+        <v>15132.19024392781</v>
       </c>
       <c r="F174">
-        <v>12285.99277881293</v>
+        <v>7263.451317085349</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -14679,16 +14678,16 @@
         <v>2042</v>
       </c>
       <c r="C175">
-        <v>36305.64403173896</v>
+        <v>16763.40836223411</v>
       </c>
       <c r="D175">
-        <v>5334.661281600001</v>
+        <v>0</v>
       </c>
       <c r="E175">
-        <v>30970.98275013896</v>
+        <v>16763.40836223411</v>
       </c>
       <c r="F175">
-        <v>13930.55042777096</v>
+        <v>8046.436013872375</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -14699,16 +14698,16 @@
         <v>2043</v>
       </c>
       <c r="C176">
-        <v>35858.0810705724</v>
+        <v>16019.81899800729</v>
       </c>
       <c r="D176">
-        <v>5288.134694522401</v>
+        <v>0</v>
       </c>
       <c r="E176">
-        <v>30569.94637604999</v>
+        <v>16019.81899800729</v>
       </c>
       <c r="F176">
-        <v>13678.13326611844</v>
+        <v>7689.5131190435</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -14719,16 +14718,16 @@
         <v>2044</v>
       </c>
       <c r="C177">
-        <v>32455.92868558714</v>
+        <v>13869.42566262129</v>
       </c>
       <c r="D177">
-        <v>4827.1503196224</v>
+        <v>0</v>
       </c>
       <c r="E177">
-        <v>27628.77836596474</v>
+        <v>13869.42566262129</v>
       </c>
       <c r="F177">
-        <v>12209.48105928519</v>
+        <v>6657.324318058221</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -14739,16 +14738,16 @@
         <v>2045</v>
       </c>
       <c r="C178">
-        <v>34190.74157932608</v>
+        <v>14282.18424160463</v>
       </c>
       <c r="D178">
-        <v>5082.552745956001</v>
+        <v>0</v>
       </c>
       <c r="E178">
-        <v>29108.18883337008</v>
+        <v>14282.18424160463</v>
       </c>
       <c r="F178">
-        <v>12873.0632048592</v>
+        <v>6855.448435970222</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -14759,16 +14758,16 @@
         <v>2046</v>
       </c>
       <c r="C179">
-        <v>38515.5009943536</v>
+        <v>15883.32800744744</v>
       </c>
       <c r="D179">
-        <v>5701.352501096001</v>
+        <v>0</v>
       </c>
       <c r="E179">
-        <v>32814.1484932576</v>
+        <v>15883.32800744744</v>
       </c>
       <c r="F179">
-        <v>14602.39964689952</v>
+        <v>7623.997443574773</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -14779,16 +14778,16 @@
         <v>2047</v>
       </c>
       <c r="C180">
-        <v>40055.25801480321</v>
+        <v>16129.81805463594</v>
       </c>
       <c r="D180">
-        <v>5932.789653963201</v>
+        <v>0</v>
       </c>
       <c r="E180">
-        <v>34122.46836084002</v>
+        <v>16129.81805463594</v>
       </c>
       <c r="F180">
-        <v>15171.44312332328</v>
+        <v>7742.312666225252</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -14799,16 +14798,16 @@
         <v>2048</v>
       </c>
       <c r="C181">
-        <v>32975.41573709989</v>
+        <v>12501.90460625266</v>
       </c>
       <c r="D181">
-        <v>4958.040895180801</v>
+        <v>0</v>
       </c>
       <c r="E181">
-        <v>28017.37484191909</v>
+        <v>12501.90460625266</v>
       </c>
       <c r="F181">
-        <v>12179.97563959871</v>
+        <v>6000.914211001275</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -14819,16 +14818,16 @@
         <v>2049</v>
       </c>
       <c r="C182">
-        <v>40158.38628114431</v>
+        <v>15304.12572614405</v>
       </c>
       <c r="D182">
-        <v>5974.773726712</v>
+        <v>0</v>
       </c>
       <c r="E182">
-        <v>34183.61255443231</v>
+        <v>15304.12572614405</v>
       </c>
       <c r="F182">
-        <v>15098.47819310655</v>
+        <v>7345.980348549146</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -14839,16 +14838,16 @@
         <v>2050</v>
       </c>
       <c r="C183">
-        <v>40172.54392031163</v>
+        <v>14891.2223487789</v>
       </c>
       <c r="D183">
-        <v>5992.442702120002</v>
+        <v>0</v>
       </c>
       <c r="E183">
-        <v>34180.10121819163</v>
+        <v>14891.2223487789</v>
       </c>
       <c r="F183">
-        <v>15038.52710113403</v>
+        <v>7147.786727413873</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -14879,10 +14878,10 @@
         <v>2026</v>
       </c>
       <c r="C185">
-        <v>18979.869715</v>
+        <v>16322.6879549</v>
       </c>
       <c r="D185">
-        <v>2657.181760100001</v>
+        <v>0</v>
       </c>
       <c r="E185">
         <v>16322.6879549</v>
@@ -14899,16 +14898,16 @@
         <v>2027</v>
       </c>
       <c r="C186">
-        <v>41359.27441929181</v>
+        <v>34713.05315537459</v>
       </c>
       <c r="D186">
-        <v>5803.188586972002</v>
+        <v>0</v>
       </c>
       <c r="E186">
-        <v>35556.0858323198</v>
+        <v>34713.05315537459</v>
       </c>
       <c r="F186">
-        <v>17019.04343164924</v>
+        <v>16662.26551457981</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -14919,16 +14918,16 @@
         <v>2028</v>
       </c>
       <c r="C187">
-        <v>58849.09977188456</v>
+        <v>48394.91679173522</v>
       </c>
       <c r="D187">
-        <v>8279.388522412002</v>
+        <v>0</v>
       </c>
       <c r="E187">
-        <v>50569.71124947256</v>
+        <v>48394.91679173522</v>
       </c>
       <c r="F187">
-        <v>24122.97876931079</v>
+        <v>23229.56006003291</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -14939,16 +14938,16 @@
         <v>2029</v>
       </c>
       <c r="C188">
-        <v>77415.5871751782</v>
+        <v>62311.0905172338</v>
       </c>
       <c r="D188">
-        <v>10917.2072733976</v>
+        <v>0</v>
       </c>
       <c r="E188">
-        <v>66498.3799017806</v>
+        <v>62311.0905172338</v>
       </c>
       <c r="F188">
-        <v>31625.70066847054</v>
+        <v>29909.32344827223</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -14959,16 +14958,16 @@
         <v>2030</v>
       </c>
       <c r="C189">
-        <v>102494.9470580169</v>
+        <v>80468.73574705004</v>
       </c>
       <c r="D189">
-        <v>14478.0613302864</v>
+        <v>0</v>
       </c>
       <c r="E189">
-        <v>88016.88572773055</v>
+        <v>80468.73574705004</v>
       </c>
       <c r="F189">
-        <v>41769.82124984427</v>
+        <v>38624.99315858402</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -14979,16 +14978,16 @@
         <v>2031</v>
       </c>
       <c r="C190">
-        <v>126139.639703557</v>
+        <v>96854.43193044583</v>
       </c>
       <c r="D190">
-        <v>17853.3248531904</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>108286.3148503666</v>
+        <v>96854.43193044583</v>
       </c>
       <c r="F190">
-        <v>51257.69431931843</v>
+        <v>46490.12732661401</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -14999,16 +14998,16 @@
         <v>2032</v>
       </c>
       <c r="C191">
-        <v>155172.3080597133</v>
+        <v>116320.6301213584</v>
       </c>
       <c r="D191">
-        <v>21996.6579944944</v>
+        <v>0</v>
       </c>
       <c r="E191">
-        <v>133175.6500652189</v>
+        <v>116320.6301213584</v>
       </c>
       <c r="F191">
-        <v>62912.03967137679</v>
+        <v>55833.90245825203</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -15019,16 +15018,16 @@
         <v>2033</v>
       </c>
       <c r="C192">
-        <v>183280.2175026607</v>
+        <v>134406.6674385912</v>
       </c>
       <c r="D192">
-        <v>26027.4605351152</v>
+        <v>0</v>
       </c>
       <c r="E192">
-        <v>157252.7569675455</v>
+        <v>134406.6674385912</v>
       </c>
       <c r="F192">
-        <v>74113.61160109178</v>
+        <v>64515.2003705238</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -15039,16 +15038,16 @@
         <v>2034</v>
       </c>
       <c r="C193">
-        <v>215239.4734071737</v>
+        <v>154311.8970039768</v>
       </c>
       <c r="D193">
-        <v>30613.1717742088</v>
+        <v>0</v>
       </c>
       <c r="E193">
-        <v>184626.3016329649</v>
+        <v>154311.8970039768</v>
       </c>
       <c r="F193">
-        <v>86839.08436563502</v>
+        <v>74069.71056190885</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -15059,16 +15058,16 @@
         <v>2035</v>
       </c>
       <c r="C194">
-        <v>243878.5404759705</v>
+        <v>171376.7491339845</v>
       </c>
       <c r="D194">
-        <v>34751.85370412561</v>
+        <v>0</v>
       </c>
       <c r="E194">
-        <v>209126.686771845</v>
+        <v>171376.7491339845</v>
       </c>
       <c r="F194">
-        <v>98119.33693980942</v>
+        <v>82260.83958431255</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -15079,16 +15078,16 @@
         <v>2036</v>
       </c>
       <c r="C195">
-        <v>271610.106684738</v>
+        <v>187260.5871624511</v>
       </c>
       <c r="D195">
-        <v>38778.41860738161</v>
+        <v>0</v>
       </c>
       <c r="E195">
-        <v>232831.6880773564</v>
+        <v>187260.5871624511</v>
       </c>
       <c r="F195">
-        <v>108962.339497206</v>
+        <v>89885.08183797651</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -15099,16 +15098,16 @@
         <v>2037</v>
       </c>
       <c r="C196">
-        <v>299861.7193195834</v>
+        <v>202886.1354057964</v>
       </c>
       <c r="D196">
-        <v>42891.60594513201</v>
+        <v>0</v>
       </c>
       <c r="E196">
-        <v>256970.1133744515</v>
+        <v>202886.1354057964</v>
       </c>
       <c r="F196">
-        <v>119962.0692411441</v>
+        <v>97385.34499478228</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -15119,16 +15118,16 @@
         <v>2038</v>
       </c>
       <c r="C197">
-        <v>334457.6253065285</v>
+        <v>221650.3953716184</v>
       </c>
       <c r="D197">
-        <v>47906.70704616161</v>
+        <v>0</v>
       </c>
       <c r="E197">
-        <v>286550.9182603669</v>
+        <v>221650.3953716184</v>
       </c>
       <c r="F197">
-        <v>133523.2083243421</v>
+        <v>106392.1897783769</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -15139,16 +15138,16 @@
         <v>2039</v>
       </c>
       <c r="C198">
-        <v>368474.7461922624</v>
+        <v>239446.2657436285</v>
       </c>
       <c r="D198">
-        <v>52858.35068431681</v>
+        <v>0</v>
       </c>
       <c r="E198">
-        <v>315616.3955079456</v>
+        <v>239446.2657436285</v>
       </c>
       <c r="F198">
-        <v>146771.7210363279</v>
+        <v>114934.2075569417</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -15159,16 +15158,16 @@
         <v>2040</v>
       </c>
       <c r="C199">
-        <v>398593.3124773527</v>
+        <v>254496.5925480016</v>
       </c>
       <c r="D199">
-        <v>57280.79159389441</v>
+        <v>0</v>
       </c>
       <c r="E199">
-        <v>341312.5208834583</v>
+        <v>254496.5925480016</v>
       </c>
       <c r="F199">
-        <v>158341.3065921042</v>
+        <v>122158.3644230408</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -15179,16 +15178,16 @@
         <v>2041</v>
       </c>
       <c r="C200">
-        <v>437381.3586677296</v>
+        <v>273710.2558933908</v>
       </c>
       <c r="D200">
-        <v>62930.36249418242</v>
+        <v>0</v>
       </c>
       <c r="E200">
-        <v>374450.9961735472</v>
+        <v>273710.2558933908</v>
       </c>
       <c r="F200">
-        <v>173433.4382635588</v>
+        <v>131380.9228288276</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -15199,16 +15198,16 @@
         <v>2042</v>
       </c>
       <c r="C201">
-        <v>469563.2752624477</v>
+        <v>288842.4461373186</v>
       </c>
       <c r="D201">
-        <v>67673.94106064482</v>
+        <v>0</v>
       </c>
       <c r="E201">
-        <v>401889.3342018028</v>
+        <v>288842.4461373186</v>
       </c>
       <c r="F201">
-        <v>185719.4310423717</v>
+        <v>138644.374145913</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -15219,16 +15218,16 @@
         <v>2043</v>
       </c>
       <c r="C202">
-        <v>505868.9192941866</v>
+        <v>305605.8544995527</v>
       </c>
       <c r="D202">
-        <v>73008.60234224482</v>
+        <v>0</v>
       </c>
       <c r="E202">
-        <v>432860.3169519418</v>
+        <v>305605.8544995527</v>
       </c>
       <c r="F202">
-        <v>199649.9814701427</v>
+        <v>146690.8101597854</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -15239,16 +15238,16 @@
         <v>2044</v>
       </c>
       <c r="C203">
-        <v>541727.000364759</v>
+        <v>321625.67349756</v>
       </c>
       <c r="D203">
-        <v>78296.73703676723</v>
+        <v>0</v>
       </c>
       <c r="E203">
-        <v>463430.2633279918</v>
+        <v>321625.67349756</v>
       </c>
       <c r="F203">
-        <v>213328.1147362611</v>
+        <v>154380.3232788288</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -15259,16 +15258,16 @@
         <v>2045</v>
       </c>
       <c r="C204">
-        <v>574182.9290503461</v>
+        <v>335495.0991601813</v>
       </c>
       <c r="D204">
-        <v>83123.88735638963</v>
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>491059.0416939566</v>
+        <v>335495.0991601813</v>
       </c>
       <c r="F204">
-        <v>225537.5957955463</v>
+        <v>161037.6475968871</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -15279,16 +15278,16 @@
         <v>2046</v>
       </c>
       <c r="C205">
-        <v>608373.6706296722</v>
+        <v>349777.2834017859</v>
       </c>
       <c r="D205">
-        <v>88206.44010234563</v>
+        <v>0</v>
       </c>
       <c r="E205">
-        <v>520167.2305273267</v>
+        <v>349777.2834017859</v>
       </c>
       <c r="F205">
-        <v>238410.6590004055</v>
+        <v>167893.0960328573</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -15299,16 +15298,16 @@
         <v>2047</v>
       </c>
       <c r="C206">
-        <v>646889.1716240258</v>
+        <v>365660.6114092334</v>
       </c>
       <c r="D206">
-        <v>93907.79260344163</v>
+        <v>0</v>
       </c>
       <c r="E206">
-        <v>552981.3790205843</v>
+        <v>365660.6114092334</v>
       </c>
       <c r="F206">
-        <v>253013.058647305</v>
+        <v>175517.0934764321</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -15319,16 +15318,16 @@
         <v>2048</v>
       </c>
       <c r="C207">
-        <v>686944.429638829</v>
+        <v>381790.4294638693</v>
       </c>
       <c r="D207">
-        <v>99840.58225740484</v>
+        <v>0</v>
       </c>
       <c r="E207">
-        <v>587103.8473814243</v>
+        <v>381790.4294638693</v>
       </c>
       <c r="F207">
-        <v>268184.5017706283</v>
+        <v>183259.4061426573</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -15339,16 +15338,16 @@
         <v>2049</v>
       </c>
       <c r="C208">
-        <v>719919.8453759289</v>
+        <v>394292.334070122</v>
       </c>
       <c r="D208">
-        <v>104798.6231525856</v>
+        <v>0</v>
       </c>
       <c r="E208">
-        <v>615121.2222233433</v>
+        <v>394292.334070122</v>
       </c>
       <c r="F208">
-        <v>280364.4774102271</v>
+        <v>189260.3203536586</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -15359,16 +15358,16 @@
         <v>2050</v>
       </c>
       <c r="C209">
-        <v>760078.2316570733</v>
+        <v>409596.459796266</v>
       </c>
       <c r="D209">
-        <v>110773.3968792976</v>
+        <v>0</v>
       </c>
       <c r="E209">
-        <v>649304.8347777757</v>
+        <v>409596.459796266</v>
       </c>
       <c r="F209">
-        <v>295462.9556033336</v>
+        <v>196606.3007022078</v>
       </c>
     </row>
   </sheetData>
